--- a/research/traditional_assets/database/data/china/china_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/china/china_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ38"/>
+  <dimension ref="A1:AQ36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0751</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="E2">
-        <v>0.101</v>
+        <v>0.0925</v>
       </c>
       <c r="F2">
-        <v>0.12335</v>
+        <v>0.1068</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.002178602949728872</v>
+        <v>4.10401258220923e-05</v>
       </c>
       <c r="J2">
-        <v>0.001885044082539893</v>
+        <v>3.668930599886688e-05</v>
       </c>
       <c r="K2">
-        <v>25001.3</v>
+        <v>26118.6</v>
       </c>
       <c r="L2">
-        <v>0.4523083714307941</v>
+        <v>0.4636308931053396</v>
       </c>
       <c r="M2">
-        <v>5515.1727</v>
+        <v>7802.3445</v>
       </c>
       <c r="N2">
-        <v>0.02953761925139074</v>
+        <v>0.04775227504879367</v>
       </c>
       <c r="O2">
-        <v>0.2205954370372741</v>
+        <v>0.298727516023064</v>
       </c>
       <c r="P2">
-        <v>5510.2427</v>
+        <v>5434.6445</v>
       </c>
       <c r="Q2">
-        <v>0.02951121564250478</v>
+        <v>0.03326136636961028</v>
       </c>
       <c r="R2">
-        <v>0.2203982472911409</v>
+        <v>0.2080756434112089</v>
       </c>
       <c r="S2">
-        <v>4.93</v>
+        <v>2367.7</v>
       </c>
       <c r="T2">
-        <v>0.0008938976652535286</v>
+        <v>0.3034600689574781</v>
       </c>
       <c r="U2">
-        <v>127885.3</v>
+        <v>111202.4</v>
       </c>
       <c r="V2">
-        <v>0.6849155057737142</v>
+        <v>0.6805861482899112</v>
       </c>
       <c r="W2">
-        <v>0.1149091453698046</v>
+        <v>0.1003978822138432</v>
       </c>
       <c r="X2">
-        <v>0.1606282553324144</v>
+        <v>0.1620699428375477</v>
       </c>
       <c r="Y2">
-        <v>-0.04571910996260983</v>
+        <v>-0.06167206062370449</v>
       </c>
       <c r="Z2">
-        <v>0.06469952901404859</v>
+        <v>0.05670549964104371</v>
       </c>
       <c r="AA2">
-        <v>3.191442528704094e-05</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04572860901150145</v>
+        <v>0.06216009045976439</v>
       </c>
       <c r="AC2">
-        <v>-0.04560547947719871</v>
+        <v>-0.06216009045976439</v>
       </c>
       <c r="AD2">
-        <v>885203</v>
+        <v>906291.9</v>
       </c>
       <c r="AE2">
-        <v>1963.139699070158</v>
+        <v>4.085043079125059</v>
       </c>
       <c r="AF2">
-        <v>887166.1396990701</v>
+        <v>906295.9850430791</v>
       </c>
       <c r="AG2">
-        <v>759280.8396990701</v>
+        <v>795093.5850430791</v>
       </c>
       <c r="AH2">
-        <v>0.8261292029974484</v>
+        <v>0.8472525755081026</v>
       </c>
       <c r="AI2">
-        <v>0.7495550698095708</v>
+        <v>0.7568687595327264</v>
       </c>
       <c r="AJ2">
-        <v>0.8026243698432131</v>
+        <v>0.8295309960809103</v>
       </c>
       <c r="AK2">
-        <v>0.7192168372289895</v>
+        <v>0.7319781908984476</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1725.373745249001</v>
+        <v>289642.665388303</v>
       </c>
       <c r="AP2">
-        <v>1479.935366336751</v>
+        <v>254104.693206481</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Xi'an Co.,Ltd. (SHSE:600928)</t>
+          <t>Bank of Tianjin Co., Ltd. (SEHK:1578)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.034</v>
+        <v>-0.0187</v>
       </c>
       <c r="E3">
-        <v>0.0667</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,34 +731,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01141652156885174</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.0103691123799853</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>433.8</v>
+        <v>525.9</v>
       </c>
       <c r="L3">
-        <v>0.556296486278533</v>
+        <v>0.4271789456583543</v>
       </c>
       <c r="M3">
-        <v>166.6</v>
+        <v>0.151</v>
       </c>
       <c r="N3">
-        <v>0.05537827416566946</v>
+        <v>0.000101016858442601</v>
       </c>
       <c r="O3">
-        <v>0.384047948363301</v>
+        <v>0.0002871268301958547</v>
       </c>
       <c r="P3">
-        <v>166.6</v>
+        <v>0.151</v>
       </c>
       <c r="Q3">
-        <v>0.05537827416566946</v>
+        <v>0.000101016858442601</v>
       </c>
       <c r="R3">
-        <v>0.384047948363301</v>
+        <v>0.0002871268301958547</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,67 +767,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3056.8</v>
+        <v>2653.6</v>
       </c>
       <c r="V3">
-        <v>1.016088286132163</v>
+        <v>1.775220765319775</v>
       </c>
       <c r="W3">
-        <v>0.1190874900485903</v>
+        <v>0.06071836791243809</v>
       </c>
       <c r="X3">
-        <v>0.1462196077026818</v>
+        <v>0.5414868979000529</v>
       </c>
       <c r="Y3">
-        <v>-0.02713211765409146</v>
+        <v>-0.4807685299876148</v>
       </c>
       <c r="Z3">
-        <v>0.06642029782909156</v>
+        <v>0.03313568377506171</v>
       </c>
       <c r="AA3">
-        <v>0.0006887195325019443</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04567568790495583</v>
+        <v>0.0614221649796695</v>
       </c>
       <c r="AC3">
-        <v>-0.04498696837245389</v>
+        <v>-0.0614221649796695</v>
       </c>
       <c r="AD3">
-        <v>12720.9</v>
+        <v>36845.7</v>
       </c>
       <c r="AE3">
-        <v>54.98698240304705</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>12775.88698240305</v>
+        <v>36845.7</v>
       </c>
       <c r="AG3">
-        <v>9719.086982403045</v>
+        <v>34192.1</v>
       </c>
       <c r="AH3">
-        <v>0.8094053913645967</v>
+        <v>0.961012506357507</v>
       </c>
       <c r="AI3">
-        <v>0.7544702132914559</v>
+        <v>0.8032460596019271</v>
       </c>
       <c r="AJ3">
-        <v>0.7636296934218517</v>
+        <v>0.9581134814175509</v>
       </c>
       <c r="AK3">
-        <v>0.7003845338786046</v>
+        <v>0.7911651325623477</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>639.2412060301508</v>
-      </c>
-      <c r="AP3">
-        <v>488.3963307740224</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Chengdu Co., Ltd. (SHSE:601838)</t>
+          <t>Harbin Bank Co., Ltd. (SEHK:6138)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,6 +840,9 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.132</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -853,103 +850,97 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.007652211090744889</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.00681178025525081</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1079.2</v>
+        <v>-12.3</v>
       </c>
       <c r="L4">
-        <v>0.5847737740449743</v>
+        <v>-0.01495622568093385</v>
       </c>
       <c r="M4">
-        <v>335</v>
+        <v>1195.3</v>
       </c>
       <c r="N4">
-        <v>0.04909503920275519</v>
+        <v>2.530270956816258</v>
       </c>
       <c r="O4">
-        <v>0.3104151223128243</v>
+        <v>-97.17886178861788</v>
       </c>
       <c r="P4">
-        <v>335</v>
+        <v>1.1</v>
       </c>
       <c r="Q4">
-        <v>0.04909503920275519</v>
+        <v>0.002328535139712109</v>
       </c>
       <c r="R4">
-        <v>0.3104151223128243</v>
+        <v>-0.08943089430894309</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1194.2</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.999079728938342</v>
       </c>
       <c r="U4">
-        <v>6093.5</v>
+        <v>4882.6</v>
       </c>
       <c r="V4">
-        <v>0.8930167802447424</v>
+        <v>10.33573243014395</v>
       </c>
       <c r="W4">
-        <v>0.1922200056996295</v>
+        <v>-0.001368019485936092</v>
       </c>
       <c r="X4">
-        <v>0.113433080213688</v>
+        <v>0.5335373139061763</v>
       </c>
       <c r="Y4">
-        <v>0.07878692548594156</v>
+        <v>-0.5349053333921124</v>
       </c>
       <c r="Z4">
-        <v>0.1067992170800434</v>
+        <v>0.0677792887460337</v>
       </c>
       <c r="AA4">
-        <v>0.0007274927981820844</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04574007495795834</v>
+        <v>0.06142426131940251</v>
       </c>
       <c r="AC4">
-        <v>-0.04501258215977626</v>
+        <v>-0.06142426131940251</v>
       </c>
       <c r="AD4">
-        <v>19319.4</v>
+        <v>11450.2</v>
       </c>
       <c r="AE4">
-        <v>137.3892221601515</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>19456.78922216015</v>
+        <v>11450.2</v>
       </c>
       <c r="AG4">
-        <v>13363.28922216015</v>
+        <v>6567.6</v>
       </c>
       <c r="AH4">
-        <v>0.7403567387589378</v>
+        <v>0.9603777699495077</v>
       </c>
       <c r="AI4">
-        <v>0.7165035405565257</v>
+        <v>0.5497186641829739</v>
       </c>
       <c r="AJ4">
-        <v>0.6619819068349182</v>
+        <v>0.9328977272727274</v>
       </c>
       <c r="AK4">
-        <v>0.6344832592107527</v>
+        <v>0.4118495478660028</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>464.4086538461539</v>
-      </c>
-      <c r="AP4">
-        <v>321.2329139942345</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Suzhou Co., Ltd. (SZSE:002966)</t>
+          <t>Bank of Zhengzhou Co., Ltd. (SEHK:6196)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -968,6 +959,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.00594</v>
+      </c>
+      <c r="E5">
+        <v>-0.04190000000000001</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -975,34 +972,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.007254036495696298</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.006213683853787243</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>454.9</v>
+        <v>463.5</v>
       </c>
       <c r="L5">
-        <v>0.424386603227913</v>
+        <v>0.4254245066544287</v>
       </c>
       <c r="M5">
-        <v>354.4</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="N5">
-        <v>0.09976354014187591</v>
+        <v>0.0002802065964455651</v>
       </c>
       <c r="O5">
-        <v>0.7790723235876017</v>
+        <v>0.001486515641855448</v>
       </c>
       <c r="P5">
-        <v>354.4</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="Q5">
-        <v>0.09976354014187591</v>
+        <v>0.0002802065964455651</v>
       </c>
       <c r="R5">
-        <v>0.7790723235876017</v>
+        <v>0.001486515641855448</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,67 +1008,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2870.2</v>
+        <v>2277.4</v>
       </c>
       <c r="V5">
-        <v>0.8079608152235108</v>
+        <v>0.9261865061612916</v>
       </c>
       <c r="W5">
-        <v>0.1059681326872903</v>
+        <v>0.07369659580557454</v>
       </c>
       <c r="X5">
-        <v>0.1770683531353141</v>
+        <v>0.2340775063689042</v>
       </c>
       <c r="Y5">
-        <v>-0.07110022044802376</v>
+        <v>-0.1603809105633296</v>
       </c>
       <c r="Z5">
-        <v>0.0659228254949101</v>
+        <v>0.03626541155167363</v>
       </c>
       <c r="AA5">
-        <v>0.0004096235963737569</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04564011755782917</v>
+        <v>0.06163179004008361</v>
       </c>
       <c r="AC5">
-        <v>-0.04523049396145541</v>
+        <v>-0.06163179004008361</v>
       </c>
       <c r="AD5">
-        <v>19699.7</v>
+        <v>21540.1</v>
       </c>
       <c r="AE5">
-        <v>50.1219914013157</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>19749.82199140132</v>
+        <v>21540.1</v>
       </c>
       <c r="AG5">
-        <v>16879.62199140132</v>
+        <v>19262.7</v>
       </c>
       <c r="AH5">
-        <v>0.8475510188980749</v>
+        <v>0.8975415642318429</v>
       </c>
       <c r="AI5">
-        <v>0.7914579635938404</v>
+        <v>0.7080342116335332</v>
       </c>
       <c r="AJ5">
-        <v>0.8261356609005704</v>
+        <v>0.8867993149675898</v>
       </c>
       <c r="AK5">
-        <v>0.7643537112410671</v>
+        <v>0.6844093089358678</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>1106.724719101124</v>
-      </c>
-      <c r="AP5">
-        <v>948.2933703034447</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wuxi Rural Commercial Bank Co.,Ltd (SHSE:600908)</t>
+          <t>Chongqing Rural Commercial Bank Co., Ltd. (SEHK:3618)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,10 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0751</v>
+        <v>0.0122</v>
       </c>
       <c r="E6">
-        <v>0.11</v>
+        <v>0.0317</v>
+      </c>
+      <c r="F6">
+        <v>0.06059999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,34 +1097,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.005198191494137284</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.004716513386700205</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>233.6</v>
+        <v>1412.7</v>
       </c>
       <c r="L6">
-        <v>0.5163572060123784</v>
+        <v>0.4900274029622949</v>
       </c>
       <c r="M6">
-        <v>153</v>
+        <v>427.6</v>
       </c>
       <c r="N6">
-        <v>0.09207992296581609</v>
+        <v>0.07937774972618761</v>
       </c>
       <c r="O6">
-        <v>0.6549657534246576</v>
+        <v>0.3026828059743753</v>
       </c>
       <c r="P6">
-        <v>153</v>
+        <v>427.6</v>
       </c>
       <c r="Q6">
-        <v>0.09207992296581609</v>
+        <v>0.07937774972618761</v>
       </c>
       <c r="R6">
-        <v>0.6549657534246576</v>
+        <v>0.3026828059743753</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,67 +1133,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1486.1</v>
+        <v>4679</v>
       </c>
       <c r="V6">
-        <v>0.8943789118921521</v>
+        <v>0.8685886131170061</v>
       </c>
       <c r="W6">
-        <v>0.1316278807685806</v>
+        <v>0.08741847254365663</v>
       </c>
       <c r="X6">
-        <v>0.09119091013784751</v>
+        <v>0.2285090884751501</v>
       </c>
       <c r="Y6">
-        <v>0.04043697063073308</v>
+        <v>-0.1410906159314935</v>
       </c>
       <c r="Z6">
-        <v>0.1132261993504216</v>
+        <v>0.04610124715954976</v>
       </c>
       <c r="AA6">
-        <v>0.0005340328849614495</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04581896861679403</v>
+        <v>0.06164207209601001</v>
       </c>
       <c r="AC6">
-        <v>-0.04528493573183258</v>
+        <v>-0.06164207209601001</v>
       </c>
       <c r="AD6">
-        <v>3155.6</v>
+        <v>45639.1</v>
       </c>
       <c r="AE6">
-        <v>9.541690840261463</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>3165.141690840261</v>
+        <v>45639.1</v>
       </c>
       <c r="AG6">
-        <v>1679.041690840261</v>
+        <v>40960.1</v>
       </c>
       <c r="AH6">
-        <v>0.6557512072474836</v>
+        <v>0.8944283306549602</v>
       </c>
       <c r="AI6">
-        <v>0.5672559530911937</v>
+        <v>0.7391270549481516</v>
       </c>
       <c r="AJ6">
-        <v>0.5026105300200385</v>
+        <v>0.8837702548169245</v>
       </c>
       <c r="AK6">
-        <v>0.4101584402458098</v>
+        <v>0.7177382189411634</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>740.7511737089202</v>
-      </c>
-      <c r="AP6">
-        <v>394.141241981282</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jiangsu Zijin Rural Commercial Bank Co.,Ltd (SHSE:601860)</t>
+          <t>Bank of Guiyang Co.,Ltd. (SHSE:601997)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,10 +1207,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0459</v>
+        <v>0.0665</v>
       </c>
       <c r="E7">
-        <v>0.0721</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,34 +1219,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.005315077955849431</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.00485779833979996</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>228.4</v>
+        <v>855</v>
       </c>
       <c r="L7">
-        <v>0.4645108806182632</v>
+        <v>0.546989955856951</v>
       </c>
       <c r="M7">
-        <v>184.5</v>
+        <v>153.5604</v>
       </c>
       <c r="N7">
-        <v>0.09556614523982182</v>
+        <v>0.05276627035942548</v>
       </c>
       <c r="O7">
-        <v>0.8077933450087565</v>
+        <v>0.1796028070175439</v>
       </c>
       <c r="P7">
-        <v>184.5</v>
+        <v>153.5604</v>
       </c>
       <c r="Q7">
-        <v>0.09556614523982182</v>
+        <v>0.05276627035942548</v>
       </c>
       <c r="R7">
-        <v>0.8077933450087565</v>
+        <v>0.1796028070175439</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1267,67 +1255,61 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1777.3</v>
+        <v>1838.2</v>
       </c>
       <c r="V7">
-        <v>0.9205946337926033</v>
+        <v>0.631640437083362</v>
       </c>
       <c r="W7">
-        <v>0.1062721012469756</v>
+        <v>0.1198839019055231</v>
       </c>
       <c r="X7">
-        <v>0.1229016653560638</v>
+        <v>0.2195800806190417</v>
       </c>
       <c r="Y7">
-        <v>-0.01662956410908813</v>
+        <v>-0.09969617871351867</v>
       </c>
       <c r="Z7">
-        <v>0.07552841224588604</v>
+        <v>0.06127953519917514</v>
       </c>
       <c r="AA7">
-        <v>0.0003669017956157921</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04571714306504455</v>
+        <v>0.06165993055935257</v>
       </c>
       <c r="AC7">
-        <v>-0.04535024126942876</v>
+        <v>-0.06165993055935257</v>
       </c>
       <c r="AD7">
-        <v>6251.4</v>
+        <v>23312.8</v>
       </c>
       <c r="AE7">
-        <v>31.53288084554417</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>6282.932880845544</v>
+        <v>23312.8</v>
       </c>
       <c r="AG7">
-        <v>4505.632880845544</v>
+        <v>21474.6</v>
       </c>
       <c r="AH7">
-        <v>0.7649488925158776</v>
+        <v>0.8890210883575487</v>
       </c>
       <c r="AI7">
-        <v>0.7192386505260795</v>
+        <v>0.7426468948600735</v>
       </c>
       <c r="AJ7">
-        <v>0.7000419289138008</v>
+        <v>0.8806551622322102</v>
       </c>
       <c r="AK7">
-        <v>0.6475254504988676</v>
+        <v>0.7266396646059831</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>700.829596412556</v>
-      </c>
-      <c r="AP7">
-        <v>505.115793816765</v>
       </c>
     </row>
     <row r="8">
@@ -1346,6 +1328,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.105</v>
+      </c>
+      <c r="E8">
+        <v>0.108</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1353,100 +1341,97 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.003543644521725289</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.002903534475188694</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>951.2</v>
+        <v>930</v>
       </c>
       <c r="L8">
-        <v>0.442624476500698</v>
+        <v>0.4392801473714043</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>20</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.005074210326018014</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.02150537634408602</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>20</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.005074210326018014</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.02150537634408602</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>7426.7</v>
+        <v>2645.5</v>
       </c>
       <c r="V8">
-        <v>1.502103474778528</v>
+        <v>0.6711911708740327</v>
       </c>
       <c r="W8">
-        <v>0.1721192819918935</v>
+        <v>0.1246749068289675</v>
       </c>
       <c r="X8">
-        <v>0.195958014406159</v>
+        <v>0.2152764729098584</v>
       </c>
       <c r="Y8">
-        <v>-0.02383873241426551</v>
+        <v>-0.09060156608089096</v>
       </c>
       <c r="Z8">
-        <v>0.08826939740048434</v>
+        <v>0.05930235489536444</v>
       </c>
       <c r="AA8">
-        <v>0.0002562932384564375</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04562459789904978</v>
+        <v>0.06166920787546004</v>
       </c>
       <c r="AC8">
-        <v>-0.04536830466059334</v>
+        <v>-0.06166920787546004</v>
       </c>
       <c r="AD8">
-        <v>31266.8</v>
+        <v>30697.5</v>
       </c>
       <c r="AE8">
-        <v>195.4235396140618</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>31462.22353961406</v>
+        <v>30697.5</v>
       </c>
       <c r="AG8">
-        <v>24035.52353961406</v>
+        <v>28052</v>
       </c>
       <c r="AH8">
-        <v>0.8641942954209665</v>
+        <v>0.8862120730967984</v>
       </c>
       <c r="AI8">
-        <v>0.7847090985422975</v>
+        <v>0.7815085616525542</v>
       </c>
       <c r="AJ8">
-        <v>0.8293910570526497</v>
+        <v>0.8768031006298155</v>
       </c>
       <c r="AK8">
-        <v>0.7357642854958381</v>
+        <v>0.765730476629825</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
         <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>669.5246252676659</v>
-      </c>
-      <c r="AP8">
-        <v>514.6793049167893</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jiangsu Zhangjiagang Rural Commercial Bank Co., Ltd (SZSE:002839)</t>
+          <t>Xiamen Bank Co., Ltd. (SHSE:601187)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1472,34 +1457,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.003733553785354651</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.003733553785354651</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>187.4</v>
+        <v>345.2</v>
       </c>
       <c r="L9">
-        <v>0.4594263299828389</v>
+        <v>0.5258187357197258</v>
       </c>
       <c r="M9">
-        <v>92.5</v>
+        <v>109.3</v>
       </c>
       <c r="N9">
-        <v>0.05642652351613494</v>
+        <v>0.04985176738882554</v>
       </c>
       <c r="O9">
-        <v>0.4935965848452508</v>
+        <v>0.3166280417149478</v>
       </c>
       <c r="P9">
-        <v>92.5</v>
+        <v>109.3</v>
       </c>
       <c r="Q9">
-        <v>0.05642652351613494</v>
+        <v>0.04985176738882554</v>
       </c>
       <c r="R9">
-        <v>0.4935965848452508</v>
+        <v>0.3166280417149478</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1508,67 +1493,61 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>305.8</v>
+        <v>3227.2</v>
       </c>
       <c r="V9">
-        <v>0.1865430366619899</v>
+        <v>1.471927023945268</v>
       </c>
       <c r="W9">
-        <v>0.1162170542635659</v>
+        <v>0.100847210049664</v>
       </c>
       <c r="X9">
-        <v>0.09387026923657113</v>
+        <v>0.2111070288947496</v>
       </c>
       <c r="Y9">
-        <v>0.02234678502699476</v>
+        <v>-0.1102598188450856</v>
       </c>
       <c r="Z9">
-        <v>0.1098636075562842</v>
+        <v>0.03817393124622041</v>
       </c>
       <c r="AA9">
-        <v>0.0004101816878644826</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04580684394898285</v>
+        <v>0.06167865514159834</v>
       </c>
       <c r="AC9">
-        <v>-0.04539666226111837</v>
+        <v>-0.06167865514159834</v>
       </c>
       <c r="AD9">
-        <v>3294</v>
+        <v>16603.3</v>
       </c>
       <c r="AE9">
-        <v>15.58541705476919</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>3309.585417054769</v>
+        <v>16603.3</v>
       </c>
       <c r="AG9">
-        <v>3003.785417054769</v>
+        <v>13376.1</v>
       </c>
       <c r="AH9">
-        <v>0.668753696670634</v>
+        <v>0.8833515998254929</v>
       </c>
       <c r="AI9">
-        <v>0.6009576882604269</v>
+        <v>0.8291617143256659</v>
       </c>
       <c r="AJ9">
-        <v>0.6469373589426982</v>
+        <v>0.8591716660457588</v>
       </c>
       <c r="AK9">
-        <v>0.5774971812712989</v>
+        <v>0.7963386318985533</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>709.9137931034484</v>
-      </c>
-      <c r="AP9">
-        <v>647.367546779045</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bank of Guiyang Co.,Ltd. (SHSE:601997)</t>
+          <t>Bank of Jiangsu Co., Ltd. (SHSE:600919)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,10 +1567,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.106</v>
+        <v>0.152</v>
       </c>
       <c r="E10">
-        <v>0.116</v>
+        <v>0.164</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1600,34 +1579,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.004074598423755094</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.003688038874470846</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>932.3</v>
+        <v>3454.9</v>
       </c>
       <c r="L10">
-        <v>0.5477029726236634</v>
+        <v>0.5065612949576999</v>
       </c>
       <c r="M10">
-        <v>171.8414</v>
+        <v>827.1032</v>
       </c>
       <c r="N10">
-        <v>0.04586351019536671</v>
+        <v>0.05298275552822405</v>
       </c>
       <c r="O10">
-        <v>0.184319854124209</v>
+        <v>0.2394000405221569</v>
       </c>
       <c r="P10">
-        <v>171.8414</v>
+        <v>827.1032</v>
       </c>
       <c r="Q10">
-        <v>0.04586351019536671</v>
+        <v>0.05298275552822405</v>
       </c>
       <c r="R10">
-        <v>0.184319854124209</v>
+        <v>0.2394000405221569</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1636,67 +1615,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2404.9</v>
+        <v>9248</v>
       </c>
       <c r="V10">
-        <v>0.6418543824063201</v>
+        <v>0.5924103825556666</v>
       </c>
       <c r="W10">
-        <v>0.1732513194083104</v>
+        <v>0.1315866649908401</v>
       </c>
       <c r="X10">
-        <v>0.1722212714128524</v>
+        <v>0.2042252150313255</v>
       </c>
       <c r="Y10">
-        <v>0.001030047995458</v>
+        <v>-0.07263855004048539</v>
       </c>
       <c r="Z10">
-        <v>0.06672724178686644</v>
+        <v>0.0559358258946878</v>
       </c>
       <c r="AA10">
-        <v>0.0002460926616961789</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04564473308583156</v>
+        <v>0.06169533213958692</v>
       </c>
       <c r="AC10">
-        <v>-0.04539864042413538</v>
+        <v>-0.06169533213958692</v>
       </c>
       <c r="AD10">
-        <v>20005.9</v>
+        <v>112664.2</v>
       </c>
       <c r="AE10">
-        <v>51.8210928154204</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>20057.72109281542</v>
+        <v>112664.2</v>
       </c>
       <c r="AG10">
-        <v>17652.82109281542</v>
+        <v>103416.2</v>
       </c>
       <c r="AH10">
-        <v>0.8426013283194829</v>
+        <v>0.8783020853634769</v>
       </c>
       <c r="AI10">
-        <v>0.7108981200503495</v>
+        <v>0.7901978717494802</v>
       </c>
       <c r="AJ10">
-        <v>0.8249127877662317</v>
+        <v>0.8688465642249237</v>
       </c>
       <c r="AK10">
-        <v>0.6839601648283362</v>
+        <v>0.7756455450118953</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>1156.410404624278</v>
-      </c>
-      <c r="AP10">
-        <v>1020.394282821701</v>
       </c>
     </row>
     <row r="11">
@@ -1707,7 +1680,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bank of Jiangsu Co., Ltd. (SHSE:600919)</t>
+          <t>Qingdao Rural Commercial Bank Co., Ltd. (SZSE:002958)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1715,12 +1688,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.1</v>
-      </c>
-      <c r="E11">
-        <v>0.124</v>
-      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1728,34 +1695,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.004067729969958173</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.003291944516003044</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>2903.8</v>
+        <v>440.2</v>
       </c>
       <c r="L11">
-        <v>0.5015891660333034</v>
+        <v>0.4860329027271723</v>
       </c>
       <c r="M11">
-        <v>723.7104</v>
+        <v>112.1</v>
       </c>
       <c r="N11">
-        <v>0.05339223584613342</v>
+        <v>0.04815498947549293</v>
       </c>
       <c r="O11">
-        <v>0.2492287347613472</v>
+        <v>0.2546569741026806</v>
       </c>
       <c r="P11">
-        <v>723.7104</v>
+        <v>112.1</v>
       </c>
       <c r="Q11">
-        <v>0.05339223584613342</v>
+        <v>0.04815498947549293</v>
       </c>
       <c r="R11">
-        <v>0.2492287347613472</v>
+        <v>0.2546569741026806</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1764,67 +1731,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9814</v>
+        <v>1956.3</v>
       </c>
       <c r="V11">
-        <v>0.7240346450651439</v>
+        <v>0.8403711499634864</v>
       </c>
       <c r="W11">
-        <v>0.1224839292041371</v>
+        <v>0.08360397318291454</v>
       </c>
       <c r="X11">
-        <v>0.2242657911698182</v>
+        <v>0.1891440586744876</v>
       </c>
       <c r="Y11">
-        <v>-0.1017818619656811</v>
+        <v>-0.105540085491573</v>
       </c>
       <c r="Z11">
-        <v>0.05837761095277833</v>
+        <v>0.04355101628655098</v>
       </c>
       <c r="AA11">
-        <v>0.0001921758562333579</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04560679249785111</v>
+        <v>0.06173745716984197</v>
       </c>
       <c r="AC11">
-        <v>-0.04541461664161776</v>
+        <v>-0.06173745716984197</v>
       </c>
       <c r="AD11">
-        <v>102389.1</v>
+        <v>14986</v>
       </c>
       <c r="AE11">
-        <v>194.2554882895907</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>102583.3554882896</v>
+        <v>14986</v>
       </c>
       <c r="AG11">
-        <v>92769.3554882896</v>
+        <v>13029.7</v>
       </c>
       <c r="AH11">
-        <v>0.8832888012966034</v>
+        <v>0.8655473348003626</v>
       </c>
       <c r="AI11">
-        <v>0.7731988928101573</v>
+        <v>0.7416792457499196</v>
       </c>
       <c r="AJ11">
-        <v>0.8725160295462023</v>
+        <v>0.8484203260926186</v>
       </c>
       <c r="AK11">
-        <v>0.7550821186577096</v>
+        <v>0.713987462464108</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>1640.850961538462</v>
-      </c>
-      <c r="AP11">
-        <v>1486.68838923541</v>
       </c>
     </row>
     <row r="12">
@@ -1835,7 +1796,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jiangsu Changshu Rural Commercial Bank Co., Ltd. (SHSE:601128)</t>
+          <t>Bank of Hangzhou Co., Ltd. (SHSE:600926)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1844,10 +1805,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.143</v>
+        <v>0.187</v>
       </c>
       <c r="E12">
-        <v>0.154</v>
+        <v>0.216</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1856,34 +1817,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.002847836562677254</v>
+        <v>0.0001923308315862105</v>
       </c>
       <c r="J12">
-        <v>0.0024690320513229</v>
+        <v>0.0001726662164051478</v>
       </c>
       <c r="K12">
-        <v>321</v>
+        <v>1616.5</v>
       </c>
       <c r="L12">
-        <v>0.3623433796139519</v>
+        <v>0.5225472765475998</v>
       </c>
       <c r="M12">
-        <v>144.1</v>
+        <v>290.5847</v>
       </c>
       <c r="N12">
-        <v>0.05052771836319647</v>
+        <v>0.02583824902412349</v>
       </c>
       <c r="O12">
-        <v>0.4489096573208722</v>
+        <v>0.1797616455304671</v>
       </c>
       <c r="P12">
-        <v>144.1</v>
+        <v>290.5847</v>
       </c>
       <c r="Q12">
-        <v>0.05052771836319647</v>
+        <v>0.02583824902412349</v>
       </c>
       <c r="R12">
-        <v>0.4489096573208722</v>
+        <v>0.1797616455304671</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1892,55 +1853,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>793.4</v>
+        <v>2413.3</v>
       </c>
       <c r="V12">
-        <v>0.2782004979136716</v>
+        <v>0.214586130549603</v>
       </c>
       <c r="W12">
-        <v>0.1244861552780579</v>
+        <v>0.1337918590985085</v>
       </c>
       <c r="X12">
-        <v>0.08911269673791289</v>
+        <v>0.1742889536050742</v>
       </c>
       <c r="Y12">
-        <v>0.03537345854014498</v>
+        <v>-0.04049709450656569</v>
       </c>
       <c r="Z12">
-        <v>0.1652278931106947</v>
+        <v>0.04629470616348308</v>
       </c>
       <c r="AA12">
-        <v>0.0004079529638628594</v>
+        <v>7.993531752836701e-06</v>
       </c>
       <c r="AB12">
-        <v>0.04582904903589829</v>
+        <v>0.06178857698570092</v>
       </c>
       <c r="AC12">
-        <v>-0.04542109607203543</v>
+        <v>-0.06178058345394809</v>
       </c>
       <c r="AD12">
-        <v>5129.4</v>
+        <v>63762.9</v>
       </c>
       <c r="AE12">
-        <v>50.8855079456211</v>
+        <v>0.6951228624402891</v>
       </c>
       <c r="AF12">
-        <v>5180.28550794562</v>
+        <v>63763.59512286244</v>
       </c>
       <c r="AG12">
-        <v>4386.885507945621</v>
+        <v>61350.29512286244</v>
       </c>
       <c r="AH12">
-        <v>0.6449409694062923</v>
+        <v>0.8500691144604439</v>
       </c>
       <c r="AI12">
-        <v>0.6191192370512563</v>
+        <v>0.8235456591210401</v>
       </c>
       <c r="AJ12">
-        <v>0.6060250719033429</v>
+        <v>0.845085021123005</v>
       </c>
       <c r="AK12">
-        <v>0.5792196654293102</v>
+        <v>0.8178687671867708</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1949,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>403.8897637795275</v>
+        <v>86870.43596730246</v>
       </c>
       <c r="AP12">
-        <v>345.4240557437497</v>
+        <v>83583.50834177443</v>
       </c>
     </row>
     <row r="13">
@@ -1963,7 +1924,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qingdao Rural Commercial Bank Co., Ltd. (SZSE:002958)</t>
+          <t>Bank of Suzhou Co., Ltd. (SZSE:002966)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1978,34 +1939,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.003513378309456624</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.003402826881453768</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>499.5</v>
+        <v>526.4</v>
       </c>
       <c r="L13">
-        <v>0.5162257131045886</v>
+        <v>0.4355812991311543</v>
       </c>
       <c r="M13">
-        <v>128.5</v>
+        <v>399.9</v>
       </c>
       <c r="N13">
-        <v>0.03806617886660545</v>
+        <v>0.09668762088974854</v>
       </c>
       <c r="O13">
-        <v>0.2572572572572572</v>
+        <v>0.7596884498480243</v>
       </c>
       <c r="P13">
-        <v>128.5</v>
+        <v>399.9</v>
       </c>
       <c r="Q13">
-        <v>0.03806617886660545</v>
+        <v>0.09668762088974854</v>
       </c>
       <c r="R13">
-        <v>0.2572572572572572</v>
+        <v>0.7596884498480243</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2014,67 +1975,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1937.8</v>
+        <v>1483.4</v>
       </c>
       <c r="V13">
-        <v>0.57404390200551</v>
+        <v>0.3586557059961316</v>
       </c>
       <c r="W13">
-        <v>0.1291465211883031</v>
+        <v>0.1062747314867157</v>
       </c>
       <c r="X13">
-        <v>0.1682618438268719</v>
+        <v>0.1582488286258202</v>
       </c>
       <c r="Y13">
-        <v>-0.03911532263856873</v>
+        <v>-0.05197409713910453</v>
       </c>
       <c r="Z13">
-        <v>0.06100420278228418</v>
+        <v>0.05547980737006891</v>
       </c>
       <c r="AA13">
-        <v>0.0002075867411092133</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04564873183193344</v>
+        <v>0.06185886631770332</v>
       </c>
       <c r="AC13">
-        <v>-0.04544114509082423</v>
+        <v>-0.06185886631770332</v>
       </c>
       <c r="AD13">
-        <v>17468.8</v>
+        <v>20021</v>
       </c>
       <c r="AE13">
-        <v>33.50227573884885</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>17502.30227573885</v>
+        <v>20021</v>
       </c>
       <c r="AG13">
-        <v>15564.50227573885</v>
+        <v>18537.6</v>
       </c>
       <c r="AH13">
-        <v>0.8383130744303677</v>
+        <v>0.8287866870886286</v>
       </c>
       <c r="AI13">
-        <v>0.7641190881024116</v>
+        <v>0.7811792798838825</v>
       </c>
       <c r="AJ13">
-        <v>0.8217706468571326</v>
+        <v>0.8175852092301178</v>
       </c>
       <c r="AK13">
-        <v>0.7423190565551538</v>
+        <v>0.7677360037770543</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1729.584158415842</v>
-      </c>
-      <c r="AP13">
-        <v>1541.039829281074</v>
       </c>
     </row>
     <row r="14">
@@ -2085,7 +2040,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank of Nanjing Co., Ltd. (SHSE:601009)</t>
+          <t>Bank of Guizhou Co., Ltd. (SEHK:6199)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2093,12 +2048,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.102</v>
-      </c>
-      <c r="E14">
-        <v>0.134</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2106,103 +2055,97 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.003463002304410271</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.002967722503215428</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>2382.9</v>
+        <v>562</v>
       </c>
       <c r="L14">
-        <v>0.5221878903425153</v>
+        <v>0.4871283695934818</v>
       </c>
       <c r="M14">
-        <v>36.83</v>
+        <v>153.8</v>
       </c>
       <c r="N14">
-        <v>0.002609391826786828</v>
+        <v>0.03137622914031581</v>
       </c>
       <c r="O14">
-        <v>0.01545595702715179</v>
+        <v>0.2736654804270463</v>
       </c>
       <c r="P14">
-        <v>31.9</v>
+        <v>153.8</v>
       </c>
       <c r="Q14">
-        <v>0.002260103157059457</v>
+        <v>0.03137622914031581</v>
       </c>
       <c r="R14">
-        <v>0.01338704939359604</v>
+        <v>0.2736654804270463</v>
       </c>
       <c r="S14">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>0.1338582677165354</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3269.6</v>
+        <v>3098.1</v>
       </c>
       <c r="V14">
-        <v>0.2316499461542821</v>
+        <v>0.6320331306866864</v>
       </c>
       <c r="W14">
-        <v>0.1724602123455718</v>
+        <v>0.09733624302885448</v>
       </c>
       <c r="X14">
-        <v>0.159880939650364</v>
+        <v>0.1458705276769378</v>
       </c>
       <c r="Y14">
-        <v>0.01257927269520781</v>
+        <v>-0.04853428464808336</v>
       </c>
       <c r="Z14">
-        <v>0.06799358289252598</v>
+        <v>0.07102577046677419</v>
       </c>
       <c r="AA14">
-        <v>0.0002017860860243929</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04565795865909318</v>
+        <v>0.06192842895190486</v>
       </c>
       <c r="AC14">
-        <v>-0.04545617257306879</v>
+        <v>-0.06192842895190486</v>
       </c>
       <c r="AD14">
-        <v>67975.10000000001</v>
+        <v>20591.8</v>
       </c>
       <c r="AE14">
-        <v>170.9864079214231</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>68146.08640792142</v>
+        <v>20591.8</v>
       </c>
       <c r="AG14">
-        <v>64876.48640792142</v>
+        <v>17493.7</v>
       </c>
       <c r="AH14">
-        <v>0.8284182282851075</v>
+        <v>0.8077242915869081</v>
       </c>
       <c r="AI14">
-        <v>0.7897187807601336</v>
+        <v>0.7736246726752901</v>
       </c>
       <c r="AJ14">
-        <v>0.8213160955415666</v>
+        <v>0.7811256725681499</v>
       </c>
       <c r="AK14">
-        <v>0.7814374145320538</v>
+        <v>0.7438050613966461</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
         <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>1359.502</v>
-      </c>
-      <c r="AP14">
-        <v>1297.529728158428</v>
       </c>
     </row>
     <row r="15">
@@ -2213,7 +2156,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jiangsu Suzhou Rural Commercial Bank Co., Ltd (SHSE:603323)</t>
+          <t>Bank of Xi'an Co.,Ltd. (SHSE:600928)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2222,10 +2165,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.103</v>
+        <v>0.0226</v>
       </c>
       <c r="E15">
-        <v>0.119</v>
+        <v>0.0403</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2234,34 +2177,34 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.002869538980418028</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.002354458766644363</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>171.6</v>
+        <v>358.9</v>
       </c>
       <c r="L15">
-        <v>0.4224519940915805</v>
+        <v>0.5490286063943705</v>
       </c>
       <c r="M15">
-        <v>58.2</v>
+        <v>410.6</v>
       </c>
       <c r="N15">
-        <v>0.04210374014323953</v>
+        <v>0.1810246010052024</v>
       </c>
       <c r="O15">
-        <v>0.3391608391608392</v>
+        <v>1.144051267762608</v>
       </c>
       <c r="P15">
-        <v>58.2</v>
+        <v>410.6</v>
       </c>
       <c r="Q15">
-        <v>0.04210374014323953</v>
+        <v>0.1810246010052024</v>
       </c>
       <c r="R15">
-        <v>0.3391608391608392</v>
+        <v>1.144051267762608</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2270,67 +2213,61 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>697</v>
+        <v>2052.7</v>
       </c>
       <c r="V15">
-        <v>0.5042320769731606</v>
+        <v>0.9049907415571818</v>
       </c>
       <c r="W15">
-        <v>0.09710825646539528</v>
+        <v>0.0865215399821605</v>
       </c>
       <c r="X15">
-        <v>0.09086813313697126</v>
+        <v>0.1444170496144894</v>
       </c>
       <c r="Y15">
-        <v>0.006240123328424024</v>
+        <v>-0.05789550963232887</v>
       </c>
       <c r="Z15">
-        <v>0.1301872184431581</v>
+        <v>0.04732772476506277</v>
       </c>
       <c r="AA15">
-        <v>0.0003065204377685382</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04582049379797382</v>
+        <v>0.06193773637570153</v>
       </c>
       <c r="AC15">
-        <v>-0.04551397336020527</v>
+        <v>-0.06193773637570153</v>
       </c>
       <c r="AD15">
-        <v>2600.1</v>
+        <v>9358</v>
       </c>
       <c r="AE15">
-        <v>14.02196633077098</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2614.121966330771</v>
+        <v>9358</v>
       </c>
       <c r="AG15">
-        <v>1917.121966330771</v>
+        <v>7305.3</v>
       </c>
       <c r="AH15">
-        <v>0.6541156034959118</v>
+        <v>0.8049061602243209</v>
       </c>
       <c r="AI15">
-        <v>0.5613170505797107</v>
+        <v>0.6978738636617871</v>
       </c>
       <c r="AJ15">
-        <v>0.5810478277389808</v>
+        <v>0.7630751553768215</v>
       </c>
       <c r="AK15">
-        <v>0.4841067983840583</v>
+        <v>0.6432647095081274</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
         <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>654.9370277078085</v>
-      </c>
-      <c r="AP15">
-        <v>482.9022585216048</v>
       </c>
     </row>
     <row r="16">
@@ -2341,7 +2278,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bank of Tianjin Co., Ltd. (SEHK:1578)</t>
+          <t>Bank of Nanjing Co., Ltd. (SHSE:601009)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2350,10 +2287,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.0302</v>
+        <v>0.137</v>
       </c>
       <c r="E16">
-        <v>-0.0359</v>
+        <v>0.146</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2368,28 +2305,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>673.8</v>
+        <v>2598.2</v>
       </c>
       <c r="L16">
-        <v>0.4727425805093664</v>
+        <v>0.5155261017083672</v>
       </c>
       <c r="M16">
-        <v>29.7</v>
+        <v>37.9</v>
       </c>
       <c r="N16">
-        <v>0.01774405544270522</v>
+        <v>0.002426221112604827</v>
       </c>
       <c r="O16">
-        <v>0.04407836153161176</v>
+        <v>0.01458702178431222</v>
       </c>
       <c r="P16">
-        <v>29.7</v>
+        <v>37.9</v>
       </c>
       <c r="Q16">
-        <v>0.01774405544270522</v>
+        <v>0.002426221112604827</v>
       </c>
       <c r="R16">
-        <v>0.04407836153161176</v>
+        <v>0.01458702178431222</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2398,55 +2335,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>2598.8</v>
+        <v>5421.1</v>
       </c>
       <c r="V16">
-        <v>1.552634723383917</v>
+        <v>0.3470392420459638</v>
       </c>
       <c r="W16">
-        <v>0.09175211405694676</v>
+        <v>0.1581799142801481</v>
       </c>
       <c r="X16">
-        <v>0.4829022733729139</v>
+        <v>0.1392272877373059</v>
       </c>
       <c r="Y16">
-        <v>-0.3911501593159671</v>
+        <v>0.01895262654284222</v>
       </c>
       <c r="Z16">
-        <v>0.03944408006708233</v>
+        <v>0.06097181812132906</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.04554559742353383</v>
+        <v>0.06197331849613262</v>
       </c>
       <c r="AC16">
-        <v>-0.04554559742353383</v>
+        <v>-0.06197331849613262</v>
       </c>
       <c r="AD16">
-        <v>31090.8</v>
+        <v>60257.9</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>31090.8</v>
+        <v>60257.9</v>
       </c>
       <c r="AG16">
-        <v>28492</v>
+        <v>54836.8</v>
       </c>
       <c r="AH16">
-        <v>0.9489143771021163</v>
+        <v>0.7941324926955979</v>
       </c>
       <c r="AI16">
-        <v>0.7796010070109627</v>
+        <v>0.7601343211471289</v>
       </c>
       <c r="AJ16">
-        <v>0.9445133230346949</v>
+        <v>0.778292822086412</v>
       </c>
       <c r="AK16">
-        <v>0.7642375863696838</v>
+        <v>0.7425269053074002</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2463,7 +2400,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Huishang Bank Corporation Limited (SEHK:3698)</t>
+          <t>Bank of Ningbo Co., Ltd. (SZSE:002142)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2472,10 +2409,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.077</v>
+        <v>0.196</v>
       </c>
       <c r="E17">
-        <v>0.101</v>
+        <v>0.205</v>
+      </c>
+      <c r="F17">
+        <v>0.153</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2484,94 +2424,103 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.0002342110310313056</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.0002149558711982977</v>
       </c>
       <c r="K17">
-        <v>1628.4</v>
+        <v>3152.8</v>
       </c>
       <c r="L17">
-        <v>0.501880046847069</v>
+        <v>0.4819910719745613</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>462.2520000000001</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.0148784782013937</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.1466163410301954</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>462.2520000000001</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.0148784782013937</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.1466163410301954</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>8665.799999999999</v>
+        <v>6733.9</v>
       </c>
       <c r="V17">
-        <v>1.863973672323675</v>
+        <v>0.2167436471023706</v>
       </c>
       <c r="W17">
-        <v>0.1354775909548491</v>
+        <v>0.1727495383738706</v>
       </c>
       <c r="X17">
-        <v>0.3094165829471118</v>
+        <v>0.1314707521894604</v>
       </c>
       <c r="Y17">
-        <v>-0.1739389919922626</v>
+        <v>0.04127878618441014</v>
       </c>
       <c r="Z17">
-        <v>0.06027841098038342</v>
+        <v>0.06198492191635124</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.332402289168774e-05</v>
       </c>
       <c r="AB17">
-        <v>0.04557444473635781</v>
+        <v>0.06203448407976375</v>
       </c>
       <c r="AC17">
-        <v>-0.04557444473635781</v>
+        <v>-0.06202116005687206</v>
       </c>
       <c r="AD17">
-        <v>52032.4</v>
+        <v>107388.9</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.789894019090118</v>
       </c>
       <c r="AF17">
-        <v>52032.4</v>
+        <v>107390.6898940191</v>
       </c>
       <c r="AG17">
-        <v>43366.60000000001</v>
+        <v>100656.7898940191</v>
       </c>
       <c r="AH17">
-        <v>0.9179785291497226</v>
+        <v>0.7756125828572246</v>
       </c>
       <c r="AI17">
-        <v>0.7500068467580241</v>
+        <v>0.8216523237224976</v>
       </c>
       <c r="AJ17">
-        <v>0.9031754197064711</v>
+        <v>0.7641417223298846</v>
       </c>
       <c r="AK17">
-        <v>0.7143226580091286</v>
+        <v>0.8119644590876315</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>56819.52380952381</v>
+      </c>
+      <c r="AP17">
+        <v>53257.5607904863</v>
       </c>
     </row>
     <row r="18">
@@ -2582,7 +2531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jinshang Bank Co., Ltd. (SEHK:2558)</t>
+          <t>Bank of Chengdu Co., Ltd. (SHSE:601838)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2603,28 +2552,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>258.4</v>
+        <v>1328.6</v>
       </c>
       <c r="L18">
-        <v>0.4650827933765298</v>
+        <v>0.6022392457277549</v>
       </c>
       <c r="M18">
-        <v>114</v>
+        <v>413</v>
       </c>
       <c r="N18">
-        <v>0.1036175240865297</v>
+        <v>0.05053162202836133</v>
       </c>
       <c r="O18">
-        <v>0.4411764705882353</v>
+        <v>0.3108535300316123</v>
       </c>
       <c r="P18">
-        <v>114</v>
+        <v>413</v>
       </c>
       <c r="Q18">
-        <v>0.1036175240865297</v>
+        <v>0.05053162202836133</v>
       </c>
       <c r="R18">
-        <v>0.4411764705882353</v>
+        <v>0.3108535300316123</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2633,55 +2582,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>1014.1</v>
+        <v>8814</v>
       </c>
       <c r="V18">
-        <v>0.9217415015451735</v>
+        <v>1.078415778590743</v>
       </c>
       <c r="W18">
-        <v>0.09007878407585582</v>
+        <v>0.1728732401696724</v>
       </c>
       <c r="X18">
-        <v>0.2838777755283558</v>
+        <v>0.1301357740433892</v>
       </c>
       <c r="Y18">
-        <v>-0.1937989914525</v>
+        <v>0.04273746612628321</v>
       </c>
       <c r="Z18">
-        <v>0.05003602305475505</v>
+        <v>0.1054979843433933</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04558193026117092</v>
+        <v>0.06204613877720083</v>
       </c>
       <c r="AC18">
-        <v>-0.04558193026117092</v>
+        <v>-0.06204613877720083</v>
       </c>
       <c r="AD18">
-        <v>11117.6</v>
+        <v>27687</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>11117.6</v>
+        <v>27687</v>
       </c>
       <c r="AG18">
-        <v>10103.5</v>
+        <v>18873</v>
       </c>
       <c r="AH18">
-        <v>0.9099510550180883</v>
+        <v>0.772083736520534</v>
       </c>
       <c r="AI18">
-        <v>0.7707709373266778</v>
+        <v>0.7728250948341554</v>
       </c>
       <c r="AJ18">
-        <v>0.901800298115801</v>
+        <v>0.6978085565016768</v>
       </c>
       <c r="AK18">
-        <v>0.7534358943765427</v>
+        <v>0.6986972311998134</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2698,7 +2647,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bank of Hangzhou Co., Ltd. (SHSE:600926)</t>
+          <t>Bank of Gansu Co., Ltd. (SEHK:2139)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2707,10 +2656,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.132</v>
+        <v>-0.144</v>
       </c>
       <c r="E19">
-        <v>0.17</v>
+        <v>-0.291</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2719,34 +2668,34 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.001269660234831</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.001127553646193213</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1333.8</v>
+        <v>87</v>
       </c>
       <c r="L19">
-        <v>0.4949716109399933</v>
+        <v>0.2080841903850753</v>
       </c>
       <c r="M19">
-        <v>320.2308</v>
+        <v>0.008</v>
       </c>
       <c r="N19">
-        <v>0.0267581469968916</v>
+        <v>3.942246094712463e-06</v>
       </c>
       <c r="O19">
-        <v>0.2400890688259109</v>
+        <v>9.195402298850575e-05</v>
       </c>
       <c r="P19">
-        <v>320.2308</v>
+        <v>0.008</v>
       </c>
       <c r="Q19">
-        <v>0.0267581469968916</v>
+        <v>3.942246094712463e-06</v>
       </c>
       <c r="R19">
-        <v>0.2400890688259109</v>
+        <v>9.195402298850575e-05</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2755,67 +2704,61 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>5056.9</v>
+        <v>907.1</v>
       </c>
       <c r="V19">
-        <v>0.4225492162171195</v>
+        <v>0.4470014290642094</v>
       </c>
       <c r="W19">
-        <v>0.1303404604620255</v>
+        <v>0.0176642572890441</v>
       </c>
       <c r="X19">
-        <v>0.1613755710144649</v>
+        <v>0.1236030879855518</v>
       </c>
       <c r="Y19">
-        <v>-0.03103511055243935</v>
+        <v>-0.1059388306965077</v>
       </c>
       <c r="Z19">
-        <v>0.05660826053782669</v>
+        <v>0.04195137613758367</v>
       </c>
       <c r="AA19">
-        <v>6.382885057408187e-05</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.04565623131958461</v>
+        <v>0.06210889746164504</v>
       </c>
       <c r="AC19">
-        <v>-0.04559240246901053</v>
+        <v>-0.06210889746164504</v>
       </c>
       <c r="AD19">
-        <v>58247.4</v>
+        <v>6189.2</v>
       </c>
       <c r="AE19">
-        <v>294.8932328260045</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>58542.29323282601</v>
+        <v>6189.2</v>
       </c>
       <c r="AG19">
-        <v>53485.39323282601</v>
+        <v>5282.099999999999</v>
       </c>
       <c r="AH19">
-        <v>0.8302706265561545</v>
+        <v>0.753081462553994</v>
       </c>
       <c r="AI19">
-        <v>0.8111384966946275</v>
+        <v>0.5611394688885464</v>
       </c>
       <c r="AJ19">
-        <v>0.8171573306444601</v>
+        <v>0.7224471373471565</v>
       </c>
       <c r="AK19">
-        <v>0.7969086199234653</v>
+        <v>0.5218125777962184</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
         <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>933.4519230769231</v>
-      </c>
-      <c r="AP19">
-        <v>857.1377120645193</v>
       </c>
     </row>
     <row r="20">
@@ -2826,7 +2769,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chongqing Rural Commercial Bank Co., Ltd. (SEHK:3618)</t>
+          <t>Jiangsu Zijin Rural Commercial Bank Co.,Ltd (SHSE:601860)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2835,13 +2778,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.00333</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E20">
-        <v>0.0393</v>
-      </c>
-      <c r="F20">
-        <v>0.09470000000000001</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2856,28 +2796,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>1456.1</v>
+        <v>225.1</v>
       </c>
       <c r="L20">
-        <v>0.4806721024659162</v>
+        <v>0.4254394254394254</v>
       </c>
       <c r="M20">
-        <v>480.6</v>
+        <v>71.5</v>
       </c>
       <c r="N20">
-        <v>0.07686525389844062</v>
+        <v>0.05201134793045755</v>
       </c>
       <c r="O20">
-        <v>0.3300597486436371</v>
+        <v>0.3176366059529098</v>
       </c>
       <c r="P20">
-        <v>480.6</v>
+        <v>71.5</v>
       </c>
       <c r="Q20">
-        <v>0.07686525389844062</v>
+        <v>0.05201134793045755</v>
       </c>
       <c r="R20">
-        <v>0.3300597486436371</v>
+        <v>0.3176366059529098</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2886,55 +2826,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>6510.3</v>
+        <v>1554.4</v>
       </c>
       <c r="V20">
-        <v>1.041231507397041</v>
+        <v>1.130719429693751</v>
       </c>
       <c r="W20">
-        <v>0.1064307224512469</v>
+        <v>0.09178015167577265</v>
       </c>
       <c r="X20">
-        <v>0.2454339187535883</v>
+        <v>0.1148630134953368</v>
       </c>
       <c r="Y20">
-        <v>-0.1390031963023414</v>
+        <v>-0.02308286181956411</v>
       </c>
       <c r="Z20">
-        <v>0.06959732206653022</v>
+        <v>0.07638558043512785</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.04559643855536961</v>
+        <v>0.06221128345788374</v>
       </c>
       <c r="AC20">
-        <v>-0.04559643855536961</v>
+        <v>-0.06221128345788374</v>
       </c>
       <c r="AD20">
-        <v>52952.5</v>
+        <v>3571.7</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>52952.5</v>
+        <v>3571.7</v>
       </c>
       <c r="AG20">
-        <v>46442.2</v>
+        <v>2017.3</v>
       </c>
       <c r="AH20">
-        <v>0.8943923655096698</v>
+        <v>0.7220807051593078</v>
       </c>
       <c r="AI20">
-        <v>0.7635445250169789</v>
+        <v>0.5999529672618548</v>
       </c>
       <c r="AJ20">
-        <v>0.8813448031775492</v>
+        <v>0.5947228773584905</v>
       </c>
       <c r="AK20">
-        <v>0.7390476857318358</v>
+        <v>0.4585919207074496</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2951,7 +2891,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Harbin Bank Co., Ltd. (SEHK:6138)</t>
+          <t>Jiangsu Zhangjiagang Rural Commercial Bank Co., Ltd (SZSE:002839)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2960,7 +2900,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.143</v>
+        <v>0.144</v>
+      </c>
+      <c r="E21">
+        <v>0.169</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2975,28 +2918,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-40.4</v>
+        <v>224.5</v>
       </c>
       <c r="L21">
-        <v>-0.04943105346873853</v>
+        <v>0.5199166280685502</v>
       </c>
       <c r="M21">
-        <v>79.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="N21">
-        <v>0.0716466151912372</v>
+        <v>0.05868156116397737</v>
       </c>
       <c r="O21">
-        <v>-1.975247524752475</v>
+        <v>0.3790645879732739</v>
       </c>
       <c r="P21">
-        <v>79.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Q21">
-        <v>0.0716466151912372</v>
+        <v>0.05868156116397737</v>
       </c>
       <c r="R21">
-        <v>-1.975247524752475</v>
+        <v>0.3790645879732739</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3005,55 +2948,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>4654.3</v>
+        <v>483.7</v>
       </c>
       <c r="V21">
-        <v>4.178757407074879</v>
+        <v>0.3335402013515377</v>
       </c>
       <c r="W21">
-        <v>-0.005652800514908561</v>
+        <v>0.1031804393786193</v>
       </c>
       <c r="X21">
-        <v>0.2109174151516875</v>
+        <v>0.1148235029009465</v>
       </c>
       <c r="Y21">
-        <v>-0.2165702156665961</v>
+        <v>-0.0116430635223272</v>
       </c>
       <c r="Z21">
-        <v>0.08177661266922145</v>
+        <v>0.08361735089078234</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.04561452039902781</v>
+        <v>0.06221180471326795</v>
       </c>
       <c r="AC21">
-        <v>-0.04561452039902781</v>
+        <v>-0.06221180471326795</v>
       </c>
       <c r="AD21">
-        <v>7796.7</v>
+        <v>3764.9</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>7796.7</v>
+        <v>3764.9</v>
       </c>
       <c r="AG21">
-        <v>3142.4</v>
+        <v>3281.2</v>
       </c>
       <c r="AH21">
-        <v>0.8750014028393468</v>
+        <v>0.7219228777971659</v>
       </c>
       <c r="AI21">
-        <v>0.456216829823463</v>
+        <v>0.6317794334810041</v>
       </c>
       <c r="AJ21">
-        <v>0.7383111695878952</v>
+        <v>0.6934945259331275</v>
       </c>
       <c r="AK21">
-        <v>0.2526938788639068</v>
+        <v>0.5992512099351658</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3070,7 +3013,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bank of Zhengzhou Co., Ltd. (SEHK:6196)</t>
+          <t>Jiangsu Suzhou Rural Commercial Bank Co., Ltd (SHSE:603323)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3079,10 +3022,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.00247</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="E22">
-        <v>-0.04650000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3097,28 +3040,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>497.6</v>
+        <v>193.2</v>
       </c>
       <c r="L22">
-        <v>0.4306733598753678</v>
+        <v>0.5214574898785425</v>
       </c>
       <c r="M22">
-        <v>0.736</v>
+        <v>82.8</v>
       </c>
       <c r="N22">
-        <v>0.0002049625442089727</v>
+        <v>0.06753119647663323</v>
       </c>
       <c r="O22">
-        <v>0.001479099678456591</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="P22">
-        <v>0.736</v>
+        <v>82.8</v>
       </c>
       <c r="Q22">
-        <v>0.0002049625442089727</v>
+        <v>0.06753119647663323</v>
       </c>
       <c r="R22">
-        <v>0.001479099678456591</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3127,55 +3070,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>2022.3</v>
+        <v>631.6</v>
       </c>
       <c r="V22">
-        <v>0.5631735776546269</v>
+        <v>0.5151292716744149</v>
       </c>
       <c r="W22">
-        <v>0.1023383995228596</v>
+        <v>0.09549228944246738</v>
       </c>
       <c r="X22">
-        <v>0.2071513589082354</v>
+        <v>0.1127247147659523</v>
       </c>
       <c r="Y22">
-        <v>-0.1048129593853759</v>
+        <v>-0.01723242532348492</v>
       </c>
       <c r="Z22">
-        <v>0.04320754505304648</v>
+        <v>0.09436365025596617</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.04561690327510329</v>
+        <v>0.06224037106473297</v>
       </c>
       <c r="AC22">
-        <v>-0.04561690327510329</v>
+        <v>-0.06224037106473297</v>
       </c>
       <c r="AD22">
-        <v>24561.1</v>
+        <v>3050.1</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>24561.1</v>
+        <v>3050.1</v>
       </c>
       <c r="AG22">
-        <v>22538.8</v>
+        <v>2418.5</v>
       </c>
       <c r="AH22">
-        <v>0.8724460073884626</v>
+        <v>0.7132734670969553</v>
       </c>
       <c r="AI22">
-        <v>0.7601090596238</v>
+        <v>0.5991631634777825</v>
       </c>
       <c r="AJ22">
-        <v>0.8625740058247894</v>
+        <v>0.6635844811501949</v>
       </c>
       <c r="AK22">
-        <v>0.7440929934665553</v>
+        <v>0.542386185243328</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3192,7 +3135,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bank of Ningbo Co., Ltd. (SZSE:002142)</t>
+          <t>Jiangsu Jiangyin Rural Commercial Bank Co.,LTD. (SZSE:002807)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3201,13 +3144,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.161</v>
+        <v>0.104</v>
       </c>
       <c r="E23">
-        <v>0.19</v>
-      </c>
-      <c r="F23">
-        <v>0.152</v>
+        <v>0.131</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3216,34 +3156,34 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0.001686419876181967</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0.001617660390971367</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>2806.5</v>
+        <v>202.6</v>
       </c>
       <c r="L23">
-        <v>0.4765179299103504</v>
+        <v>0.5337197049525816</v>
       </c>
       <c r="M23">
-        <v>515.0808000000001</v>
+        <v>67.5</v>
       </c>
       <c r="N23">
-        <v>0.01294416787082993</v>
+        <v>0.05399136138217885</v>
       </c>
       <c r="O23">
-        <v>0.183531373597007</v>
+        <v>0.3331688055281343</v>
       </c>
       <c r="P23">
-        <v>515.0808000000001</v>
+        <v>67.5</v>
       </c>
       <c r="Q23">
-        <v>0.01294416787082993</v>
+        <v>0.05399136138217885</v>
       </c>
       <c r="R23">
-        <v>0.183531373597007</v>
+        <v>0.3331688055281343</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3252,67 +3192,61 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>5747.6</v>
+        <v>585.5</v>
       </c>
       <c r="V23">
-        <v>0.1444392787585601</v>
+        <v>0.4683250679891217</v>
       </c>
       <c r="W23">
-        <v>0.1896668243562884</v>
+        <v>0.1048165968234259</v>
       </c>
       <c r="X23">
-        <v>0.1003012660635665</v>
+        <v>0.1094245982048211</v>
       </c>
       <c r="Y23">
-        <v>0.0893655582927219</v>
+        <v>-0.004608001381395138</v>
       </c>
       <c r="Z23">
-        <v>0.08429267692597542</v>
+        <v>0.08170469220835126</v>
       </c>
       <c r="AA23">
-        <v>0.0001363569247120965</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.04578116911555787</v>
+        <v>0.06228906732986537</v>
       </c>
       <c r="AC23">
-        <v>-0.04564481219084578</v>
+        <v>-0.06228906732986537</v>
       </c>
       <c r="AD23">
-        <v>90725.89999999999</v>
+        <v>2896.8</v>
       </c>
       <c r="AE23">
-        <v>501.8383074861934</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>91227.73830748619</v>
+        <v>2896.8</v>
       </c>
       <c r="AG23">
-        <v>85480.13830748618</v>
+        <v>2311.3</v>
       </c>
       <c r="AH23">
-        <v>0.6962873788504905</v>
+        <v>0.6985290571497469</v>
       </c>
       <c r="AI23">
-        <v>0.8155379580758177</v>
+        <v>0.5999378689033862</v>
       </c>
       <c r="AJ23">
-        <v>0.6823528223112226</v>
+        <v>0.6489681314053068</v>
       </c>
       <c r="AK23">
-        <v>0.8055467255058326</v>
+        <v>0.5447325005892057</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>822.5376246600181</v>
-      </c>
-      <c r="AP23">
-        <v>774.9785884631567</v>
       </c>
     </row>
     <row r="24">
@@ -3323,7 +3257,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jiangsu Jiangyin Rural Commercial Bank Co.,LTD. (SZSE:002807)</t>
+          <t>Shengjing Bank Co., Ltd. (SEHK:2066)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3332,10 +3266,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.0579</v>
+        <v>-0.12</v>
       </c>
       <c r="E24">
-        <v>0.0825</v>
+        <v>-0.458</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3344,103 +3278,94 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0.001171722847136224</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.001171722847136224</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>179.6</v>
+        <v>47.1</v>
       </c>
       <c r="L24">
-        <v>0.4957217775324316</v>
+        <v>0.05120121752364388</v>
       </c>
       <c r="M24">
-        <v>63.3</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.0480893413355618</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>0.3524498886414254</v>
+        <v>-0</v>
       </c>
       <c r="P24">
-        <v>63.3</v>
+        <v>-0</v>
       </c>
       <c r="Q24">
-        <v>0.0480893413355618</v>
+        <v>-0</v>
       </c>
       <c r="R24">
-        <v>0.3524498886414254</v>
+        <v>-0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
       <c r="U24">
-        <v>406.2</v>
+        <v>5025.5</v>
       </c>
       <c r="V24">
-        <v>0.3085922662007141</v>
+        <v>0.7372119291760184</v>
       </c>
       <c r="W24">
-        <v>0.1061026761977905</v>
+        <v>0.00377909542416535</v>
       </c>
       <c r="X24">
-        <v>0.100073591514741</v>
+        <v>0.1082577699398754</v>
       </c>
       <c r="Y24">
-        <v>0.006029084683049496</v>
+        <v>-0.1044786745157101</v>
       </c>
       <c r="Z24">
-        <v>0.09143269758457391</v>
+        <v>0.03763234114971118</v>
       </c>
       <c r="AA24">
-        <v>0.0001071337807351423</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.04578200497935642</v>
+        <v>0.06230750558489676</v>
       </c>
       <c r="AC24">
-        <v>-0.04567487119862127</v>
+        <v>-0.06230750558489676</v>
       </c>
       <c r="AD24">
-        <v>3001.3</v>
+        <v>15384.1</v>
       </c>
       <c r="AE24">
-        <v>3.67742406241273</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>3004.977424062413</v>
+        <v>15384.1</v>
       </c>
       <c r="AG24">
-        <v>2598.777424062413</v>
+        <v>10358.6</v>
       </c>
       <c r="AH24">
-        <v>0.695390998811978</v>
+        <v>0.6929462636818161</v>
       </c>
       <c r="AI24">
-        <v>0.6127383176062209</v>
+        <v>0.5582606360588158</v>
       </c>
       <c r="AJ24">
-        <v>0.663786981092659</v>
+        <v>0.6031032575470875</v>
       </c>
       <c r="AK24">
-        <v>0.5777657776048351</v>
+        <v>0.4597345073829316</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
         <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>2587.327586206897</v>
-      </c>
-      <c r="AP24">
-        <v>2240.325365571046</v>
       </c>
     </row>
     <row r="25">
@@ -3451,7 +3376,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guangzhou Rural Commercial Bank Co., Ltd. (SEHK:1551)</t>
+          <t>Dongguan Rural Commercial Bank Co., Ltd. (SEHK:9889)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3459,6 +3384,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D25">
+        <v>0.08130000000000001</v>
+      </c>
+      <c r="E25">
+        <v>0.0776</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3472,28 +3403,28 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>793.8</v>
+        <v>893.8</v>
       </c>
       <c r="L25">
-        <v>0.353035356904603</v>
+        <v>0.5406811445163632</v>
       </c>
       <c r="M25">
-        <v>354.9903</v>
+        <v>306.4</v>
       </c>
       <c r="N25">
-        <v>0.0704891284922857</v>
+        <v>0.04816928422078637</v>
       </c>
       <c r="O25">
-        <v>0.4472037037037037</v>
+        <v>0.3428059968673081</v>
       </c>
       <c r="P25">
-        <v>354.9903</v>
+        <v>306.4</v>
       </c>
       <c r="Q25">
-        <v>0.0704891284922857</v>
+        <v>0.04816928422078637</v>
       </c>
       <c r="R25">
-        <v>0.4472037037037037</v>
+        <v>0.3428059968673081</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3502,55 +3433,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>7265.8</v>
+        <v>3798.8</v>
       </c>
       <c r="V25">
-        <v>1.442743392704672</v>
+        <v>0.5972110864814728</v>
       </c>
       <c r="W25">
-        <v>0.09498737570151611</v>
+        <v>0.1527158405522238</v>
       </c>
       <c r="X25">
-        <v>0.1353588494489031</v>
+        <v>0.1049320716607749</v>
       </c>
       <c r="Y25">
-        <v>-0.040371473747387</v>
+        <v>0.04778376889144886</v>
       </c>
       <c r="Z25">
-        <v>0.1115903045221742</v>
+        <v>0.09689520359656989</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.04569285696116689</v>
+        <v>0.06236401417785729</v>
       </c>
       <c r="AC25">
-        <v>-0.04569285696116689</v>
+        <v>-0.06236401417785729</v>
       </c>
       <c r="AD25">
-        <v>19059.3</v>
+        <v>13261.6</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>19059.3</v>
+        <v>13261.6</v>
       </c>
       <c r="AG25">
-        <v>11793.5</v>
+        <v>9462.799999999999</v>
       </c>
       <c r="AH25">
-        <v>0.7909933016260364</v>
+        <v>0.6758364122818193</v>
       </c>
       <c r="AI25">
-        <v>0.6150522297268952</v>
+        <v>0.6329061970553845</v>
       </c>
       <c r="AJ25">
-        <v>0.7007593763369302</v>
+        <v>0.5980143708487901</v>
       </c>
       <c r="AK25">
-        <v>0.4971482529097094</v>
+        <v>0.551615592228369</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3567,7 +3498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bank of Guizhou Co., Ltd. (SEHK:6199)</t>
+          <t>Wuxi Rural Commercial Bank Co.,Ltd (SHSE:600908)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3575,6 +3506,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>0.104</v>
+      </c>
+      <c r="E26">
+        <v>0.136</v>
+      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3588,28 +3525,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>602.7</v>
+        <v>256.9</v>
       </c>
       <c r="L26">
-        <v>0.4762544448834453</v>
+        <v>0.547994880546075</v>
       </c>
       <c r="M26">
-        <v>75.7</v>
+        <v>112</v>
       </c>
       <c r="N26">
-        <v>0.01538555343278729</v>
+        <v>0.07873462214411248</v>
       </c>
       <c r="O26">
-        <v>0.1256014600962336</v>
+        <v>0.4359673024523161</v>
       </c>
       <c r="P26">
-        <v>75.7</v>
+        <v>112</v>
       </c>
       <c r="Q26">
-        <v>0.01538555343278729</v>
+        <v>0.07873462214411248</v>
       </c>
       <c r="R26">
-        <v>0.1256014600962336</v>
+        <v>0.4359673024523161</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3618,55 +3555,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>112.8</v>
+        <v>1495.4</v>
       </c>
       <c r="V26">
-        <v>0.0229258973212471</v>
+        <v>1.051247803163445</v>
       </c>
       <c r="W26">
-        <v>0.1136012364760433</v>
+        <v>0.1072651356993737</v>
       </c>
       <c r="X26">
-        <v>0.1352610779800349</v>
+        <v>0.1025870776338148</v>
       </c>
       <c r="Y26">
-        <v>-0.0216598415039916</v>
+        <v>0.004678058065558863</v>
       </c>
       <c r="Z26">
-        <v>0.08159830806827049</v>
+        <v>0.1153401402386517</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.04569302660022683</v>
+        <v>0.06240779977510787</v>
       </c>
       <c r="AC26">
-        <v>-0.04569302660022683</v>
+        <v>-0.06240779977510787</v>
       </c>
       <c r="AD26">
-        <v>18600.2</v>
+        <v>2793.3</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>18600.2</v>
+        <v>2793.3</v>
       </c>
       <c r="AG26">
-        <v>18487.4</v>
+        <v>1297.9</v>
       </c>
       <c r="AH26">
-        <v>0.7908113807588306</v>
+        <v>0.6625788699653684</v>
       </c>
       <c r="AI26">
-        <v>0.7560472971599754</v>
+        <v>0.5388102310867636</v>
       </c>
       <c r="AJ26">
-        <v>0.7898033117449034</v>
+        <v>0.4770989560358771</v>
       </c>
       <c r="AK26">
-        <v>0.7549236190795089</v>
+        <v>0.3518488397310779</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3683,7 +3620,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank of Jiujiang Co., Ltd. (SEHK:6190)</t>
+          <t>Jiangsu Changshu Rural Commercial Bank Co., Ltd. (SHSE:601128)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3691,6 +3628,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D27">
+        <v>0.151</v>
+      </c>
+      <c r="E27">
+        <v>0.176</v>
+      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3704,28 +3647,28 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>295.7</v>
+        <v>366.4</v>
       </c>
       <c r="L27">
-        <v>0.3568239411125859</v>
+        <v>0.3845507976490344</v>
       </c>
       <c r="M27">
-        <v>38.5184</v>
+        <v>135.2</v>
       </c>
       <c r="N27">
-        <v>0.01142741863707835</v>
+        <v>0.0450621604506216</v>
       </c>
       <c r="O27">
-        <v>0.1302617517754481</v>
+        <v>0.3689956331877729</v>
       </c>
       <c r="P27">
-        <v>38.5184</v>
+        <v>135.2</v>
       </c>
       <c r="Q27">
-        <v>0.01142741863707835</v>
+        <v>0.0450621604506216</v>
       </c>
       <c r="R27">
-        <v>0.1302617517754481</v>
+        <v>0.3689956331877729</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3734,55 +3677,55 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>5606.7</v>
+        <v>1476.9</v>
       </c>
       <c r="V27">
-        <v>1.663363693001454</v>
+        <v>0.4922507749225077</v>
       </c>
       <c r="W27">
-        <v>0.07730314754784064</v>
+        <v>0.1228746772192226</v>
       </c>
       <c r="X27">
-        <v>0.1278596862386176</v>
+        <v>0.1013911889956824</v>
       </c>
       <c r="Y27">
-        <v>-0.05055653869077693</v>
+        <v>0.02148348822354021</v>
       </c>
       <c r="Z27">
-        <v>0.0682450794696533</v>
+        <v>0.1302012872545402</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.04570678624499031</v>
+        <v>0.06243153766507768</v>
       </c>
       <c r="AC27">
-        <v>-0.04570678624499031</v>
+        <v>-0.06243153766507768</v>
       </c>
       <c r="AD27">
-        <v>11680.8</v>
+        <v>5706.1</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>11680.8</v>
+        <v>5706.1</v>
       </c>
       <c r="AG27">
-        <v>6074.099999999999</v>
+        <v>4229.200000000001</v>
       </c>
       <c r="AH27">
-        <v>0.7760555426369464</v>
+        <v>0.6553914361848754</v>
       </c>
       <c r="AI27">
-        <v>0.6758783502291348</v>
+        <v>0.6315900160495878</v>
       </c>
       <c r="AJ27">
-        <v>0.6431157885820769</v>
+        <v>0.5849920464762431</v>
       </c>
       <c r="AK27">
-        <v>0.5202343328451399</v>
+        <v>0.5595956388271409</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3799,7 +3742,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shengjing Bank Co., Ltd. (SEHK:2066)</t>
+          <t>Luzhou Bank Co., Ltd. (SEHK:1983)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3808,7 +3751,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.225</v>
+        <v>0.133</v>
+      </c>
+      <c r="E28">
+        <v>0.0604</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3823,10 +3769,10 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>-92.2</v>
+        <v>137.2</v>
       </c>
       <c r="L28">
-        <v>-0.1662459430219978</v>
+        <v>0.357198646185889</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3835,7 +3781,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3844,61 +3790,61 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>5797.2</v>
+        <v>1524.8</v>
       </c>
       <c r="V28">
-        <v>0.7342503229728703</v>
+        <v>1.411198519204072</v>
       </c>
       <c r="W28">
-        <v>-0.008097379329726692</v>
+        <v>0.09113251411491198</v>
       </c>
       <c r="X28">
-        <v>0.09934120569143075</v>
+        <v>0.123960536163848</v>
       </c>
       <c r="Y28">
-        <v>-0.1074385850211574</v>
+        <v>-0.03282802204893599</v>
       </c>
       <c r="Z28">
-        <v>0.01675053006094946</v>
+        <v>0.07530634251543966</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.04578472757907943</v>
+        <v>0.06646071514810008</v>
       </c>
       <c r="AC28">
-        <v>-0.04578472757907943</v>
+        <v>-0.06646071514810008</v>
       </c>
       <c r="AD28">
-        <v>17778.3</v>
+        <v>3315.4</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>17778.3</v>
+        <v>3315.4</v>
       </c>
       <c r="AG28">
-        <v>11981.1</v>
+        <v>1790.6</v>
       </c>
       <c r="AH28">
-        <v>0.6924712838429989</v>
+        <v>0.7542027798630543</v>
       </c>
       <c r="AI28">
-        <v>0.5860424179692908</v>
+        <v>0.6881135717398974</v>
       </c>
       <c r="AJ28">
-        <v>0.602777148894423</v>
+        <v>0.6236634042701403</v>
       </c>
       <c r="AK28">
-        <v>0.4882472798402542</v>
+        <v>0.5437099565785078</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3915,7 +3861,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bank of Gansu Co., Ltd. (SEHK:2139)</t>
+          <t>QILU BANK CO., LTD. (SHSE:601665)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3924,10 +3870,10 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.06469999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="E29">
-        <v>-0.13</v>
+        <v>0.125</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3942,28 +3888,28 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>88.8</v>
+        <v>485.7</v>
       </c>
       <c r="L29">
-        <v>0.2150641801889077</v>
+        <v>0.5162627551020408</v>
       </c>
       <c r="M29">
-        <v>0.023</v>
+        <v>31.2</v>
       </c>
       <c r="N29">
-        <v>7.934043947704302e-06</v>
+        <v>0.01126557140278029</v>
       </c>
       <c r="O29">
-        <v>0.000259009009009009</v>
+        <v>0.06423718344657196</v>
       </c>
       <c r="P29">
-        <v>0.023</v>
+        <v>31.2</v>
       </c>
       <c r="Q29">
-        <v>7.934043947704302e-06</v>
+        <v>0.01126557140278029</v>
       </c>
       <c r="R29">
-        <v>0.000259009009009009</v>
+        <v>0.06423718344657196</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3972,55 +3918,55 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1391.3</v>
+        <v>1917.9</v>
       </c>
       <c r="V29">
-        <v>0.4799406671496084</v>
+        <v>0.6925076728651381</v>
       </c>
       <c r="W29">
-        <v>0.02505855461805458</v>
+        <v>0.09994855437802243</v>
       </c>
       <c r="X29">
-        <v>0.09857004820122514</v>
+        <v>0.1658910570492752</v>
       </c>
       <c r="Y29">
-        <v>-0.07351149358317056</v>
+        <v>-0.0659425026712528</v>
       </c>
       <c r="Z29">
-        <v>0.04270701888665935</v>
+        <v>0.05687685146000846</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.04578765129584141</v>
+        <v>0.06667192341238404</v>
       </c>
       <c r="AC29">
-        <v>-0.04578765129584141</v>
+        <v>-0.06667192341238404</v>
       </c>
       <c r="AD29">
-        <v>6432.4</v>
+        <v>14500.2</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>6432.4</v>
+        <v>14500.2</v>
       </c>
       <c r="AG29">
-        <v>5041.099999999999</v>
+        <v>12582.3</v>
       </c>
       <c r="AH29">
-        <v>0.6893358910334038</v>
+        <v>0.8396324197872574</v>
       </c>
       <c r="AI29">
-        <v>0.5660729372007884</v>
+        <v>0.7521201715847733</v>
       </c>
       <c r="AJ29">
-        <v>0.6348992443324937</v>
+        <v>0.8195977018981487</v>
       </c>
       <c r="AK29">
-        <v>0.5055305408197033</v>
+        <v>0.724736769347741</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -4037,7 +3983,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xiamen Bank Co., Ltd. (SHSE:601187)</t>
+          <t>Bank of Qingdao Co., Ltd. (SEHK:3866)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4046,10 +3992,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.09390000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="E30">
-        <v>0.157</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4058,103 +4004,97 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0.006771944157043778</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0.006297696862802266</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>322.9</v>
+        <v>435.6</v>
       </c>
       <c r="L30">
-        <v>0.4930523744083066</v>
+        <v>0.4052469997209043</v>
       </c>
       <c r="M30">
-        <v>73.5</v>
+        <v>1301.5488</v>
       </c>
       <c r="N30">
-        <v>0.02564102564102564</v>
+        <v>0.4932164159308803</v>
       </c>
       <c r="O30">
-        <v>0.227624651594921</v>
+        <v>2.987944903581267</v>
       </c>
       <c r="P30">
-        <v>73.5</v>
+        <v>128.0488</v>
       </c>
       <c r="Q30">
-        <v>0.02564102564102564</v>
+        <v>0.04852355147978323</v>
       </c>
       <c r="R30">
-        <v>0.227624651594921</v>
+        <v>0.2939595959595959</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1173.5</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>0.9016181337188433</v>
       </c>
       <c r="U30">
-        <v>2324.9</v>
+        <v>2059.2</v>
       </c>
       <c r="V30">
-        <v>0.811058782487354</v>
+        <v>0.7803251354731137</v>
       </c>
       <c r="W30">
-        <v>0.1382099901553739</v>
+        <v>0.1159651785001198</v>
       </c>
       <c r="X30">
-        <v>0.1789153364361288</v>
+        <v>0.2098145978569709</v>
       </c>
       <c r="Y30">
-        <v>-0.04070534628075489</v>
+        <v>-0.09384941935685114</v>
       </c>
       <c r="Z30">
-        <v>0.05041599442993464</v>
+        <v>0.04147822865698366</v>
       </c>
       <c r="AA30">
-        <v>0.0003175046499564559</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.04858006666138917</v>
+        <v>0.06677774572810634</v>
       </c>
       <c r="AC30">
-        <v>-0.04826256201143272</v>
+        <v>-0.06677774572810634</v>
       </c>
       <c r="AD30">
-        <v>16099.5</v>
+        <v>19807.5</v>
       </c>
       <c r="AE30">
-        <v>62.32526885776014</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>16161.82526885776</v>
+        <v>19807.5</v>
       </c>
       <c r="AG30">
-        <v>13836.92526885776</v>
+        <v>17748.3</v>
       </c>
       <c r="AH30">
-        <v>0.8493561593309851</v>
+        <v>0.8824354907691211</v>
       </c>
       <c r="AI30">
-        <v>0.8220318856328821</v>
+        <v>0.7921447396310323</v>
       </c>
       <c r="AJ30">
-        <v>0.8283884919493507</v>
+        <v>0.8705609401977711</v>
       </c>
       <c r="AK30">
-        <v>0.7981647967596167</v>
+        <v>0.7734913295301517</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
         <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>952.6331360946747</v>
-      </c>
-      <c r="AP30">
-        <v>818.7529744886249</v>
       </c>
     </row>
     <row r="31">
@@ -4165,7 +4105,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dongguan Rural Commercial Bank Co., Ltd. (SEHK:9889)</t>
+          <t>Bank of Lanzhou Co., Ltd. (SZSE:001227)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4186,28 +4126,28 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>830.8</v>
+        <v>245.6</v>
       </c>
       <c r="L31">
-        <v>0.5220560512756063</v>
+        <v>0.4003259983700082</v>
       </c>
       <c r="M31">
-        <v>275.54</v>
+        <v>66</v>
       </c>
       <c r="N31">
-        <v>0.04131220294765882</v>
+        <v>0.02119937044293836</v>
       </c>
       <c r="O31">
-        <v>0.331656234954261</v>
+        <v>0.2687296416938111</v>
       </c>
       <c r="P31">
-        <v>275.54</v>
+        <v>66</v>
       </c>
       <c r="Q31">
-        <v>0.04131220294765882</v>
+        <v>0.02119937044293836</v>
       </c>
       <c r="R31">
-        <v>0.331656234954261</v>
+        <v>0.2687296416938111</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -4216,55 +4156,55 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>5999.2</v>
+        <v>544.8</v>
       </c>
       <c r="V31">
-        <v>0.8994707408129301</v>
+        <v>0.1749911669289821</v>
       </c>
       <c r="W31">
-        <v>0.1495616482744964</v>
+        <v>0.05680845650313417</v>
       </c>
       <c r="X31">
-        <v>0.09886715534997029</v>
+        <v>0.1273073758869652</v>
       </c>
       <c r="Y31">
-        <v>0.0506944929245261</v>
+        <v>-0.07049891938383104</v>
       </c>
       <c r="Z31">
-        <v>0.1110669095426534</v>
+        <v>0.06594646888100611</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.0497560898273162</v>
+        <v>0.06866354977306099</v>
       </c>
       <c r="AC31">
-        <v>-0.0497560898273162</v>
+        <v>-0.06866354977306099</v>
       </c>
       <c r="AD31">
-        <v>14883.8</v>
+        <v>10091.4</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>14883.8</v>
+        <v>10091.4</v>
       </c>
       <c r="AG31">
-        <v>8884.599999999999</v>
+        <v>9546.6</v>
       </c>
       <c r="AH31">
-        <v>0.6905514185631104</v>
+        <v>0.7642278885548327</v>
       </c>
       <c r="AI31">
-        <v>0.6600501119758753</v>
+        <v>0.6841580735045865</v>
       </c>
       <c r="AJ31">
-        <v>0.5711989610589997</v>
+        <v>0.7540817857960963</v>
       </c>
       <c r="AK31">
-        <v>0.5368241059074457</v>
+        <v>0.6720449409727356</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -4281,7 +4221,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QILU BANK CO., LTD. (SHSE:601665)</t>
+          <t>Guangzhou Rural Commercial Bank Co., Ltd. (SEHK:1551)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4290,10 +4230,10 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.08800000000000001</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="E32">
-        <v>0.114</v>
+        <v>-0.141</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4302,34 +4242,34 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0.004384958161802969</v>
+        <v>0.0001318095906527036</v>
       </c>
       <c r="J32">
-        <v>0.003972331230499116</v>
+        <v>0.0001279966865312043</v>
       </c>
       <c r="K32">
-        <v>431</v>
+        <v>383.9</v>
       </c>
       <c r="L32">
-        <v>0.48091943762553</v>
+        <v>0.2735304595653723</v>
       </c>
       <c r="M32">
-        <v>241.8</v>
+        <v>292.8</v>
       </c>
       <c r="N32">
-        <v>0.06009394338544127</v>
+        <v>0.07548726410229968</v>
       </c>
       <c r="O32">
-        <v>0.5610208816705337</v>
+        <v>0.7626986194321439</v>
       </c>
       <c r="P32">
-        <v>241.8</v>
+        <v>292.8</v>
       </c>
       <c r="Q32">
-        <v>0.06009394338544127</v>
+        <v>0.07548726410229968</v>
       </c>
       <c r="R32">
-        <v>0.5610208816705337</v>
+        <v>0.7626986194321439</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -4338,55 +4278,55 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>1524.9</v>
+        <v>6548.9</v>
       </c>
       <c r="V32">
-        <v>0.3789795461888312</v>
+        <v>1.688383005053109</v>
       </c>
       <c r="W32">
-        <v>0.1213913533305168</v>
+        <v>0.04102240791596765</v>
       </c>
       <c r="X32">
-        <v>0.1240815866529689</v>
+        <v>0.2198081062618941</v>
       </c>
       <c r="Y32">
-        <v>-0.002690233322452079</v>
+        <v>-0.1787856983459264</v>
       </c>
       <c r="Z32">
-        <v>0.08448857775996337</v>
+        <v>0.06221022483312686</v>
       </c>
       <c r="AA32">
-        <v>0.0003356166160563556</v>
+        <v>7.962702647001483e-06</v>
       </c>
       <c r="AB32">
-        <v>0.05012758701280108</v>
+        <v>0.06932850902755268</v>
       </c>
       <c r="AC32">
-        <v>-0.04979197039674473</v>
+        <v>-0.06932054632490568</v>
       </c>
       <c r="AD32">
-        <v>13206.4</v>
+        <v>31116.1</v>
       </c>
       <c r="AE32">
-        <v>90.35100247696089</v>
+        <v>1.600026197594653</v>
       </c>
       <c r="AF32">
-        <v>13296.75100247696</v>
+        <v>31117.70002619759</v>
       </c>
       <c r="AG32">
-        <v>11771.85100247696</v>
+        <v>24568.80002619759</v>
       </c>
       <c r="AH32">
-        <v>0.7676908066987067</v>
+        <v>0.8891660595460569</v>
       </c>
       <c r="AI32">
-        <v>0.7308577183316396</v>
+        <v>0.7042753034525455</v>
       </c>
       <c r="AJ32">
-        <v>0.7452637138540448</v>
+        <v>0.8636510638356844</v>
       </c>
       <c r="AK32">
-        <v>0.7062354504763305</v>
+        <v>0.6528161213626478</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -4395,10 +4335,10 @@
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>600.2909090909091</v>
+        <v>61616.03960396039</v>
       </c>
       <c r="AP32">
-        <v>535.0841364762255</v>
+        <v>48651.08916078731</v>
       </c>
     </row>
     <row r="33">
@@ -4409,7 +4349,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luzhou Bank Co., Ltd. (SEHK:1983)</t>
+          <t>Huishang Bank Corporation Limited (SEHK:3698)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4417,6 +4357,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D33">
+        <v>0.102</v>
+      </c>
+      <c r="E33">
+        <v>0.115</v>
+      </c>
       <c r="G33">
         <v>0</v>
       </c>
@@ -4430,28 +4376,28 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>107</v>
+        <v>1867.1</v>
       </c>
       <c r="L33">
-        <v>0.315541138307284</v>
+        <v>0.5225727000475804</v>
       </c>
       <c r="M33">
-        <v>40</v>
+        <v>180.5674</v>
       </c>
       <c r="N33">
-        <v>0.03984857541342897</v>
+        <v>0.04087269681742043</v>
       </c>
       <c r="O33">
-        <v>0.3738317757009346</v>
+        <v>0.09671008515880242</v>
       </c>
       <c r="P33">
-        <v>40</v>
+        <v>180.5674</v>
       </c>
       <c r="Q33">
-        <v>0.03984857541342897</v>
+        <v>0.04087269681742043</v>
       </c>
       <c r="R33">
-        <v>0.3738317757009346</v>
+        <v>0.09671008515880242</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4460,55 +4406,55 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>645.4</v>
+        <v>5410.1</v>
       </c>
       <c r="V33">
-        <v>0.6429567642956764</v>
+        <v>1.224614061297479</v>
       </c>
       <c r="W33">
-        <v>0.0861721832970927</v>
+        <v>0.1165117004680187</v>
       </c>
       <c r="X33">
-        <v>0.147172917317323</v>
+        <v>0.3164863926176956</v>
       </c>
       <c r="Y33">
-        <v>-0.06100073402023026</v>
+        <v>-0.1999746921496768</v>
       </c>
       <c r="Z33">
-        <v>0.08946285352469398</v>
+        <v>0.06153467256368922</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.05033552421006793</v>
+        <v>0.06953876681280302</v>
       </c>
       <c r="AC33">
-        <v>-0.05033552421006793</v>
+        <v>-0.06953876681280302</v>
       </c>
       <c r="AD33">
-        <v>4303.6</v>
+        <v>57517.8</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>4303.6</v>
+        <v>57517.8</v>
       </c>
       <c r="AG33">
-        <v>3658.2</v>
+        <v>52107.7</v>
       </c>
       <c r="AH33">
-        <v>0.8108678448958059</v>
+        <v>0.9286710712417414</v>
       </c>
       <c r="AI33">
-        <v>0.7459742420828206</v>
+        <v>0.7656136857349748</v>
       </c>
       <c r="AJ33">
-        <v>0.7846846846846848</v>
+        <v>0.9218441234487089</v>
       </c>
       <c r="AK33">
-        <v>0.7139762281164002</v>
+        <v>0.747424920714381</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4525,7 +4471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jiangxi Bank Co., Ltd. (SEHK:1916)</t>
+          <t>Zhongyuan Bank Co., Ltd. (SEHK:1216)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4533,6 +4479,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D34">
+        <v>0.07200000000000001</v>
+      </c>
+      <c r="E34">
+        <v>0.0133</v>
+      </c>
       <c r="G34">
         <v>0</v>
       </c>
@@ -4546,85 +4498,82 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>299.4</v>
+        <v>526.9</v>
       </c>
       <c r="L34">
-        <v>0.3217279174725983</v>
+        <v>0.2628192338387869</v>
       </c>
       <c r="M34">
-        <v>49.5</v>
+        <v>-0</v>
       </c>
       <c r="N34">
-        <v>0.02390726877565805</v>
+        <v>-0</v>
       </c>
       <c r="O34">
-        <v>0.1653306613226453</v>
+        <v>-0</v>
       </c>
       <c r="P34">
-        <v>49.5</v>
+        <v>-0</v>
       </c>
       <c r="Q34">
-        <v>0.02390726877565805</v>
+        <v>-0</v>
       </c>
       <c r="R34">
-        <v>0.1653306613226453</v>
+        <v>-0</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
       <c r="U34">
-        <v>1334.4</v>
+        <v>10415.4</v>
       </c>
       <c r="V34">
-        <v>0.6444820091765274</v>
+        <v>3.526937794182385</v>
       </c>
       <c r="W34">
-        <v>0.06045797827228303</v>
+        <v>0.06652273817640077</v>
       </c>
       <c r="X34">
-        <v>0.1772681737868336</v>
+        <v>0.3514366820550447</v>
       </c>
       <c r="Y34">
-        <v>-0.1168101955145506</v>
+        <v>-0.284913943878644</v>
       </c>
       <c r="Z34">
-        <v>0.0542475240021685</v>
+        <v>0.07577177758292263</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.05051313802868644</v>
+        <v>0.06958210080368762</v>
       </c>
       <c r="AC34">
-        <v>-0.05051313802868644</v>
+        <v>-0.06958210080368762</v>
       </c>
       <c r="AD34">
-        <v>11528.7</v>
+        <v>43782.8</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>11528.7</v>
+        <v>43782.8</v>
       </c>
       <c r="AG34">
-        <v>10194.3</v>
+        <v>33367.4</v>
       </c>
       <c r="AH34">
-        <v>0.8477483969645273</v>
+        <v>0.9368130281004539</v>
       </c>
       <c r="AI34">
-        <v>0.6674173304927752</v>
+        <v>0.7709175938626347</v>
       </c>
       <c r="AJ34">
-        <v>0.831183549670602</v>
+        <v>0.9186932999270385</v>
       </c>
       <c r="AK34">
-        <v>0.6395741317004618</v>
+        <v>0.719470780137868</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -4641,7 +4590,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bank of Jinzhou Co., Ltd. (SEHK:416)</t>
+          <t>Jiangxi Bank Co., Ltd. (SEHK:1916)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4649,12 +4598,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D35">
-        <v>-0.226</v>
-      </c>
-      <c r="E35">
-        <v>-0.4320000000000001</v>
-      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -4668,82 +4611,85 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>66.3</v>
+        <v>301.7</v>
       </c>
       <c r="L35">
-        <v>0.1241805581569582</v>
+        <v>0.3295107033639144</v>
       </c>
       <c r="M35">
-        <v>-0</v>
+        <v>46.2</v>
       </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0.06499718626899269</v>
       </c>
       <c r="O35">
-        <v>-0</v>
+        <v>0.1531322505800464</v>
       </c>
       <c r="P35">
-        <v>-0</v>
+        <v>46.2</v>
       </c>
       <c r="Q35">
-        <v>-0</v>
+        <v>0.06499718626899269</v>
       </c>
       <c r="R35">
-        <v>-0</v>
+        <v>0.1531322505800464</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
       <c r="U35">
-        <v>3072.3</v>
+        <v>1686.9</v>
       </c>
       <c r="V35">
-        <v>0.9796875</v>
+        <v>2.373241418120428</v>
       </c>
       <c r="W35">
-        <v>0.01014040561622465</v>
+        <v>0.05352327561737155</v>
       </c>
       <c r="X35">
-        <v>0.2293351816786089</v>
+        <v>0.4709363005163651</v>
       </c>
       <c r="Y35">
-        <v>-0.2191947760623842</v>
+        <v>-0.4174130248989936</v>
       </c>
       <c r="Z35">
-        <v>0.01961519102675734</v>
+        <v>0.05783954516740367</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.05069810267809438</v>
+        <v>0.06967650760490099</v>
       </c>
       <c r="AC35">
-        <v>-0.05069810267809438</v>
+        <v>-0.06967650760490099</v>
       </c>
       <c r="AD35">
-        <v>24410.3</v>
+        <v>14928.7</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>24410.3</v>
+        <v>14928.7</v>
       </c>
       <c r="AG35">
-        <v>21338</v>
+        <v>13241.8</v>
       </c>
       <c r="AH35">
-        <v>0.8861553094244962</v>
+        <v>0.9545509766936283</v>
       </c>
       <c r="AI35">
-        <v>0.6881025403948717</v>
+        <v>0.6982259867451791</v>
       </c>
       <c r="AJ35">
-        <v>0.8718640189588952</v>
+        <v>0.9490560899043906</v>
       </c>
       <c r="AK35">
-        <v>0.6585294344572178</v>
+        <v>0.6723773738194374</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4760,7 +4706,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bank of Qingdao Co., Ltd. (SEHK:3866)</t>
+          <t>Bank of Chongqing Co., Ltd. (SEHK:1963)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4769,10 +4715,10 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.0786</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="E36">
-        <v>0.06519999999999999</v>
+        <v>0.0473</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4787,28 +4733,28 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>435.2</v>
+        <v>679.8</v>
       </c>
       <c r="L36">
-        <v>0.3943100480202953</v>
+        <v>0.516604605213162</v>
       </c>
       <c r="M36">
-        <v>126.2716</v>
+        <v>9.68</v>
       </c>
       <c r="N36">
-        <v>0.04123558226111946</v>
+        <v>0.003601860465116279</v>
       </c>
       <c r="O36">
-        <v>0.2901461397058823</v>
+        <v>0.01423948220064725</v>
       </c>
       <c r="P36">
-        <v>126.2716</v>
+        <v>9.68</v>
       </c>
       <c r="Q36">
-        <v>0.04123558226111946</v>
+        <v>0.003601860465116279</v>
       </c>
       <c r="R36">
-        <v>0.2901461397058823</v>
+        <v>0.01423948220064725</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4817,295 +4763,60 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>4461.5</v>
+        <v>1711.2</v>
       </c>
       <c r="V36">
-        <v>1.456959049049703</v>
+        <v>0.6367255813953488</v>
       </c>
       <c r="W36">
-        <v>0.1343956519053795</v>
+        <v>0.1045411905823735</v>
       </c>
       <c r="X36">
-        <v>0.2413476973227345</v>
+        <v>0.2935775881718679</v>
       </c>
       <c r="Y36">
-        <v>-0.1069520454173549</v>
+        <v>-0.1890363975894944</v>
       </c>
       <c r="Z36">
-        <v>0.05686742270059716</v>
+        <v>0.03338110881394199</v>
       </c>
       <c r="AA36">
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.05072825657566471</v>
+        <v>0.07095603784690484</v>
       </c>
       <c r="AC36">
-        <v>-0.05072825657566471</v>
+        <v>-0.07095603784690484</v>
       </c>
       <c r="AD36">
-        <v>25401.3</v>
+        <v>31807.8</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>25401.3</v>
+        <v>31807.8</v>
       </c>
       <c r="AG36">
-        <v>20939.8</v>
+        <v>30096.6</v>
       </c>
       <c r="AH36">
-        <v>0.8924166037205543</v>
+        <v>0.9220908355631056</v>
       </c>
       <c r="AI36">
-        <v>0.833351377419958</v>
+        <v>0.8099358321450397</v>
       </c>
       <c r="AJ36">
-        <v>0.8724189650862428</v>
+        <v>0.9180242861631096</v>
       </c>
       <c r="AK36">
-        <v>0.8047764360438748</v>
+        <v>0.8012768631126068</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Zhongyuan Bank Co., Ltd. (SEHK:1216)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>532.4</v>
-      </c>
-      <c r="L37">
-        <v>0.2923347243575664</v>
-      </c>
-      <c r="M37">
-        <v>-0</v>
-      </c>
-      <c r="N37">
-        <v>-0</v>
-      </c>
-      <c r="O37">
-        <v>-0</v>
-      </c>
-      <c r="P37">
-        <v>-0</v>
-      </c>
-      <c r="Q37">
-        <v>-0</v>
-      </c>
-      <c r="R37">
-        <v>-0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>7570.5</v>
-      </c>
-      <c r="V37">
-        <v>3.501456916886361</v>
-      </c>
-      <c r="W37">
-        <v>0.07601045072312722</v>
-      </c>
-      <c r="X37">
-        <v>0.3147791995072171</v>
-      </c>
-      <c r="Y37">
-        <v>-0.2387687487840899</v>
-      </c>
-      <c r="Z37">
-        <v>0.06424189833186945</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>0.05085861898601207</v>
-      </c>
-      <c r="AC37">
-        <v>-0.05085861898601207</v>
-      </c>
-      <c r="AD37">
-        <v>24691.5</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>24691.5</v>
-      </c>
-      <c r="AG37">
-        <v>17121</v>
-      </c>
-      <c r="AH37">
-        <v>0.9194856555545625</v>
-      </c>
-      <c r="AI37">
-        <v>0.7201417446845744</v>
-      </c>
-      <c r="AJ37">
-        <v>0.8878759120680804</v>
-      </c>
-      <c r="AK37">
-        <v>0.6408399303801022</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Bank of Chongqing Co., Ltd. (SEHK:1963)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>0.04269999999999999</v>
-      </c>
-      <c r="E38">
-        <v>0.059</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>714.1</v>
-      </c>
-      <c r="L38">
-        <v>0.5075337597725658</v>
-      </c>
-      <c r="M38">
-        <v>86.7</v>
-      </c>
-      <c r="N38">
-        <v>0.02436282912299435</v>
-      </c>
-      <c r="O38">
-        <v>0.1214115670074219</v>
-      </c>
-      <c r="P38">
-        <v>86.7</v>
-      </c>
-      <c r="Q38">
-        <v>0.02436282912299435</v>
-      </c>
-      <c r="R38">
-        <v>0.1214115670074219</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>2169</v>
-      </c>
-      <c r="V38">
-        <v>0.6094922303088207</v>
-      </c>
-      <c r="W38">
-        <v>0.1380383515039048</v>
-      </c>
-      <c r="X38">
-        <v>0.2730759214202005</v>
-      </c>
-      <c r="Y38">
-        <v>-0.1350375699162957</v>
-      </c>
-      <c r="Z38">
-        <v>0.05179573265008614</v>
-      </c>
-      <c r="AA38">
-        <v>0</v>
-      </c>
-      <c r="AB38">
-        <v>0.0518740065028091</v>
-      </c>
-      <c r="AC38">
-        <v>-0.0518740065028091</v>
-      </c>
-      <c r="AD38">
-        <v>34325</v>
-      </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
-      <c r="AF38">
-        <v>34325</v>
-      </c>
-      <c r="AG38">
-        <v>32156</v>
-      </c>
-      <c r="AH38">
-        <v>0.9060625018147648</v>
-      </c>
-      <c r="AI38">
-        <v>0.819451009601841</v>
-      </c>
-      <c r="AJ38">
-        <v>0.9003575558523522</v>
-      </c>
-      <c r="AK38">
-        <v>0.809591427736991</v>
-      </c>
-      <c r="AL38">
-        <v>0</v>
-      </c>
-      <c r="AM38">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/china/china_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/china/china_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ36"/>
+  <dimension ref="A1:AQ38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08990000000000001</v>
+        <v>0.0721</v>
       </c>
       <c r="E2">
-        <v>0.0925</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="F2">
-        <v>0.1068</v>
+        <v>0.113</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.10401258220923e-05</v>
+        <v>1.561621512945217e-05</v>
       </c>
       <c r="J2">
-        <v>3.668930599886688e-05</v>
+        <v>1.415330824126514e-05</v>
       </c>
       <c r="K2">
-        <v>26118.6</v>
+        <v>28611</v>
       </c>
       <c r="L2">
-        <v>0.4636308931053396</v>
+        <v>0.4682367843518478</v>
       </c>
       <c r="M2">
-        <v>7802.3445</v>
+        <v>6867.4466</v>
       </c>
       <c r="N2">
-        <v>0.04775227504879367</v>
+        <v>0.05232033320711851</v>
       </c>
       <c r="O2">
-        <v>0.298727516023064</v>
+        <v>0.2400281919541435</v>
       </c>
       <c r="P2">
-        <v>5434.6445</v>
+        <v>6152.1466</v>
       </c>
       <c r="Q2">
-        <v>0.03326136636961028</v>
+        <v>0.04687074815420352</v>
       </c>
       <c r="R2">
-        <v>0.2080756434112089</v>
+        <v>0.2150273181643424</v>
       </c>
       <c r="S2">
-        <v>2367.7</v>
+        <v>715.3</v>
       </c>
       <c r="T2">
-        <v>0.3034600689574781</v>
+        <v>0.1041580723758376</v>
       </c>
       <c r="U2">
-        <v>111202.4</v>
+        <v>117844.5</v>
       </c>
       <c r="V2">
-        <v>0.6805861482899112</v>
+        <v>0.8978101856119678</v>
       </c>
       <c r="W2">
-        <v>0.1003978822138432</v>
+        <v>0.09561399855064559</v>
       </c>
       <c r="X2">
-        <v>0.1620699428375477</v>
+        <v>0.138849761028187</v>
       </c>
       <c r="Y2">
-        <v>-0.06167206062370449</v>
+        <v>-0.04323576247754138</v>
       </c>
       <c r="Z2">
-        <v>0.05670549964104371</v>
+        <v>0.05529938157600559</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06216009045976439</v>
+        <v>0.05242309155635307</v>
       </c>
       <c r="AC2">
-        <v>-0.06216009045976439</v>
+        <v>-0.05242221636939942</v>
       </c>
       <c r="AD2">
-        <v>906291.9</v>
+        <v>953531.7</v>
       </c>
       <c r="AE2">
-        <v>4.085043079125059</v>
+        <v>7.883957377972469</v>
       </c>
       <c r="AF2">
-        <v>906295.9850430791</v>
+        <v>953539.5839573779</v>
       </c>
       <c r="AG2">
-        <v>795093.5850430791</v>
+        <v>835695.0839573779</v>
       </c>
       <c r="AH2">
-        <v>0.8472525755081026</v>
+        <v>0.8790025547250935</v>
       </c>
       <c r="AI2">
-        <v>0.7568687595327264</v>
+        <v>0.7487526118636539</v>
       </c>
       <c r="AJ2">
-        <v>0.8295309960809103</v>
+        <v>0.8642563502813332</v>
       </c>
       <c r="AK2">
-        <v>0.7319781908984476</v>
+        <v>0.7231325065313945</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>289642.665388303</v>
+        <v>376741.0904780719</v>
       </c>
       <c r="AP2">
-        <v>254104.693206481</v>
+        <v>330183.7550206945</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Tianjin Co., Ltd. (SEHK:1578)</t>
+          <t>Zhongyuan Bank Co., Ltd. (SEHK:1216)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0187</v>
+        <v>0.0635</v>
       </c>
       <c r="E3">
-        <v>-0.04969999999999999</v>
+        <v>-0.0217</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,85 +737,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>525.9</v>
+        <v>490.7</v>
       </c>
       <c r="L3">
-        <v>0.4271789456583543</v>
+        <v>0.2277664314890457</v>
       </c>
       <c r="M3">
-        <v>0.151</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.000101016858442601</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.0002871268301958547</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.151</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.000101016858442601</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.0002871268301958547</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>2653.6</v>
+        <v>6243.4</v>
       </c>
       <c r="V3">
-        <v>1.775220765319775</v>
+        <v>3.984809803420985</v>
       </c>
       <c r="W3">
-        <v>0.06071836791243809</v>
+        <v>0.04176312385102472</v>
       </c>
       <c r="X3">
-        <v>0.5414868979000529</v>
+        <v>0.4295153091987704</v>
       </c>
       <c r="Y3">
-        <v>-0.4807685299876148</v>
+        <v>-0.3877521853477457</v>
       </c>
       <c r="Z3">
-        <v>0.03313568377506171</v>
+        <v>0.04838293122769667</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0614221649796695</v>
+        <v>0.05201365630504722</v>
       </c>
       <c r="AC3">
-        <v>-0.0614221649796695</v>
+        <v>-0.05201365630504722</v>
       </c>
       <c r="AD3">
-        <v>36845.7</v>
+        <v>47433.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>36845.7</v>
+        <v>47433.7</v>
       </c>
       <c r="AG3">
-        <v>34192.1</v>
+        <v>41190.3</v>
       </c>
       <c r="AH3">
-        <v>0.961012506357507</v>
+        <v>0.9680248160733053</v>
       </c>
       <c r="AI3">
-        <v>0.8032460596019271</v>
+        <v>0.7818685910485255</v>
       </c>
       <c r="AJ3">
-        <v>0.9581134814175509</v>
+        <v>0.9633557935407219</v>
       </c>
       <c r="AK3">
-        <v>0.7911651325623477</v>
+        <v>0.7568449039664704</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harbin Bank Co., Ltd. (SEHK:6138)</t>
+          <t>Bank of Tianjin Co., Ltd. (SEHK:1578)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,7 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.132</v>
+        <v>-0.00532</v>
+      </c>
+      <c r="E4">
+        <v>-0.0208</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-12.3</v>
+        <v>513.3</v>
       </c>
       <c r="L4">
-        <v>-0.01495622568093385</v>
+        <v>0.4468140668523677</v>
       </c>
       <c r="M4">
-        <v>1195.3</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>2.530270956816258</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-97.17886178861788</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>1.1</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.002328535139712109</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0.08943089430894309</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>1194.2</v>
-      </c>
-      <c r="T4">
-        <v>0.999079728938342</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>4882.6</v>
+        <v>5367.5</v>
       </c>
       <c r="V4">
-        <v>10.33573243014395</v>
+        <v>3.837217615098656</v>
       </c>
       <c r="W4">
-        <v>-0.001368019485936092</v>
+        <v>0.05767545338097485</v>
       </c>
       <c r="X4">
-        <v>0.5335373139061763</v>
+        <v>0.3617586940732595</v>
       </c>
       <c r="Y4">
-        <v>-0.5349053333921124</v>
+        <v>-0.3040832406922847</v>
       </c>
       <c r="Z4">
-        <v>0.0677792887460337</v>
+        <v>0.02665930256034197</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06142426131940251</v>
+        <v>0.05203659797985238</v>
       </c>
       <c r="AC4">
-        <v>-0.06142426131940251</v>
+        <v>-0.05203659797985238</v>
       </c>
       <c r="AD4">
-        <v>11450.2</v>
+        <v>34680.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11450.2</v>
+        <v>34680.4</v>
       </c>
       <c r="AG4">
-        <v>6567.6</v>
+        <v>29312.9</v>
       </c>
       <c r="AH4">
-        <v>0.9603777699495077</v>
+        <v>0.9612297390186034</v>
       </c>
       <c r="AI4">
-        <v>0.5497186641829739</v>
+        <v>0.7971149735447304</v>
       </c>
       <c r="AJ4">
-        <v>0.9328977272727274</v>
+        <v>0.9544538400674661</v>
       </c>
       <c r="AK4">
-        <v>0.4118495478660028</v>
+        <v>0.7685625814435801</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Zhengzhou Co., Ltd. (SEHK:6196)</t>
+          <t>Harbin Bank Co., Ltd. (SEHK:6138)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00594</v>
+        <v>-0.122</v>
       </c>
       <c r="E5">
-        <v>-0.04190000000000001</v>
+        <v>-0.344</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +975,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>463.5</v>
+        <v>89.2</v>
       </c>
       <c r="L5">
-        <v>0.4254245066544287</v>
+        <v>0.1095015958752762</v>
       </c>
       <c r="M5">
-        <v>0.6889999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="N5">
-        <v>0.0002802065964455651</v>
+        <v>0.2030321046373365</v>
       </c>
       <c r="O5">
-        <v>0.001486515641855448</v>
+        <v>0.7656950672645739</v>
       </c>
       <c r="P5">
-        <v>0.6889999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="Q5">
-        <v>0.0002802065964455651</v>
+        <v>0.2030321046373365</v>
       </c>
       <c r="R5">
-        <v>0.001486515641855448</v>
+        <v>0.7656950672645739</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1005,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2277.4</v>
+        <v>3839.4</v>
       </c>
       <c r="V5">
-        <v>0.9261865061612916</v>
+        <v>11.41319857312723</v>
       </c>
       <c r="W5">
-        <v>0.07369659580557454</v>
+        <v>0.00983613788236332</v>
       </c>
       <c r="X5">
-        <v>0.2340775063689042</v>
+        <v>0.292482682767922</v>
       </c>
       <c r="Y5">
-        <v>-0.1603809105633296</v>
+        <v>-0.2826465448855587</v>
       </c>
       <c r="Z5">
-        <v>0.03626541155167363</v>
+        <v>0.05209705682966449</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06163179004008361</v>
+        <v>0.05207293367912774</v>
       </c>
       <c r="AC5">
-        <v>-0.06163179004008361</v>
+        <v>-0.05207293367912774</v>
       </c>
       <c r="AD5">
-        <v>21540.1</v>
+        <v>6455.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>21540.1</v>
+        <v>6455.1</v>
       </c>
       <c r="AG5">
-        <v>19262.7</v>
+        <v>2615.7</v>
       </c>
       <c r="AH5">
-        <v>0.8975415642318429</v>
+        <v>0.9504674961348746</v>
       </c>
       <c r="AI5">
-        <v>0.7080342116335332</v>
+        <v>0.4243258877509433</v>
       </c>
       <c r="AJ5">
-        <v>0.8867993149675898</v>
+        <v>0.8860472206226077</v>
       </c>
       <c r="AK5">
-        <v>0.6844093089358678</v>
+        <v>0.2299880420637991</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chongqing Rural Commercial Bank Co., Ltd. (SEHK:3618)</t>
+          <t>Bank of Zhengzhou Co., Ltd. (SEHK:6196)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,13 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0122</v>
+        <v>-0.0824</v>
       </c>
       <c r="E6">
-        <v>0.0317</v>
-      </c>
-      <c r="F6">
-        <v>0.06059999999999999</v>
+        <v>-0.165</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,85 +1097,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1412.7</v>
+        <v>242.5</v>
       </c>
       <c r="L6">
-        <v>0.4900274029622949</v>
+        <v>0.3158785984108375</v>
       </c>
       <c r="M6">
-        <v>427.6</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.07937774972618761</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.3026828059743753</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>427.6</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.07937774972618761</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.3026828059743753</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>4679</v>
+        <v>1665.3</v>
       </c>
       <c r="V6">
-        <v>0.8685886131170061</v>
+        <v>0.7504055515501082</v>
       </c>
       <c r="W6">
-        <v>0.08741847254365663</v>
+        <v>0.03221649484536083</v>
       </c>
       <c r="X6">
-        <v>0.2285090884751501</v>
+        <v>0.1945564559431615</v>
       </c>
       <c r="Y6">
-        <v>-0.1410906159314935</v>
+        <v>-0.1623399610978006</v>
       </c>
       <c r="Z6">
-        <v>0.04610124715954976</v>
+        <v>0.02752609367548826</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06164207209601001</v>
+        <v>0.05218093219482033</v>
       </c>
       <c r="AC6">
-        <v>-0.06164207209601001</v>
+        <v>-0.05218093219482033</v>
       </c>
       <c r="AD6">
-        <v>45639.1</v>
+        <v>25003.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>45639.1</v>
+        <v>25003.4</v>
       </c>
       <c r="AG6">
-        <v>40960.1</v>
+        <v>23338.1</v>
       </c>
       <c r="AH6">
-        <v>0.8944283306549602</v>
+        <v>0.9184794986518554</v>
       </c>
       <c r="AI6">
-        <v>0.7391270549481516</v>
+        <v>0.7664206280116235</v>
       </c>
       <c r="AJ6">
-        <v>0.8837702548169245</v>
+        <v>0.913167666381034</v>
       </c>
       <c r="AK6">
-        <v>0.7177382189411634</v>
+        <v>0.7538559933846497</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of Guiyang Co.,Ltd. (SHSE:601997)</t>
+          <t>Xiamen Bank Co., Ltd. (SHSE:601187)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1206,12 +1197,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0665</v>
-      </c>
-      <c r="E7">
-        <v>0.07980000000000001</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1225,28 +1210,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>855</v>
+        <v>379.6</v>
       </c>
       <c r="L7">
-        <v>0.546989955856951</v>
+        <v>0.5310576385002799</v>
       </c>
       <c r="M7">
-        <v>153.5604</v>
+        <v>121</v>
       </c>
       <c r="N7">
-        <v>0.05276627035942548</v>
+        <v>0.06412294647588765</v>
       </c>
       <c r="O7">
-        <v>0.1796028070175439</v>
+        <v>0.3187565858798735</v>
       </c>
       <c r="P7">
-        <v>153.5604</v>
+        <v>121</v>
       </c>
       <c r="Q7">
-        <v>0.05276627035942548</v>
+        <v>0.06412294647588765</v>
       </c>
       <c r="R7">
-        <v>0.1796028070175439</v>
+        <v>0.3187565858798735</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1255,55 +1240,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1838.2</v>
+        <v>3070.2</v>
       </c>
       <c r="V7">
-        <v>0.631640437083362</v>
+        <v>1.627027027027027</v>
       </c>
       <c r="W7">
-        <v>0.1198839019055231</v>
+        <v>0.1134387233661058</v>
       </c>
       <c r="X7">
-        <v>0.2195800806190417</v>
+        <v>0.1808275171399706</v>
       </c>
       <c r="Y7">
-        <v>-0.09969617871351867</v>
+        <v>-0.06738879377386471</v>
       </c>
       <c r="Z7">
-        <v>0.06127953519917514</v>
+        <v>0.04274506051762905</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06165993055935257</v>
+        <v>0.0522083320405362</v>
       </c>
       <c r="AC7">
-        <v>-0.06165993055935257</v>
+        <v>-0.0522083320405362</v>
       </c>
       <c r="AD7">
-        <v>23312.8</v>
+        <v>19164.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>23312.8</v>
+        <v>19164.8</v>
       </c>
       <c r="AG7">
-        <v>21474.6</v>
+        <v>16094.6</v>
       </c>
       <c r="AH7">
-        <v>0.8890210883575487</v>
+        <v>0.9103639593763954</v>
       </c>
       <c r="AI7">
-        <v>0.7426468948600735</v>
+        <v>0.8239664304877209</v>
       </c>
       <c r="AJ7">
-        <v>0.8806551622322102</v>
+        <v>0.8950593940472483</v>
       </c>
       <c r="AK7">
-        <v>0.7266396646059831</v>
+        <v>0.7971964931398285</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,7 +1305,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank of Changsha Co., Ltd. (SHSE:601577)</t>
+          <t>Bank of Qingdao Co., Ltd. (SEHK:3866)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1329,10 +1314,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.105</v>
+        <v>0.113</v>
       </c>
       <c r="E8">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,28 +1332,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>930</v>
+        <v>476.5</v>
       </c>
       <c r="L8">
-        <v>0.4392801473714043</v>
+        <v>0.4390895687430888</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>128.0488</v>
       </c>
       <c r="N8">
-        <v>0.005074210326018014</v>
+        <v>0.06153234022104756</v>
       </c>
       <c r="O8">
-        <v>0.02150537634408602</v>
+        <v>0.2687278069254984</v>
       </c>
       <c r="P8">
-        <v>20</v>
+        <v>128.0488</v>
       </c>
       <c r="Q8">
-        <v>0.005074210326018014</v>
+        <v>0.06153234022104756</v>
       </c>
       <c r="R8">
-        <v>0.02150537634408602</v>
+        <v>0.2687278069254984</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1377,55 +1362,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2645.5</v>
+        <v>2484.4</v>
       </c>
       <c r="V8">
-        <v>0.6711911708740327</v>
+        <v>1.193849111004325</v>
       </c>
       <c r="W8">
-        <v>0.1246749068289675</v>
+        <v>0.09359838142568112</v>
       </c>
       <c r="X8">
-        <v>0.2152764729098584</v>
+        <v>0.1748427739952964</v>
       </c>
       <c r="Y8">
-        <v>-0.09060156608089096</v>
+        <v>-0.08124439256961531</v>
       </c>
       <c r="Z8">
-        <v>0.05930235489536444</v>
+        <v>0.04751479911730708</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06166920787546004</v>
+        <v>0.05222206109792431</v>
       </c>
       <c r="AC8">
-        <v>-0.06166920787546004</v>
+        <v>-0.05222206109792431</v>
       </c>
       <c r="AD8">
-        <v>30697.5</v>
+        <v>20127.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>30697.5</v>
+        <v>20127.6</v>
       </c>
       <c r="AG8">
-        <v>28052</v>
+        <v>17643.2</v>
       </c>
       <c r="AH8">
-        <v>0.8862120730967984</v>
+        <v>0.906297560404528</v>
       </c>
       <c r="AI8">
-        <v>0.7815085616525542</v>
+        <v>0.7892897897721257</v>
       </c>
       <c r="AJ8">
-        <v>0.8768031006298155</v>
+        <v>0.8944950872532219</v>
       </c>
       <c r="AK8">
-        <v>0.765730476629825</v>
+        <v>0.7665457389264223</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1442,7 +1427,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xiamen Bank Co., Ltd. (SHSE:601187)</t>
+          <t>Bank of Changsha Co., Ltd. (SHSE:601577)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1450,6 +1435,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="E9">
+        <v>0.113</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1463,28 +1454,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>345.2</v>
+        <v>1001</v>
       </c>
       <c r="L9">
-        <v>0.5258187357197258</v>
+        <v>0.452838724270527</v>
       </c>
       <c r="M9">
-        <v>109.3</v>
+        <v>22.8</v>
       </c>
       <c r="N9">
-        <v>0.04985176738882554</v>
+        <v>0.005894671527185294</v>
       </c>
       <c r="O9">
-        <v>0.3166280417149478</v>
+        <v>0.02277722277722278</v>
       </c>
       <c r="P9">
-        <v>109.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q9">
-        <v>0.04985176738882554</v>
+        <v>0.005894671527185294</v>
       </c>
       <c r="R9">
-        <v>0.3166280417149478</v>
+        <v>0.02277722277722278</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1493,55 +1484,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>3227.2</v>
+        <v>7324.6</v>
       </c>
       <c r="V9">
-        <v>1.471927023945268</v>
+        <v>1.893689081930763</v>
       </c>
       <c r="W9">
-        <v>0.100847210049664</v>
+        <v>0.1337913336362907</v>
       </c>
       <c r="X9">
-        <v>0.2111070288947496</v>
+        <v>0.1682111400067597</v>
       </c>
       <c r="Y9">
-        <v>-0.1102598188450856</v>
+        <v>-0.03441980637046901</v>
       </c>
       <c r="Z9">
-        <v>0.03817393124622041</v>
+        <v>0.06076808884979107</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06167865514159834</v>
+        <v>0.05223880603362552</v>
       </c>
       <c r="AC9">
-        <v>-0.06167865514159834</v>
+        <v>-0.05223880603362552</v>
       </c>
       <c r="AD9">
-        <v>16603.3</v>
+        <v>35335.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>16603.3</v>
+        <v>35335.6</v>
       </c>
       <c r="AG9">
-        <v>13376.1</v>
+        <v>28011</v>
       </c>
       <c r="AH9">
-        <v>0.8833515998254929</v>
+        <v>0.9013378907495504</v>
       </c>
       <c r="AI9">
-        <v>0.8291617143256659</v>
+        <v>0.7938247392340682</v>
       </c>
       <c r="AJ9">
-        <v>0.8591716660457588</v>
+        <v>0.8786689628563094</v>
       </c>
       <c r="AK9">
-        <v>0.7963386318985533</v>
+        <v>0.7532167202226495</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1558,7 +1549,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bank of Jiangsu Co., Ltd. (SHSE:600919)</t>
+          <t>Bank of Guiyang Co.,Ltd. (SHSE:601997)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1567,10 +1558,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.152</v>
+        <v>0.035</v>
       </c>
       <c r="E10">
-        <v>0.164</v>
+        <v>0.0332</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,28 +1576,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3454.9</v>
+        <v>819.3</v>
       </c>
       <c r="L10">
-        <v>0.5065612949576999</v>
+        <v>0.5557213592891541</v>
       </c>
       <c r="M10">
-        <v>827.1032</v>
+        <v>149.9042</v>
       </c>
       <c r="N10">
-        <v>0.05298275552822405</v>
+        <v>0.05656121948458664</v>
       </c>
       <c r="O10">
-        <v>0.2394000405221569</v>
+        <v>0.1829661906505554</v>
       </c>
       <c r="P10">
-        <v>827.1032</v>
+        <v>149.9042</v>
       </c>
       <c r="Q10">
-        <v>0.05298275552822405</v>
+        <v>0.05656121948458664</v>
       </c>
       <c r="R10">
-        <v>0.2394000405221569</v>
+        <v>0.1829661906505554</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1615,55 +1606,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>9248</v>
+        <v>1367.4</v>
       </c>
       <c r="V10">
-        <v>0.5924103825556666</v>
+        <v>0.5159415915179414</v>
       </c>
       <c r="W10">
-        <v>0.1315866649908401</v>
+        <v>0.1152985547221323</v>
       </c>
       <c r="X10">
-        <v>0.2042252150313255</v>
+        <v>0.1649653957963486</v>
       </c>
       <c r="Y10">
-        <v>-0.07263855004048539</v>
+        <v>-0.04966684107421628</v>
       </c>
       <c r="Z10">
-        <v>0.0559358258946878</v>
+        <v>0.05034782103864792</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06169533213958692</v>
+        <v>0.05224766485060164</v>
       </c>
       <c r="AC10">
-        <v>-0.06169533213958692</v>
+        <v>-0.05224766485060164</v>
       </c>
       <c r="AD10">
-        <v>112664.2</v>
+        <v>23516.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>112664.2</v>
+        <v>23516.2</v>
       </c>
       <c r="AG10">
-        <v>103416.2</v>
+        <v>22148.8</v>
       </c>
       <c r="AH10">
-        <v>0.8783020853634769</v>
+        <v>0.8987140045477997</v>
       </c>
       <c r="AI10">
-        <v>0.7901978717494802</v>
+        <v>0.7344543484099868</v>
       </c>
       <c r="AJ10">
-        <v>0.8688465642249237</v>
+        <v>0.8931291861398196</v>
       </c>
       <c r="AK10">
-        <v>0.7756455450118953</v>
+        <v>0.7226079239964505</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1680,7 +1671,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qingdao Rural Commercial Bank Co., Ltd. (SZSE:002958)</t>
+          <t>Chongqing Rural Commercial Bank Co., Ltd. (SEHK:3618)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1688,6 +1679,15 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.0168</v>
+      </c>
+      <c r="E11">
+        <v>0.0413</v>
+      </c>
+      <c r="F11">
+        <v>0.0454</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1701,28 +1701,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>440.2</v>
+        <v>1506</v>
       </c>
       <c r="L11">
-        <v>0.4860329027271723</v>
+        <v>0.4931722173101484</v>
       </c>
       <c r="M11">
-        <v>112.1</v>
+        <v>455</v>
       </c>
       <c r="N11">
-        <v>0.04815498947549293</v>
+        <v>0.07504040637266221</v>
       </c>
       <c r="O11">
-        <v>0.2546569741026806</v>
+        <v>0.302124833997344</v>
       </c>
       <c r="P11">
-        <v>112.1</v>
+        <v>455</v>
       </c>
       <c r="Q11">
-        <v>0.04815498947549293</v>
+        <v>0.07504040637266221</v>
       </c>
       <c r="R11">
-        <v>0.2546569741026806</v>
+        <v>0.302124833997344</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1731,55 +1731,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1956.3</v>
+        <v>4373</v>
       </c>
       <c r="V11">
-        <v>0.8403711499634864</v>
+        <v>0.7212125210278062</v>
       </c>
       <c r="W11">
-        <v>0.08360397318291454</v>
+        <v>0.09490619663101908</v>
       </c>
       <c r="X11">
-        <v>0.1891440586744876</v>
+        <v>0.1530782585949976</v>
       </c>
       <c r="Y11">
-        <v>-0.105540085491573</v>
+        <v>-0.05817206196397855</v>
       </c>
       <c r="Z11">
-        <v>0.04355101628655098</v>
+        <v>0.05379405106885223</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06173745716984197</v>
+        <v>0.05228456619944929</v>
       </c>
       <c r="AC11">
-        <v>-0.06173745716984197</v>
+        <v>-0.05228456619944929</v>
       </c>
       <c r="AD11">
-        <v>14986</v>
+        <v>47970</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>14986</v>
+        <v>47970</v>
       </c>
       <c r="AG11">
-        <v>13029.7</v>
+        <v>43597</v>
       </c>
       <c r="AH11">
-        <v>0.8655473348003626</v>
+        <v>0.8877842223513605</v>
       </c>
       <c r="AI11">
-        <v>0.7416792457499196</v>
+        <v>0.7401315789473684</v>
       </c>
       <c r="AJ11">
-        <v>0.8484203260926186</v>
+        <v>0.8779027152419231</v>
       </c>
       <c r="AK11">
-        <v>0.713987462464108</v>
+        <v>0.721329322731048</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1805,11 +1805,14 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.187</v>
+        <v>0.205</v>
       </c>
       <c r="E12">
         <v>0.216</v>
       </c>
+      <c r="F12">
+        <v>0.185</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1817,34 +1820,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.0001923308315862105</v>
+        <v>9.544722640297163e-05</v>
       </c>
       <c r="J12">
-        <v>0.0001726662164051478</v>
+        <v>8.338737244512318e-05</v>
       </c>
       <c r="K12">
-        <v>1616.5</v>
+        <v>1931.9</v>
       </c>
       <c r="L12">
-        <v>0.5225472765475998</v>
+        <v>0.5281734423271455</v>
       </c>
       <c r="M12">
-        <v>290.5847</v>
+        <v>326.1665</v>
       </c>
       <c r="N12">
-        <v>0.02583824902412349</v>
+        <v>0.03896107076305604</v>
       </c>
       <c r="O12">
-        <v>0.1797616455304671</v>
+        <v>0.1688319788808944</v>
       </c>
       <c r="P12">
-        <v>290.5847</v>
+        <v>326.1665</v>
       </c>
       <c r="Q12">
-        <v>0.02583824902412349</v>
+        <v>0.03896107076305604</v>
       </c>
       <c r="R12">
-        <v>0.1797616455304671</v>
+        <v>0.1688319788808944</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1853,55 +1856,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2413.3</v>
+        <v>5375.4</v>
       </c>
       <c r="V12">
-        <v>0.214586130549603</v>
+        <v>0.6420994791915523</v>
       </c>
       <c r="W12">
-        <v>0.1337918590985085</v>
+        <v>0.1575851999282184</v>
       </c>
       <c r="X12">
-        <v>0.1742889536050742</v>
+        <v>0.1484002801153</v>
       </c>
       <c r="Y12">
-        <v>-0.04049709450656569</v>
+        <v>0.00918491981291833</v>
       </c>
       <c r="Z12">
-        <v>0.04629470616348308</v>
+        <v>0.0487614603642462</v>
       </c>
       <c r="AA12">
-        <v>7.993531752836701e-06</v>
+        <v>4.06609005636151e-06</v>
       </c>
       <c r="AB12">
-        <v>0.06178857698570092</v>
+        <v>0.0523013686868895</v>
       </c>
       <c r="AC12">
-        <v>-0.06178058345394809</v>
+        <v>-0.05229730259683314</v>
       </c>
       <c r="AD12">
-        <v>63762.9</v>
+        <v>63062.6</v>
       </c>
       <c r="AE12">
-        <v>0.6951228624402891</v>
+        <v>0.4094133999292535</v>
       </c>
       <c r="AF12">
-        <v>63763.59512286244</v>
+        <v>63063.00941339993</v>
       </c>
       <c r="AG12">
-        <v>61350.29512286244</v>
+        <v>57687.60941339993</v>
       </c>
       <c r="AH12">
-        <v>0.8500691144604439</v>
+        <v>0.8828075064909695</v>
       </c>
       <c r="AI12">
-        <v>0.8235456591210401</v>
+        <v>0.8093571114359277</v>
       </c>
       <c r="AJ12">
-        <v>0.845085021123005</v>
+        <v>0.8732712656669813</v>
       </c>
       <c r="AK12">
-        <v>0.8178687671867708</v>
+        <v>0.7952303758867741</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1910,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>86870.43596730246</v>
+        <v>146316.9373549884</v>
       </c>
       <c r="AP12">
-        <v>83583.50834177443</v>
+        <v>133845.9615160091</v>
       </c>
     </row>
     <row r="13">
@@ -1924,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank of Suzhou Co., Ltd. (SZSE:002966)</t>
+          <t>Qingdao Rural Commercial Bank Co., Ltd. (SZSE:002958)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1945,28 +1948,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>526.4</v>
+        <v>351.5</v>
       </c>
       <c r="L13">
-        <v>0.4355812991311543</v>
+        <v>0.5060466455513964</v>
       </c>
       <c r="M13">
-        <v>399.9</v>
+        <v>36.3</v>
       </c>
       <c r="N13">
-        <v>0.09668762088974854</v>
+        <v>0.01768402591708482</v>
       </c>
       <c r="O13">
-        <v>0.7596884498480243</v>
+        <v>0.103271692745377</v>
       </c>
       <c r="P13">
-        <v>399.9</v>
+        <v>36.3</v>
       </c>
       <c r="Q13">
-        <v>0.09668762088974854</v>
+        <v>0.01768402591708482</v>
       </c>
       <c r="R13">
-        <v>0.7596884498480243</v>
+        <v>0.103271692745377</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1975,55 +1978,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1483.4</v>
+        <v>1853.8</v>
       </c>
       <c r="V13">
-        <v>0.3586557059961316</v>
+        <v>0.9031032298923369</v>
       </c>
       <c r="W13">
-        <v>0.1062747314867157</v>
+        <v>0.06688485909462828</v>
       </c>
       <c r="X13">
-        <v>0.1582488286258202</v>
+        <v>0.1489535431428312</v>
       </c>
       <c r="Y13">
-        <v>-0.05197409713910453</v>
+        <v>-0.08206868404820296</v>
       </c>
       <c r="Z13">
-        <v>0.05547980737006891</v>
+        <v>0.03660606060606061</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06185886631770332</v>
+        <v>0.05229930415844612</v>
       </c>
       <c r="AC13">
-        <v>-0.06185886631770332</v>
+        <v>-0.05229930415844612</v>
       </c>
       <c r="AD13">
-        <v>20021</v>
+        <v>15554.8</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>20021</v>
+        <v>15554.8</v>
       </c>
       <c r="AG13">
-        <v>18537.6</v>
+        <v>13701</v>
       </c>
       <c r="AH13">
-        <v>0.8287866870886286</v>
+        <v>0.8834189975862559</v>
       </c>
       <c r="AI13">
-        <v>0.7811792798838825</v>
+        <v>0.7421643517966287</v>
       </c>
       <c r="AJ13">
-        <v>0.8175852092301178</v>
+        <v>0.8697004513225464</v>
       </c>
       <c r="AK13">
-        <v>0.7677360037770543</v>
+        <v>0.7171458631031828</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2040,7 +2043,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank of Guizhou Co., Ltd. (SEHK:6199)</t>
+          <t>Bank of Nanjing Co., Ltd. (SHSE:601009)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2048,6 +2051,15 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.111</v>
+      </c>
+      <c r="E14">
+        <v>0.116</v>
+      </c>
+      <c r="F14">
+        <v>-0.0158</v>
+      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2061,28 +2073,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>562</v>
+        <v>2565.8</v>
       </c>
       <c r="L14">
-        <v>0.4871283695934818</v>
+        <v>0.5271180869422303</v>
       </c>
       <c r="M14">
-        <v>153.8</v>
+        <v>134.2</v>
       </c>
       <c r="N14">
-        <v>0.03137622914031581</v>
+        <v>0.01246574706237518</v>
       </c>
       <c r="O14">
-        <v>0.2736654804270463</v>
+        <v>0.05230337516564034</v>
       </c>
       <c r="P14">
-        <v>153.8</v>
+        <v>134.2</v>
       </c>
       <c r="Q14">
-        <v>0.03137622914031581</v>
+        <v>0.01246574706237518</v>
       </c>
       <c r="R14">
-        <v>0.2736654804270463</v>
+        <v>0.05230337516564034</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2091,55 +2103,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>3098.1</v>
+        <v>5536</v>
       </c>
       <c r="V14">
-        <v>0.6320331306866864</v>
+        <v>0.5142352886535693</v>
       </c>
       <c r="W14">
-        <v>0.09733624302885448</v>
+        <v>0.1472938529013296</v>
       </c>
       <c r="X14">
-        <v>0.1458705276769378</v>
+        <v>0.1408529913998399</v>
       </c>
       <c r="Y14">
-        <v>-0.04853428464808336</v>
+        <v>0.006440861501489648</v>
       </c>
       <c r="Z14">
-        <v>0.07102577046677419</v>
+        <v>0.06612401036770579</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06192842895190486</v>
+        <v>0.05233186129705987</v>
       </c>
       <c r="AC14">
-        <v>-0.06192842895190486</v>
+        <v>-0.05233186129705987</v>
       </c>
       <c r="AD14">
-        <v>20591.8</v>
+        <v>74523.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>20591.8</v>
+        <v>74523.3</v>
       </c>
       <c r="AG14">
-        <v>17493.7</v>
+        <v>68987.3</v>
       </c>
       <c r="AH14">
-        <v>0.8077242915869081</v>
+        <v>0.8737759236851732</v>
       </c>
       <c r="AI14">
-        <v>0.7736246726752901</v>
+        <v>0.762320412035782</v>
       </c>
       <c r="AJ14">
-        <v>0.7811256725681499</v>
+        <v>0.8650141437040455</v>
       </c>
       <c r="AK14">
-        <v>0.7438050613966461</v>
+        <v>0.7480528070698582</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2156,7 +2168,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bank of Xi'an Co.,Ltd. (SHSE:600928)</t>
+          <t>Bank of Guizhou Co., Ltd. (SEHK:6199)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2164,12 +2176,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.0226</v>
-      </c>
-      <c r="E15">
-        <v>0.0403</v>
-      </c>
       <c r="G15">
         <v>0</v>
       </c>
@@ -2183,28 +2189,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>358.9</v>
+        <v>531</v>
       </c>
       <c r="L15">
-        <v>0.5490286063943705</v>
+        <v>0.4812398042414355</v>
       </c>
       <c r="M15">
-        <v>410.6</v>
+        <v>120.3</v>
       </c>
       <c r="N15">
-        <v>0.1810246010052024</v>
+        <v>0.04051596389599892</v>
       </c>
       <c r="O15">
-        <v>1.144051267762608</v>
+        <v>0.2265536723163842</v>
       </c>
       <c r="P15">
-        <v>410.6</v>
+        <v>120.3</v>
       </c>
       <c r="Q15">
-        <v>0.1810246010052024</v>
+        <v>0.04051596389599892</v>
       </c>
       <c r="R15">
-        <v>1.144051267762608</v>
+        <v>0.2265536723163842</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2213,55 +2219,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2052.7</v>
+        <v>740.7</v>
       </c>
       <c r="V15">
-        <v>0.9049907415571818</v>
+        <v>0.2494611343122727</v>
       </c>
       <c r="W15">
-        <v>0.0865215399821605</v>
+        <v>0.08812546676624347</v>
       </c>
       <c r="X15">
-        <v>0.1444170496144894</v>
+        <v>0.136846530656534</v>
       </c>
       <c r="Y15">
-        <v>-0.05789550963232887</v>
+        <v>-0.04872106389029054</v>
       </c>
       <c r="Z15">
-        <v>0.04732772476506277</v>
+        <v>0.04691486104969557</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.06193773637570153</v>
+        <v>0.05235003936682769</v>
       </c>
       <c r="AC15">
-        <v>-0.06193773637570153</v>
+        <v>-0.05235003936682769</v>
       </c>
       <c r="AD15">
-        <v>9358</v>
+        <v>19591.7</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>9358</v>
+        <v>19591.7</v>
       </c>
       <c r="AG15">
-        <v>7305.3</v>
+        <v>18851</v>
       </c>
       <c r="AH15">
-        <v>0.8049061602243209</v>
+        <v>0.868391775150814</v>
       </c>
       <c r="AI15">
-        <v>0.6978738636617871</v>
+        <v>0.7517487481534064</v>
       </c>
       <c r="AJ15">
-        <v>0.7630751553768215</v>
+        <v>0.8639242536732019</v>
       </c>
       <c r="AK15">
-        <v>0.6432647095081274</v>
+        <v>0.7444867460743737</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2278,7 +2284,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bank of Nanjing Co., Ltd. (SHSE:601009)</t>
+          <t>Bank of Jiangsu Co., Ltd. (SHSE:600919)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2287,10 +2293,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.137</v>
+        <v>0.182</v>
       </c>
       <c r="E16">
-        <v>0.146</v>
+        <v>0.187</v>
+      </c>
+      <c r="F16">
+        <v>0.0728</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2305,28 +2314,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>2598.2</v>
+        <v>4187</v>
       </c>
       <c r="L16">
-        <v>0.5155261017083672</v>
+        <v>0.5277487174962502</v>
       </c>
       <c r="M16">
-        <v>37.9</v>
+        <v>1229.5371</v>
       </c>
       <c r="N16">
-        <v>0.002426221112604827</v>
+        <v>0.07101486097794824</v>
       </c>
       <c r="O16">
-        <v>0.01458702178431222</v>
+        <v>0.293655863386673</v>
       </c>
       <c r="P16">
-        <v>37.9</v>
+        <v>1229.5371</v>
       </c>
       <c r="Q16">
-        <v>0.002426221112604827</v>
+        <v>0.07101486097794824</v>
       </c>
       <c r="R16">
-        <v>0.01458702178431222</v>
+        <v>0.293655863386673</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2335,55 +2344,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>5421.1</v>
+        <v>9901.6</v>
       </c>
       <c r="V16">
-        <v>0.3470392420459638</v>
+        <v>0.5718906305952478</v>
       </c>
       <c r="W16">
-        <v>0.1581799142801481</v>
+        <v>0.1599080347390371</v>
       </c>
       <c r="X16">
-        <v>0.1392272877373059</v>
+        <v>0.1345736187597076</v>
       </c>
       <c r="Y16">
-        <v>0.01895262654284222</v>
+        <v>0.02533441597932953</v>
       </c>
       <c r="Z16">
-        <v>0.06097181812132906</v>
+        <v>0.05991853972679919</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06197331849613262</v>
+        <v>0.05236105854043498</v>
       </c>
       <c r="AC16">
-        <v>-0.06197331849613262</v>
+        <v>-0.05236105854043498</v>
       </c>
       <c r="AD16">
-        <v>60257.9</v>
+        <v>111058.3</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>60257.9</v>
+        <v>111058.3</v>
       </c>
       <c r="AG16">
-        <v>54836.8</v>
+        <v>101156.7</v>
       </c>
       <c r="AH16">
-        <v>0.7941324926955979</v>
+        <v>0.865128014576376</v>
       </c>
       <c r="AI16">
-        <v>0.7601343211471289</v>
+        <v>0.7618808165818975</v>
       </c>
       <c r="AJ16">
-        <v>0.778292822086412</v>
+        <v>0.853855601183417</v>
       </c>
       <c r="AK16">
-        <v>0.7425269053074002</v>
+        <v>0.7445273686767206</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2400,7 +2409,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bank of Ningbo Co., Ltd. (SZSE:002142)</t>
+          <t>Bank of Suzhou Co., Ltd. (SZSE:002966)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2408,14 +2417,8 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.196</v>
-      </c>
-      <c r="E17">
-        <v>0.205</v>
-      </c>
       <c r="F17">
-        <v>0.153</v>
+        <v>0.13</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2424,34 +2427,34 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0.0002342110310313056</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>0.0002149558711982977</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>3152.8</v>
+        <v>627.8</v>
       </c>
       <c r="L17">
-        <v>0.4819910719745613</v>
+        <v>0.4747787945246918</v>
       </c>
       <c r="M17">
-        <v>462.2520000000001</v>
+        <v>281.3</v>
       </c>
       <c r="N17">
-        <v>0.0148784782013937</v>
+        <v>0.08420895075587487</v>
       </c>
       <c r="O17">
-        <v>0.1466163410301954</v>
+        <v>0.4480726345970055</v>
       </c>
       <c r="P17">
-        <v>462.2520000000001</v>
+        <v>281.3</v>
       </c>
       <c r="Q17">
-        <v>0.0148784782013937</v>
+        <v>0.08420895075587487</v>
       </c>
       <c r="R17">
-        <v>0.1466163410301954</v>
+        <v>0.4480726345970055</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2460,67 +2463,61 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>6733.9</v>
+        <v>1649.9</v>
       </c>
       <c r="V17">
-        <v>0.2167436471023706</v>
+        <v>0.4939080975901811</v>
       </c>
       <c r="W17">
-        <v>0.1727495383738706</v>
+        <v>0.1174599610836701</v>
       </c>
       <c r="X17">
-        <v>0.1314707521894604</v>
+        <v>0.1316960145387727</v>
       </c>
       <c r="Y17">
-        <v>0.04127878618441014</v>
+        <v>-0.01423605345510257</v>
       </c>
       <c r="Z17">
-        <v>0.06198492191635124</v>
+        <v>0.05536713228151275</v>
       </c>
       <c r="AA17">
-        <v>1.332402289168774e-05</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06203448407976375</v>
+        <v>0.0523758186727725</v>
       </c>
       <c r="AC17">
-        <v>-0.06202116005687206</v>
+        <v>-0.0523758186727725</v>
       </c>
       <c r="AD17">
-        <v>107388.9</v>
+        <v>20649.8</v>
       </c>
       <c r="AE17">
-        <v>1.789894019090118</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>107390.6898940191</v>
+        <v>20649.8</v>
       </c>
       <c r="AG17">
-        <v>100656.7898940191</v>
+        <v>18999.9</v>
       </c>
       <c r="AH17">
-        <v>0.7756125828572246</v>
+        <v>0.8607562223065155</v>
       </c>
       <c r="AI17">
-        <v>0.8216523237224976</v>
+        <v>0.7637466481738326</v>
       </c>
       <c r="AJ17">
-        <v>0.7641417223298846</v>
+        <v>0.8504726862544986</v>
       </c>
       <c r="AK17">
-        <v>0.8119644590876315</v>
+        <v>0.7483929162268194</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>56819.52380952381</v>
-      </c>
-      <c r="AP17">
-        <v>53257.5607904863</v>
       </c>
     </row>
     <row r="18">
@@ -2531,7 +2528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bank of Chengdu Co., Ltd. (SHSE:601838)</t>
+          <t>Bank of Xi'an Co.,Ltd. (SHSE:600928)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2539,6 +2536,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.00473</v>
+      </c>
+      <c r="E18">
+        <v>0.0191</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2552,28 +2555,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>1328.6</v>
+        <v>349.6</v>
       </c>
       <c r="L18">
-        <v>0.6022392457277549</v>
+        <v>0.5554496345726089</v>
       </c>
       <c r="M18">
-        <v>413</v>
+        <v>131.8</v>
       </c>
       <c r="N18">
-        <v>0.05053162202836133</v>
+        <v>0.06314679954005367</v>
       </c>
       <c r="O18">
-        <v>0.3108535300316123</v>
+        <v>0.3770022883295195</v>
       </c>
       <c r="P18">
-        <v>413</v>
+        <v>131.8</v>
       </c>
       <c r="Q18">
-        <v>0.05053162202836133</v>
+        <v>0.06314679954005367</v>
       </c>
       <c r="R18">
-        <v>0.3108535300316123</v>
+        <v>0.3770022883295195</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2582,55 +2585,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>8814</v>
+        <v>3123.1</v>
       </c>
       <c r="V18">
-        <v>1.078415778590743</v>
+        <v>1.496310847067842</v>
       </c>
       <c r="W18">
-        <v>0.1728732401696724</v>
+        <v>0.08648327726103305</v>
       </c>
       <c r="X18">
-        <v>0.1301357740433892</v>
+        <v>0.1309992991726956</v>
       </c>
       <c r="Y18">
-        <v>0.04273746612628321</v>
+        <v>-0.04451602191166257</v>
       </c>
       <c r="Z18">
-        <v>0.1054979843433933</v>
+        <v>0.05546498409369299</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.06204613877720083</v>
+        <v>0.05237953736672359</v>
       </c>
       <c r="AC18">
-        <v>-0.06204613877720083</v>
+        <v>-0.05237953736672359</v>
       </c>
       <c r="AD18">
-        <v>27687</v>
+        <v>12784.7</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>27687</v>
+        <v>12784.7</v>
       </c>
       <c r="AG18">
-        <v>18873</v>
+        <v>9661.6</v>
       </c>
       <c r="AH18">
-        <v>0.772083736520534</v>
+        <v>0.8596547851989321</v>
       </c>
       <c r="AI18">
-        <v>0.7728250948341554</v>
+        <v>0.7537570822991161</v>
       </c>
       <c r="AJ18">
-        <v>0.6978085565016768</v>
+        <v>0.8223478142448591</v>
       </c>
       <c r="AK18">
-        <v>0.6986972311998134</v>
+        <v>0.698183289734214</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2647,7 +2650,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bank of Gansu Co., Ltd. (SEHK:2139)</t>
+          <t>Qilu Bank Co., Ltd. (SHSE:601665)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2656,10 +2659,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.144</v>
+        <v>0.112</v>
       </c>
       <c r="E19">
-        <v>-0.291</v>
+        <v>0.139</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2674,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>87</v>
+        <v>547.8</v>
       </c>
       <c r="L19">
-        <v>0.2080841903850753</v>
+        <v>0.5370588235294117</v>
       </c>
       <c r="M19">
-        <v>0.008</v>
+        <v>229.2</v>
       </c>
       <c r="N19">
-        <v>3.942246094712463e-06</v>
+        <v>0.08828627556719695</v>
       </c>
       <c r="O19">
-        <v>9.195402298850575e-05</v>
+        <v>0.4184008762322016</v>
       </c>
       <c r="P19">
-        <v>0.008</v>
+        <v>229.2</v>
       </c>
       <c r="Q19">
-        <v>3.942246094712463e-06</v>
+        <v>0.08828627556719695</v>
       </c>
       <c r="R19">
-        <v>9.195402298850575e-05</v>
+        <v>0.4184008762322016</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2704,55 +2707,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>907.1</v>
+        <v>2320.1</v>
       </c>
       <c r="V19">
-        <v>0.4470014290642094</v>
+        <v>0.8936866838719618</v>
       </c>
       <c r="W19">
-        <v>0.0176642572890441</v>
+        <v>0.115562306183153</v>
       </c>
       <c r="X19">
-        <v>0.1236030879855518</v>
+        <v>0.1241609678964556</v>
       </c>
       <c r="Y19">
-        <v>-0.1059388306965077</v>
+        <v>-0.00859866171330266</v>
       </c>
       <c r="Z19">
-        <v>0.04195137613758367</v>
+        <v>0.05888261577361367</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.06210889746164504</v>
+        <v>0.05241942203252785</v>
       </c>
       <c r="AC19">
-        <v>-0.06210889746164504</v>
+        <v>-0.05241942203252785</v>
       </c>
       <c r="AD19">
-        <v>6189.2</v>
+        <v>14465.7</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>6189.2</v>
+        <v>14465.7</v>
       </c>
       <c r="AG19">
-        <v>5282.099999999999</v>
+        <v>12145.6</v>
       </c>
       <c r="AH19">
-        <v>0.753081462553994</v>
+        <v>0.8478413766425583</v>
       </c>
       <c r="AI19">
-        <v>0.5611394688885464</v>
+        <v>0.7364340295984808</v>
       </c>
       <c r="AJ19">
-        <v>0.7224471373471565</v>
+        <v>0.8238941234728695</v>
       </c>
       <c r="AK19">
-        <v>0.5218125777962184</v>
+        <v>0.7011337659038955</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2769,7 +2772,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jiangsu Zijin Rural Commercial Bank Co.,Ltd (SHSE:601860)</t>
+          <t>Bank of Ningbo Co., Ltd. (SZSE:002142)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2778,10 +2781,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.08400000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="E20">
-        <v>0.09359999999999999</v>
+        <v>0.183</v>
+      </c>
+      <c r="F20">
+        <v>0.108</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2790,34 +2796,34 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3.314776131001377e-05</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3.057867981208257e-05</v>
       </c>
       <c r="K20">
-        <v>225.1</v>
+        <v>3458.2</v>
       </c>
       <c r="L20">
-        <v>0.4254394254394254</v>
+        <v>0.4879914204272853</v>
       </c>
       <c r="M20">
-        <v>71.5</v>
+        <v>455.6484</v>
       </c>
       <c r="N20">
-        <v>0.05201134793045755</v>
+        <v>0.02432979495941905</v>
       </c>
       <c r="O20">
-        <v>0.3176366059529098</v>
+        <v>0.1317588340755306</v>
       </c>
       <c r="P20">
-        <v>71.5</v>
+        <v>455.6484</v>
       </c>
       <c r="Q20">
-        <v>0.05201134793045755</v>
+        <v>0.02432979495941905</v>
       </c>
       <c r="R20">
-        <v>0.3176366059529098</v>
+        <v>0.1317588340755306</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2826,61 +2832,67 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>1554.4</v>
+        <v>7825.4</v>
       </c>
       <c r="V20">
-        <v>1.130719429693751</v>
+        <v>0.4178449380606578</v>
       </c>
       <c r="W20">
-        <v>0.09178015167577265</v>
+        <v>0.1638514714034597</v>
       </c>
       <c r="X20">
-        <v>0.1148630134953368</v>
+        <v>0.1235098236631012</v>
       </c>
       <c r="Y20">
-        <v>-0.02308286181956411</v>
+        <v>0.04034164774035852</v>
       </c>
       <c r="Z20">
-        <v>0.07638558043512785</v>
+        <v>0.05724164411440848</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.750373907291678e-06</v>
       </c>
       <c r="AB20">
-        <v>0.06221128345788374</v>
+        <v>0.05242357278547723</v>
       </c>
       <c r="AC20">
-        <v>-0.06221128345788374</v>
+        <v>-0.05242182241156994</v>
       </c>
       <c r="AD20">
-        <v>3571.7</v>
+        <v>103367.3</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>0.2754753735022819</v>
       </c>
       <c r="AF20">
-        <v>3571.7</v>
+        <v>103367.5754753735</v>
       </c>
       <c r="AG20">
-        <v>2017.3</v>
+        <v>95542.17547537351</v>
       </c>
       <c r="AH20">
-        <v>0.7220807051593078</v>
+        <v>0.8466119683118459</v>
       </c>
       <c r="AI20">
-        <v>0.5999529672618548</v>
+        <v>0.7934946428886521</v>
       </c>
       <c r="AJ20">
-        <v>0.5947228773584905</v>
+        <v>0.8361077164527844</v>
       </c>
       <c r="AK20">
-        <v>0.4585919207074496</v>
+        <v>0.7802968115215795</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>356438.9655172414</v>
+      </c>
+      <c r="AP20">
+        <v>329455.777501288</v>
       </c>
     </row>
     <row r="21">
@@ -2891,7 +2903,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jiangsu Zhangjiagang Rural Commercial Bank Co., Ltd (SZSE:002839)</t>
+          <t>Jinshang Bank Co., Ltd. (SEHK:2558)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2899,12 +2911,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.144</v>
-      </c>
-      <c r="E21">
-        <v>0.169</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2918,28 +2924,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>224.5</v>
+        <v>262</v>
       </c>
       <c r="L21">
-        <v>0.5199166280685502</v>
+        <v>0.4564459930313589</v>
       </c>
       <c r="M21">
-        <v>85.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N21">
-        <v>0.05868156116397737</v>
+        <v>0.07793643482266237</v>
       </c>
       <c r="O21">
-        <v>0.3790645879732739</v>
+        <v>0.3229007633587786</v>
       </c>
       <c r="P21">
-        <v>85.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q21">
-        <v>0.05868156116397737</v>
+        <v>0.07793643482266237</v>
       </c>
       <c r="R21">
-        <v>0.3790645879732739</v>
+        <v>0.3229007633587786</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2948,55 +2954,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>483.7</v>
+        <v>563.8</v>
       </c>
       <c r="V21">
-        <v>0.3335402013515377</v>
+        <v>0.5193919852602487</v>
       </c>
       <c r="W21">
-        <v>0.1031804393786193</v>
+        <v>0.07786032689450223</v>
       </c>
       <c r="X21">
-        <v>0.1148235029009465</v>
+        <v>0.1236598768384226</v>
       </c>
       <c r="Y21">
-        <v>-0.0116430635223272</v>
+        <v>-0.04579954994392041</v>
       </c>
       <c r="Z21">
-        <v>0.08361735089078234</v>
+        <v>0.05531517119756381</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06221180471326795</v>
+        <v>0.05242261032722891</v>
       </c>
       <c r="AC21">
-        <v>-0.06221180471326795</v>
+        <v>-0.05242261032722891</v>
       </c>
       <c r="AD21">
-        <v>3764.9</v>
+        <v>6004.5</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>3764.9</v>
+        <v>6004.5</v>
       </c>
       <c r="AG21">
-        <v>3281.2</v>
+        <v>5440.7</v>
       </c>
       <c r="AH21">
-        <v>0.7219228777971659</v>
+        <v>0.8468970380818054</v>
       </c>
       <c r="AI21">
-        <v>0.6317794334810041</v>
+        <v>0.6460063691526445</v>
       </c>
       <c r="AJ21">
-        <v>0.6934945259331275</v>
+        <v>0.8336704360883822</v>
       </c>
       <c r="AK21">
-        <v>0.5992512099351658</v>
+        <v>0.6231474057954415</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3013,7 +3019,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jiangsu Suzhou Rural Commercial Bank Co., Ltd (SHSE:603323)</t>
+          <t>Weihai City Commercial Bank Co., Ltd. (SEHK:9677)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3021,12 +3027,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.08990000000000001</v>
-      </c>
-      <c r="E22">
-        <v>0.142</v>
-      </c>
       <c r="G22">
         <v>0</v>
       </c>
@@ -3040,28 +3040,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>193.2</v>
+        <v>270.5</v>
       </c>
       <c r="L22">
-        <v>0.5214574898785425</v>
+        <v>0.4675077773937089</v>
       </c>
       <c r="M22">
-        <v>82.8</v>
+        <v>223.3</v>
       </c>
       <c r="N22">
-        <v>0.06753119647663323</v>
+        <v>0.1034418863204707</v>
       </c>
       <c r="O22">
-        <v>0.4285714285714286</v>
+        <v>0.8255083179297598</v>
       </c>
       <c r="P22">
-        <v>82.8</v>
+        <v>223.3</v>
       </c>
       <c r="Q22">
-        <v>0.06753119647663323</v>
+        <v>0.1034418863204707</v>
       </c>
       <c r="R22">
-        <v>0.4285714285714286</v>
+        <v>0.8255083179297598</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3070,55 +3070,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>631.6</v>
+        <v>1206.8</v>
       </c>
       <c r="V22">
-        <v>0.5151292716744149</v>
+        <v>0.5590401630611016</v>
       </c>
       <c r="W22">
-        <v>0.09549228944246738</v>
+        <v>0.0770304134867297</v>
       </c>
       <c r="X22">
-        <v>0.1127247147659523</v>
+        <v>0.1169860507756987</v>
       </c>
       <c r="Y22">
-        <v>-0.01723242532348492</v>
+        <v>-0.03995563728896902</v>
       </c>
       <c r="Z22">
-        <v>0.09436365025596617</v>
+        <v>0.04720760412842165</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06224037106473297</v>
+        <v>0.05246918746930964</v>
       </c>
       <c r="AC22">
-        <v>-0.06224037106473297</v>
+        <v>-0.05246918746930964</v>
       </c>
       <c r="AD22">
-        <v>3050.1</v>
+        <v>10775.5</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>3050.1</v>
+        <v>10775.5</v>
       </c>
       <c r="AG22">
-        <v>2418.5</v>
+        <v>9568.700000000001</v>
       </c>
       <c r="AH22">
-        <v>0.7132734670969553</v>
+        <v>0.8331013901130336</v>
       </c>
       <c r="AI22">
-        <v>0.5991631634777825</v>
+        <v>0.7422216711783385</v>
       </c>
       <c r="AJ22">
-        <v>0.6635844811501949</v>
+        <v>0.8159268038951515</v>
       </c>
       <c r="AK22">
-        <v>0.542386185243328</v>
+        <v>0.7188511843499035</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jiangsu Jiangyin Rural Commercial Bank Co.,LTD. (SZSE:002807)</t>
+          <t>Bank of Chengdu Co., Ltd. (SHSE:601838)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3144,10 +3144,13 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.104</v>
+        <v>0.201</v>
       </c>
       <c r="E23">
-        <v>0.131</v>
+        <v>0.206</v>
+      </c>
+      <c r="F23">
+        <v>0.118</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3162,28 +3165,28 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>202.6</v>
+        <v>1568.9</v>
       </c>
       <c r="L23">
-        <v>0.5337197049525816</v>
+        <v>0.5906558241096304</v>
       </c>
       <c r="M23">
-        <v>67.5</v>
+        <v>469.1</v>
       </c>
       <c r="N23">
-        <v>0.05399136138217885</v>
+        <v>0.07745653286660172</v>
       </c>
       <c r="O23">
-        <v>0.3331688055281343</v>
+        <v>0.298999298871821</v>
       </c>
       <c r="P23">
-        <v>67.5</v>
+        <v>469.1</v>
       </c>
       <c r="Q23">
-        <v>0.05399136138217885</v>
+        <v>0.07745653286660172</v>
       </c>
       <c r="R23">
-        <v>0.3331688055281343</v>
+        <v>0.298999298871821</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3192,55 +3195,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>585.5</v>
+        <v>9517.9</v>
       </c>
       <c r="V23">
-        <v>0.4683250679891217</v>
+        <v>1.571570100556445</v>
       </c>
       <c r="W23">
-        <v>0.1048165968234259</v>
+        <v>0.1930478651408884</v>
       </c>
       <c r="X23">
-        <v>0.1094245982048211</v>
+        <v>0.1161979858321359</v>
       </c>
       <c r="Y23">
-        <v>-0.004608001381395138</v>
+        <v>0.07684987930875245</v>
       </c>
       <c r="Z23">
-        <v>0.08170469220835126</v>
+        <v>0.09837777777777777</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.06228906732986537</v>
+        <v>0.05247524749945318</v>
       </c>
       <c r="AC23">
-        <v>-0.06228906732986537</v>
+        <v>-0.05247524749945318</v>
       </c>
       <c r="AD23">
-        <v>2896.8</v>
+        <v>29844.9</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>2896.8</v>
+        <v>29844.9</v>
       </c>
       <c r="AG23">
-        <v>2311.3</v>
+        <v>20327</v>
       </c>
       <c r="AH23">
-        <v>0.6985290571497469</v>
+        <v>0.8313064744353948</v>
       </c>
       <c r="AI23">
-        <v>0.5999378689033862</v>
+        <v>0.7623140504311579</v>
       </c>
       <c r="AJ23">
-        <v>0.6489681314053068</v>
+        <v>0.7704494888812241</v>
       </c>
       <c r="AK23">
-        <v>0.5447325005892057</v>
+        <v>0.685969796675947</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3257,7 +3260,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shengjing Bank Co., Ltd. (SEHK:2066)</t>
+          <t>Bank of Jiujiang Co., Ltd. (SEHK:6190)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3266,10 +3269,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.12</v>
+        <v>0.0331</v>
       </c>
       <c r="E24">
-        <v>-0.458</v>
+        <v>-0.0412</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3284,82 +3287,85 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>47.1</v>
+        <v>215.5</v>
       </c>
       <c r="L24">
-        <v>0.05120121752364388</v>
+        <v>0.2860366339262012</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>42.711</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.01674612821015487</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>0.1981948955916473</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>42.711</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.01674612821015487</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0.1981948955916473</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
       <c r="U24">
-        <v>5025.5</v>
+        <v>4011.7</v>
       </c>
       <c r="V24">
-        <v>0.7372119291760184</v>
+        <v>1.572907273083709</v>
       </c>
       <c r="W24">
-        <v>0.00377909542416535</v>
+        <v>0.04233874928780527</v>
       </c>
       <c r="X24">
-        <v>0.1082577699398754</v>
+        <v>0.101701421123581</v>
       </c>
       <c r="Y24">
-        <v>-0.1044786745157101</v>
+        <v>-0.05936267183577578</v>
       </c>
       <c r="Z24">
-        <v>0.03763234114971118</v>
+        <v>0.0820688227797083</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.06230750558489676</v>
+        <v>0.05261570913252848</v>
       </c>
       <c r="AC24">
-        <v>-0.06230750558489676</v>
+        <v>-0.05261570913252848</v>
       </c>
       <c r="AD24">
-        <v>15384.1</v>
+        <v>9577.6</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>15384.1</v>
+        <v>9577.6</v>
       </c>
       <c r="AG24">
-        <v>10358.6</v>
+        <v>5565.900000000001</v>
       </c>
       <c r="AH24">
-        <v>0.6929462636818161</v>
+        <v>0.7897032511275468</v>
       </c>
       <c r="AI24">
-        <v>0.5582606360588158</v>
+        <v>0.6218938100216224</v>
       </c>
       <c r="AJ24">
-        <v>0.6031032575470875</v>
+        <v>0.6857596964171307</v>
       </c>
       <c r="AK24">
-        <v>0.4597345073829316</v>
+        <v>0.4887084028448503</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3376,7 +3382,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dongguan Rural Commercial Bank Co., Ltd. (SEHK:9889)</t>
+          <t>Jiangsu Suzhou Rural Commercial Bank Co., Ltd (SHSE:603323)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3385,10 +3391,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.08130000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="E25">
-        <v>0.0776</v>
+        <v>0.154</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3403,28 +3409,28 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>893.8</v>
+        <v>232.9</v>
       </c>
       <c r="L25">
-        <v>0.5406811445163632</v>
+        <v>0.524785939612438</v>
       </c>
       <c r="M25">
-        <v>306.4</v>
+        <v>69.7</v>
       </c>
       <c r="N25">
-        <v>0.04816928422078637</v>
+        <v>0.06589147286821706</v>
       </c>
       <c r="O25">
-        <v>0.3428059968673081</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="P25">
-        <v>306.4</v>
+        <v>69.7</v>
       </c>
       <c r="Q25">
-        <v>0.04816928422078637</v>
+        <v>0.06589147286821706</v>
       </c>
       <c r="R25">
-        <v>0.3428059968673081</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3433,55 +3439,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>3798.8</v>
+        <v>567.3</v>
       </c>
       <c r="V25">
-        <v>0.5972110864814728</v>
+        <v>0.5363017583664208</v>
       </c>
       <c r="W25">
-        <v>0.1527158405522238</v>
+        <v>0.1151317415591478</v>
       </c>
       <c r="X25">
-        <v>0.1049320716607749</v>
+        <v>0.09547004237531859</v>
       </c>
       <c r="Y25">
-        <v>0.04778376889144886</v>
+        <v>0.01966169918382916</v>
       </c>
       <c r="Z25">
-        <v>0.09689520359656989</v>
+        <v>0.0999234475615797</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.06236401417785729</v>
+        <v>0.05269990258901634</v>
       </c>
       <c r="AC25">
-        <v>-0.06236401417785729</v>
+        <v>-0.05269990258901634</v>
       </c>
       <c r="AD25">
-        <v>13261.6</v>
+        <v>3439</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>13261.6</v>
+        <v>3439</v>
       </c>
       <c r="AG25">
-        <v>9462.799999999999</v>
+        <v>2871.7</v>
       </c>
       <c r="AH25">
-        <v>0.6758364122818193</v>
+        <v>0.7647660558619462</v>
       </c>
       <c r="AI25">
-        <v>0.6329061970553845</v>
+        <v>0.6173371389591973</v>
       </c>
       <c r="AJ25">
-        <v>0.5980143708487901</v>
+        <v>0.7308054459854942</v>
       </c>
       <c r="AK25">
-        <v>0.551615592228369</v>
+        <v>0.5739497141943478</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3498,7 +3504,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wuxi Rural Commercial Bank Co.,Ltd (SHSE:600908)</t>
+          <t>Jiangsu Zhangjiagang Rural Commercial Bank Co., Ltd (SZSE:002839)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3507,10 +3513,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.104</v>
+        <v>0.145</v>
       </c>
       <c r="E26">
-        <v>0.136</v>
+        <v>0.168</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3525,28 +3531,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>256.9</v>
+        <v>246.3</v>
       </c>
       <c r="L26">
-        <v>0.547994880546075</v>
+        <v>0.5040933278755628</v>
       </c>
       <c r="M26">
-        <v>112</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N26">
-        <v>0.07873462214411248</v>
+        <v>0.08389487870619945</v>
       </c>
       <c r="O26">
-        <v>0.4359673024523161</v>
+        <v>0.4043848964677222</v>
       </c>
       <c r="P26">
-        <v>112</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>0.07873462214411248</v>
+        <v>0.08389487870619945</v>
       </c>
       <c r="R26">
-        <v>0.4359673024523161</v>
+        <v>0.4043848964677222</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3555,55 +3561,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>1495.4</v>
+        <v>356.5</v>
       </c>
       <c r="V26">
-        <v>1.051247803163445</v>
+        <v>0.3002863881401617</v>
       </c>
       <c r="W26">
-        <v>0.1072651356993737</v>
+        <v>0.1109059798270893</v>
       </c>
       <c r="X26">
-        <v>0.1025870776338148</v>
+        <v>0.08646561283865359</v>
       </c>
       <c r="Y26">
-        <v>0.004678058065558863</v>
+        <v>0.02444036698843574</v>
       </c>
       <c r="Z26">
-        <v>0.1153401402386517</v>
+        <v>0.09293390394674275</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06240779977510787</v>
+        <v>0.05286413062932256</v>
       </c>
       <c r="AC26">
-        <v>-0.06240779977510787</v>
+        <v>-0.05286413062932256</v>
       </c>
       <c r="AD26">
-        <v>2793.3</v>
+        <v>2994.9</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>2793.3</v>
+        <v>2994.9</v>
       </c>
       <c r="AG26">
-        <v>1297.9</v>
+        <v>2638.4</v>
       </c>
       <c r="AH26">
-        <v>0.6625788699653684</v>
+        <v>0.7161234786351354</v>
       </c>
       <c r="AI26">
-        <v>0.5388102310867636</v>
+        <v>0.5709900669196011</v>
       </c>
       <c r="AJ26">
-        <v>0.4770989560358771</v>
+        <v>0.6896695943120033</v>
       </c>
       <c r="AK26">
-        <v>0.3518488397310779</v>
+        <v>0.5397046189092992</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3620,7 +3626,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jiangsu Changshu Rural Commercial Bank Co., Ltd. (SHSE:601128)</t>
+          <t>Jiangsu Zijin Rural Commercial Bank Co.,Ltd (SHSE:601860)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3629,10 +3635,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.151</v>
+        <v>0.0525</v>
       </c>
       <c r="E27">
-        <v>0.176</v>
+        <v>0.0565</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3647,28 +3653,28 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>366.4</v>
+        <v>229.4</v>
       </c>
       <c r="L27">
-        <v>0.3845507976490344</v>
+        <v>0.4469121371517631</v>
       </c>
       <c r="M27">
-        <v>135.2</v>
+        <v>76.8</v>
       </c>
       <c r="N27">
-        <v>0.0450621604506216</v>
+        <v>0.05879650895728065</v>
       </c>
       <c r="O27">
-        <v>0.3689956331877729</v>
+        <v>0.3347863993025283</v>
       </c>
       <c r="P27">
-        <v>135.2</v>
+        <v>76.8</v>
       </c>
       <c r="Q27">
-        <v>0.0450621604506216</v>
+        <v>0.05879650895728065</v>
       </c>
       <c r="R27">
-        <v>0.3689956331877729</v>
+        <v>0.3347863993025283</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3677,55 +3683,55 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>1476.9</v>
+        <v>1594.3</v>
       </c>
       <c r="V27">
-        <v>0.4922507749225077</v>
+        <v>1.220563466544174</v>
       </c>
       <c r="W27">
-        <v>0.1228746772192226</v>
+        <v>0.0963218004702721</v>
       </c>
       <c r="X27">
-        <v>0.1013911889956824</v>
+        <v>0.08589593473073681</v>
       </c>
       <c r="Y27">
-        <v>0.02148348822354021</v>
+        <v>0.01042586573953529</v>
       </c>
       <c r="Z27">
-        <v>0.1302012872545402</v>
+        <v>0.1166882629748346</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.06243153766507768</v>
+        <v>0.05287683547108726</v>
       </c>
       <c r="AC27">
-        <v>-0.06243153766507768</v>
+        <v>-0.05287683547108726</v>
       </c>
       <c r="AD27">
-        <v>5706.1</v>
+        <v>3234.9</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>5706.1</v>
+        <v>3234.9</v>
       </c>
       <c r="AG27">
-        <v>4229.200000000001</v>
+        <v>1640.6</v>
       </c>
       <c r="AH27">
-        <v>0.6553914361848754</v>
+        <v>0.712360441302768</v>
       </c>
       <c r="AI27">
-        <v>0.6315900160495878</v>
+        <v>0.5651171322257743</v>
       </c>
       <c r="AJ27">
-        <v>0.5849920464762431</v>
+        <v>0.556739514049138</v>
       </c>
       <c r="AK27">
-        <v>0.5595956388271409</v>
+        <v>0.3972397094430993</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3742,7 +3748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Luzhou Bank Co., Ltd. (SEHK:1983)</t>
+          <t>Jiangsu Changshu Rural Commercial Bank Co., Ltd. (SHSE:601128)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3751,10 +3757,13 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.133</v>
+        <v>0.135</v>
       </c>
       <c r="E28">
-        <v>0.0604</v>
+        <v>0.164</v>
+      </c>
+      <c r="F28">
+        <v>0.173</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3769,82 +3778,85 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>137.2</v>
+        <v>436.2</v>
       </c>
       <c r="L28">
-        <v>0.357198646185889</v>
+        <v>0.4117424957523126</v>
       </c>
       <c r="M28">
-        <v>-0</v>
+        <v>145.2</v>
       </c>
       <c r="N28">
-        <v>-0</v>
+        <v>0.05878542510121457</v>
       </c>
       <c r="O28">
-        <v>-0</v>
+        <v>0.3328748280605227</v>
       </c>
       <c r="P28">
-        <v>-0</v>
+        <v>145.2</v>
       </c>
       <c r="Q28">
-        <v>-0</v>
+        <v>0.05878542510121457</v>
       </c>
       <c r="R28">
-        <v>-0</v>
+        <v>0.3328748280605227</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
       <c r="U28">
-        <v>1524.8</v>
+        <v>1711.7</v>
       </c>
       <c r="V28">
-        <v>1.411198519204072</v>
+        <v>0.6929959514170041</v>
       </c>
       <c r="W28">
-        <v>0.09113251411491198</v>
+        <v>0.13988391110541</v>
       </c>
       <c r="X28">
-        <v>0.123960536163848</v>
+        <v>0.08581467969293954</v>
       </c>
       <c r="Y28">
-        <v>-0.03282802204893599</v>
+        <v>0.05406923141247044</v>
       </c>
       <c r="Z28">
-        <v>0.07530634251543966</v>
+        <v>0.1441850969717591</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.06646071514810008</v>
+        <v>0.05287867510360314</v>
       </c>
       <c r="AC28">
-        <v>-0.06646071514810008</v>
+        <v>-0.05287867510360314</v>
       </c>
       <c r="AD28">
-        <v>3315.4</v>
+        <v>6100.9</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>3315.4</v>
+        <v>6100.9</v>
       </c>
       <c r="AG28">
-        <v>1790.6</v>
+        <v>4389.2</v>
       </c>
       <c r="AH28">
-        <v>0.7542027798630543</v>
+        <v>0.7118155619596541</v>
       </c>
       <c r="AI28">
-        <v>0.6881135717398974</v>
+        <v>0.629101445688713</v>
       </c>
       <c r="AJ28">
-        <v>0.6236634042701403</v>
+        <v>0.6398996967576394</v>
       </c>
       <c r="AK28">
-        <v>0.5437099565785078</v>
+        <v>0.5496049385807841</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3861,7 +3873,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>QILU BANK CO., LTD. (SHSE:601665)</t>
+          <t>Jiangsu Jiangyin Rural Commercial Bank Co.,LTD. (SZSE:002807)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3870,10 +3882,10 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.105</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E29">
-        <v>0.125</v>
+        <v>0.16</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3888,28 +3900,28 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>485.7</v>
+        <v>240.5</v>
       </c>
       <c r="L29">
-        <v>0.5162627551020408</v>
+        <v>0.6180930352094577</v>
       </c>
       <c r="M29">
-        <v>31.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N29">
-        <v>0.01126557140278029</v>
+        <v>0.0615228986573478</v>
       </c>
       <c r="O29">
-        <v>0.06423718344657196</v>
+        <v>0.2781704781704782</v>
       </c>
       <c r="P29">
-        <v>31.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>0.01126557140278029</v>
+        <v>0.0615228986573478</v>
       </c>
       <c r="R29">
-        <v>0.06423718344657196</v>
+        <v>0.2781704781704782</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3918,55 +3930,55 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1917.9</v>
+        <v>302.8</v>
       </c>
       <c r="V29">
-        <v>0.6925076728651381</v>
+        <v>0.2784623873459628</v>
       </c>
       <c r="W29">
-        <v>0.09994855437802243</v>
+        <v>0.1257845188284519</v>
       </c>
       <c r="X29">
-        <v>0.1658910570492752</v>
+        <v>0.08438484955132572</v>
       </c>
       <c r="Y29">
-        <v>-0.0659425026712528</v>
+        <v>0.04139966927712616</v>
       </c>
       <c r="Z29">
-        <v>0.05687685146000846</v>
+        <v>0.09213174531764261</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.06667192341238404</v>
+        <v>0.05291222650330735</v>
       </c>
       <c r="AC29">
-        <v>-0.06667192341238404</v>
+        <v>-0.05291222650330735</v>
       </c>
       <c r="AD29">
-        <v>14500.2</v>
+        <v>2560.1</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>14500.2</v>
+        <v>2560.1</v>
       </c>
       <c r="AG29">
-        <v>12582.3</v>
+        <v>2257.3</v>
       </c>
       <c r="AH29">
-        <v>0.8396324197872574</v>
+        <v>0.7018779986291981</v>
       </c>
       <c r="AI29">
-        <v>0.7521201715847733</v>
+        <v>0.5516981294715974</v>
       </c>
       <c r="AJ29">
-        <v>0.8195977018981487</v>
+        <v>0.6748886297724758</v>
       </c>
       <c r="AK29">
-        <v>0.724736769347741</v>
+        <v>0.5204029878273698</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -3983,7 +3995,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank of Qingdao Co., Ltd. (SEHK:3866)</t>
+          <t>Wuxi Rural Commercial Bank Co.,Ltd (SHSE:600908)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3992,10 +4004,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="E30">
-        <v>0.09140000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4010,85 +4022,85 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>435.6</v>
+        <v>306.2</v>
       </c>
       <c r="L30">
-        <v>0.4052469997209043</v>
+        <v>0.5757803685596089</v>
       </c>
       <c r="M30">
-        <v>1301.5488</v>
+        <v>114.9</v>
       </c>
       <c r="N30">
-        <v>0.4932164159308803</v>
+        <v>0.075</v>
       </c>
       <c r="O30">
-        <v>2.987944903581267</v>
+        <v>0.3752449379490529</v>
       </c>
       <c r="P30">
-        <v>128.0488</v>
+        <v>114.9</v>
       </c>
       <c r="Q30">
-        <v>0.04852355147978323</v>
+        <v>0.075</v>
       </c>
       <c r="R30">
-        <v>0.2939595959595959</v>
+        <v>0.3752449379490529</v>
       </c>
       <c r="S30">
-        <v>1173.5</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>0.9016181337188433</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2059.2</v>
+        <v>1056.9</v>
       </c>
       <c r="V30">
-        <v>0.7803251354731137</v>
+        <v>0.6898825065274152</v>
       </c>
       <c r="W30">
-        <v>0.1159651785001198</v>
+        <v>0.1291002614048402</v>
       </c>
       <c r="X30">
-        <v>0.2098145978569709</v>
+        <v>0.0713106429926343</v>
       </c>
       <c r="Y30">
-        <v>-0.09384941935685114</v>
+        <v>0.05778961841220588</v>
       </c>
       <c r="Z30">
-        <v>0.04147822865698366</v>
+        <v>0.1449164781862277</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.06677774572810634</v>
+        <v>0.05337575049907988</v>
       </c>
       <c r="AC30">
-        <v>-0.06677774572810634</v>
+        <v>-0.05337575049907988</v>
       </c>
       <c r="AD30">
-        <v>19807.5</v>
+        <v>1986.5</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>19807.5</v>
+        <v>1986.5</v>
       </c>
       <c r="AG30">
-        <v>17748.3</v>
+        <v>929.5999999999999</v>
       </c>
       <c r="AH30">
-        <v>0.8824354907691211</v>
+        <v>0.5645871820378002</v>
       </c>
       <c r="AI30">
-        <v>0.7921447396310323</v>
+        <v>0.4105271859306868</v>
       </c>
       <c r="AJ30">
-        <v>0.8705609401977711</v>
+        <v>0.3776405589860253</v>
       </c>
       <c r="AK30">
-        <v>0.7734913295301517</v>
+        <v>0.2457958751983078</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -4120,34 +4132,34 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>0.000593627772757879</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>0.000593627772757879</v>
       </c>
       <c r="K31">
-        <v>245.6</v>
+        <v>256</v>
       </c>
       <c r="L31">
-        <v>0.4003259983700082</v>
+        <v>0.4105195638229634</v>
       </c>
       <c r="M31">
-        <v>66</v>
+        <v>127.7</v>
       </c>
       <c r="N31">
-        <v>0.02119937044293836</v>
+        <v>0.06114728979122773</v>
       </c>
       <c r="O31">
-        <v>0.2687296416938111</v>
+        <v>0.498828125</v>
       </c>
       <c r="P31">
-        <v>66</v>
+        <v>127.7</v>
       </c>
       <c r="Q31">
-        <v>0.02119937044293836</v>
+        <v>0.06114728979122773</v>
       </c>
       <c r="R31">
-        <v>0.2687296416938111</v>
+        <v>0.498828125</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -4156,61 +4168,67 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>544.8</v>
+        <v>2924</v>
       </c>
       <c r="V31">
-        <v>0.1749911669289821</v>
+        <v>1.400114920513312</v>
       </c>
       <c r="W31">
-        <v>0.05680845650313417</v>
+        <v>0.05551218665972764</v>
       </c>
       <c r="X31">
-        <v>0.1273073758869652</v>
+        <v>0.104898148517786</v>
       </c>
       <c r="Y31">
-        <v>-0.07049891938383104</v>
+        <v>-0.04938596185805841</v>
       </c>
       <c r="Z31">
-        <v>0.06594646888100611</v>
+        <v>0.04402276257660222</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.613313449899728e-05</v>
       </c>
       <c r="AB31">
-        <v>0.06866354977306099</v>
+        <v>0.05606868565450166</v>
       </c>
       <c r="AC31">
-        <v>-0.06866354977306099</v>
+        <v>-0.05604255252000266</v>
       </c>
       <c r="AD31">
-        <v>10091.4</v>
+        <v>8375.200000000001</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>7.199068604540933</v>
       </c>
       <c r="AF31">
-        <v>10091.4</v>
+        <v>8382.399068604542</v>
       </c>
       <c r="AG31">
-        <v>9546.6</v>
+        <v>5458.399068604542</v>
       </c>
       <c r="AH31">
-        <v>0.7642278885548327</v>
+        <v>0.8005500834924986</v>
       </c>
       <c r="AI31">
-        <v>0.6841580735045865</v>
+        <v>0.6498991838980996</v>
       </c>
       <c r="AJ31">
-        <v>0.7540817857960963</v>
+        <v>0.7232734062461054</v>
       </c>
       <c r="AK31">
-        <v>0.6720449409727356</v>
+        <v>0.5472628412194371</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
         <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>4627.182320441989</v>
+      </c>
+      <c r="AP31">
+        <v>3015.69009315168</v>
       </c>
     </row>
     <row r="32">
@@ -4221,7 +4239,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guangzhou Rural Commercial Bank Co., Ltd. (SEHK:1551)</t>
+          <t>Jiangxi Bank Co., Ltd. (SEHK:1916)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4230,10 +4248,10 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.05860000000000001</v>
+        <v>-0.0717</v>
       </c>
       <c r="E32">
-        <v>-0.141</v>
+        <v>-0.15</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4242,34 +4260,34 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0.0001318095906527036</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>0.0001279966865312043</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>383.9</v>
+        <v>202.7</v>
       </c>
       <c r="L32">
-        <v>0.2735304595653723</v>
+        <v>0.2845711076793486</v>
       </c>
       <c r="M32">
-        <v>292.8</v>
+        <v>41.6</v>
       </c>
       <c r="N32">
-        <v>0.07548726410229968</v>
+        <v>0.07492795389048991</v>
       </c>
       <c r="O32">
-        <v>0.7626986194321439</v>
+        <v>0.2052294030587075</v>
       </c>
       <c r="P32">
-        <v>292.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q32">
-        <v>0.07548726410229968</v>
+        <v>0.07492795389048991</v>
       </c>
       <c r="R32">
-        <v>0.7626986194321439</v>
+        <v>0.2052294030587075</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -4278,67 +4296,61 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>6548.9</v>
+        <v>1686.4</v>
       </c>
       <c r="V32">
-        <v>1.688383005053109</v>
+        <v>3.037463976945245</v>
       </c>
       <c r="W32">
-        <v>0.04102240791596765</v>
+        <v>0.03197160883280757</v>
       </c>
       <c r="X32">
-        <v>0.2198081062618941</v>
+        <v>0.3698930566842843</v>
       </c>
       <c r="Y32">
-        <v>-0.1787856983459264</v>
+        <v>-0.3379214478514768</v>
       </c>
       <c r="Z32">
-        <v>0.06221022483312686</v>
+        <v>0.03637758327826221</v>
       </c>
       <c r="AA32">
-        <v>7.962702647001483e-06</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.06932850902755268</v>
+        <v>0.0562275463225498</v>
       </c>
       <c r="AC32">
-        <v>-0.06932054632490568</v>
+        <v>-0.0562275463225498</v>
       </c>
       <c r="AD32">
-        <v>31116.1</v>
+        <v>14130.4</v>
       </c>
       <c r="AE32">
-        <v>1.600026197594653</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>31117.70002619759</v>
+        <v>14130.4</v>
       </c>
       <c r="AG32">
-        <v>24568.80002619759</v>
+        <v>12444</v>
       </c>
       <c r="AH32">
-        <v>0.8891660595460569</v>
+        <v>0.9621942583210764</v>
       </c>
       <c r="AI32">
-        <v>0.7042753034525455</v>
+        <v>0.681324615711007</v>
       </c>
       <c r="AJ32">
-        <v>0.8636510638356844</v>
+        <v>0.957289679364884</v>
       </c>
       <c r="AK32">
-        <v>0.6528161213626478</v>
+        <v>0.6531186362395818</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
         <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>61616.03960396039</v>
-      </c>
-      <c r="AP32">
-        <v>48651.08916078731</v>
       </c>
     </row>
     <row r="33">
@@ -4349,7 +4361,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Huishang Bank Corporation Limited (SEHK:3698)</t>
+          <t>Dongguan Rural Commercial Bank Co., Ltd. (SEHK:9889)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4358,10 +4370,10 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.102</v>
+        <v>0.0721</v>
       </c>
       <c r="E33">
-        <v>0.115</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4376,28 +4388,28 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>1867.1</v>
+        <v>823.8</v>
       </c>
       <c r="L33">
-        <v>0.5225727000475804</v>
+        <v>0.5420093427199157</v>
       </c>
       <c r="M33">
-        <v>180.5674</v>
+        <v>283.5</v>
       </c>
       <c r="N33">
-        <v>0.04087269681742043</v>
+        <v>0.04592803797365821</v>
       </c>
       <c r="O33">
-        <v>0.09671008515880242</v>
+        <v>0.3441369264384559</v>
       </c>
       <c r="P33">
-        <v>180.5674</v>
+        <v>283.5</v>
       </c>
       <c r="Q33">
-        <v>0.04087269681742043</v>
+        <v>0.04592803797365821</v>
       </c>
       <c r="R33">
-        <v>0.09671008515880242</v>
+        <v>0.3441369264384559</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4406,55 +4418,55 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>5410.1</v>
+        <v>3124.6</v>
       </c>
       <c r="V33">
-        <v>1.224614061297479</v>
+        <v>0.5061966400440649</v>
       </c>
       <c r="W33">
-        <v>0.1165117004680187</v>
+        <v>0.1129282101193985</v>
       </c>
       <c r="X33">
-        <v>0.3164863926176956</v>
+        <v>0.08828334514408659</v>
       </c>
       <c r="Y33">
-        <v>-0.1999746921496768</v>
+        <v>0.02464486497531189</v>
       </c>
       <c r="Z33">
-        <v>0.06153467256368922</v>
+        <v>0.091121103117506</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.06953876681280302</v>
+        <v>0.05745316266310514</v>
       </c>
       <c r="AC33">
-        <v>-0.06953876681280302</v>
+        <v>-0.05745316266310514</v>
       </c>
       <c r="AD33">
-        <v>57517.8</v>
+        <v>16479.3</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>57517.8</v>
+        <v>16479.3</v>
       </c>
       <c r="AG33">
-        <v>52107.7</v>
+        <v>13354.7</v>
       </c>
       <c r="AH33">
-        <v>0.9286710712417414</v>
+        <v>0.7274986756136324</v>
       </c>
       <c r="AI33">
-        <v>0.7656136857349748</v>
+        <v>0.6825620358443129</v>
       </c>
       <c r="AJ33">
-        <v>0.9218441234487089</v>
+        <v>0.6838954494709998</v>
       </c>
       <c r="AK33">
-        <v>0.747424920714381</v>
+        <v>0.6353723113227745</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -4471,7 +4483,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zhongyuan Bank Co., Ltd. (SEHK:1216)</t>
+          <t>Bank of Gansu Co., Ltd. (SEHK:2139)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4480,10 +4492,10 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.07200000000000001</v>
+        <v>-0.152</v>
       </c>
       <c r="E34">
-        <v>0.0133</v>
+        <v>-0.295</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4498,82 +4510,85 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>526.9</v>
+        <v>84.7</v>
       </c>
       <c r="L34">
-        <v>0.2628192338387869</v>
+        <v>0.2032149712092131</v>
       </c>
       <c r="M34">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="N34">
-        <v>-0</v>
+        <v>5.924170616113744e-06</v>
       </c>
       <c r="O34">
-        <v>-0</v>
+        <v>4.722550177095632e-05</v>
       </c>
       <c r="P34">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="Q34">
-        <v>-0</v>
+        <v>5.924170616113744e-06</v>
       </c>
       <c r="R34">
-        <v>-0</v>
+        <v>4.722550177095632e-05</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
       <c r="U34">
-        <v>10415.4</v>
+        <v>964.1</v>
       </c>
       <c r="V34">
-        <v>3.526937794182385</v>
+        <v>1.427873222748815</v>
       </c>
       <c r="W34">
-        <v>0.06652273817640077</v>
+        <v>0.01751918423066581</v>
       </c>
       <c r="X34">
-        <v>0.3514366820550447</v>
+        <v>0.1473940609711838</v>
       </c>
       <c r="Y34">
-        <v>-0.284913943878644</v>
+        <v>-0.129874876740518</v>
       </c>
       <c r="Z34">
-        <v>0.07577177758292263</v>
+        <v>0.04119879803890559</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.06958210080368762</v>
+        <v>0.05791331783761618</v>
       </c>
       <c r="AC34">
-        <v>-0.06958210080368762</v>
+        <v>-0.05791331783761618</v>
       </c>
       <c r="AD34">
-        <v>43782.8</v>
+        <v>5031.3</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>43782.8</v>
+        <v>5031.3</v>
       </c>
       <c r="AG34">
-        <v>33367.4</v>
+        <v>4067.2</v>
       </c>
       <c r="AH34">
-        <v>0.9368130281004539</v>
+        <v>0.8816787873477614</v>
       </c>
       <c r="AI34">
-        <v>0.7709175938626347</v>
+        <v>0.525116633442226</v>
       </c>
       <c r="AJ34">
-        <v>0.9186932999270385</v>
+        <v>0.8576248313090418</v>
       </c>
       <c r="AK34">
-        <v>0.719470780137868</v>
+        <v>0.4719862600380634</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -4590,7 +4605,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jiangxi Bank Co., Ltd. (SEHK:1916)</t>
+          <t>Guangzhou Rural Commercial Bank Co., Ltd. (SEHK:1551)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4598,6 +4613,12 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D35">
+        <v>-0.0496</v>
+      </c>
+      <c r="E35">
+        <v>-0.137</v>
+      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -4611,28 +4632,28 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>301.7</v>
+        <v>423.1</v>
       </c>
       <c r="L35">
-        <v>0.3295107033639144</v>
+        <v>0.280124470338983</v>
       </c>
       <c r="M35">
-        <v>46.2</v>
+        <v>165.8</v>
       </c>
       <c r="N35">
-        <v>0.06499718626899269</v>
+        <v>0.05139650950122446</v>
       </c>
       <c r="O35">
-        <v>0.1531322505800464</v>
+        <v>0.3918695343890333</v>
       </c>
       <c r="P35">
-        <v>46.2</v>
+        <v>165.8</v>
       </c>
       <c r="Q35">
-        <v>0.06499718626899269</v>
+        <v>0.05139650950122446</v>
       </c>
       <c r="R35">
-        <v>0.1531322505800464</v>
+        <v>0.3918695343890333</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4641,55 +4662,55 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1686.9</v>
+        <v>5153.3</v>
       </c>
       <c r="V35">
-        <v>2.373241418120428</v>
+        <v>1.597476673176478</v>
       </c>
       <c r="W35">
-        <v>0.05352327561737155</v>
+        <v>0.04014840962574964</v>
       </c>
       <c r="X35">
-        <v>0.4709363005163651</v>
+        <v>0.1640901130047037</v>
       </c>
       <c r="Y35">
-        <v>-0.4174130248989936</v>
+        <v>-0.123941703378954</v>
       </c>
       <c r="Z35">
-        <v>0.05783954516740367</v>
+        <v>0.0414240618289228</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.06967650760490099</v>
+        <v>0.05796197632049842</v>
       </c>
       <c r="AC35">
-        <v>-0.06967650760490099</v>
+        <v>-0.05796197632049842</v>
       </c>
       <c r="AD35">
-        <v>14928.7</v>
+        <v>28395.1</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>14928.7</v>
+        <v>28395.1</v>
       </c>
       <c r="AG35">
-        <v>13241.8</v>
+        <v>23241.8</v>
       </c>
       <c r="AH35">
-        <v>0.9545509766936283</v>
+        <v>0.8979823534992568</v>
       </c>
       <c r="AI35">
-        <v>0.6982259867451791</v>
+        <v>0.6975294843041066</v>
       </c>
       <c r="AJ35">
-        <v>0.9490560899043906</v>
+        <v>0.878119368135501</v>
       </c>
       <c r="AK35">
-        <v>0.6723773738194374</v>
+        <v>0.6536895159022128</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4706,117 +4727,358 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Huishang Bank Corporation Limited (SEHK:3698)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.144</v>
+      </c>
+      <c r="E36">
+        <v>0.12</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>1965.8</v>
+      </c>
+      <c r="L36">
+        <v>0.4539324804876922</v>
+      </c>
+      <c r="M36">
+        <v>236.1266</v>
+      </c>
+      <c r="N36">
+        <v>0.05603383958234456</v>
+      </c>
+      <c r="O36">
+        <v>0.1201173059314274</v>
+      </c>
+      <c r="P36">
+        <v>236.1266</v>
+      </c>
+      <c r="Q36">
+        <v>0.05603383958234456</v>
+      </c>
+      <c r="R36">
+        <v>0.1201173059314274</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>2400.7</v>
+      </c>
+      <c r="V36">
+        <v>0.5696962505932606</v>
+      </c>
+      <c r="W36">
+        <v>0.1145771405257329</v>
+      </c>
+      <c r="X36">
+        <v>0.2143901494357628</v>
+      </c>
+      <c r="Y36">
+        <v>-0.09981300891002988</v>
+      </c>
+      <c r="Z36">
+        <v>0.06454892070675003</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0.05805129293314772</v>
+      </c>
+      <c r="AC36">
+        <v>-0.05805129293314772</v>
+      </c>
+      <c r="AD36">
+        <v>54239.8</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>54239.8</v>
+      </c>
+      <c r="AG36">
+        <v>51839.10000000001</v>
+      </c>
+      <c r="AH36">
+        <v>0.927908878464702</v>
+      </c>
+      <c r="AI36">
+        <v>0.7503769883541727</v>
+      </c>
+      <c r="AJ36">
+        <v>0.9248212855310411</v>
+      </c>
+      <c r="AK36">
+        <v>0.7418016189986935</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shengjing Bank Co., Ltd. (SEHK:2066)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>-0.08650000000000001</v>
+      </c>
+      <c r="E37">
+        <v>-0.355</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>106.7</v>
+      </c>
+      <c r="L37">
+        <v>0.1130536130536131</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>-0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>4496.1</v>
+      </c>
+      <c r="V37">
+        <v>5.119093703745873</v>
+      </c>
+      <c r="W37">
+        <v>0.008834902418626988</v>
+      </c>
+      <c r="X37">
+        <v>0.3134197112166585</v>
+      </c>
+      <c r="Y37">
+        <v>-0.3045848087980315</v>
+      </c>
+      <c r="Z37">
+        <v>0.04206688447429766</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0.05813006215560662</v>
+      </c>
+      <c r="AC37">
+        <v>-0.05813006215560662</v>
+      </c>
+      <c r="AD37">
+        <v>18341.1</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>18341.1</v>
+      </c>
+      <c r="AG37">
+        <v>13845</v>
+      </c>
+      <c r="AH37">
+        <v>0.9543013829776164</v>
+      </c>
+      <c r="AI37">
+        <v>0.6176681563004098</v>
+      </c>
+      <c r="AJ37">
+        <v>0.9403462538968845</v>
+      </c>
+      <c r="AK37">
+        <v>0.5494483689181681</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Bank of Chongqing Co., Ltd. (SEHK:1963)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D36">
-        <v>0.05309999999999999</v>
-      </c>
-      <c r="E36">
-        <v>0.0473</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>679.8</v>
-      </c>
-      <c r="L36">
-        <v>0.516604605213162</v>
-      </c>
-      <c r="M36">
-        <v>9.68</v>
-      </c>
-      <c r="N36">
-        <v>0.003601860465116279</v>
-      </c>
-      <c r="O36">
-        <v>0.01423948220064725</v>
-      </c>
-      <c r="P36">
-        <v>9.68</v>
-      </c>
-      <c r="Q36">
-        <v>0.003601860465116279</v>
-      </c>
-      <c r="R36">
-        <v>0.01423948220064725</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>1711.2</v>
-      </c>
-      <c r="V36">
-        <v>0.6367255813953488</v>
-      </c>
-      <c r="W36">
-        <v>0.1045411905823735</v>
-      </c>
-      <c r="X36">
-        <v>0.2935775881718679</v>
-      </c>
-      <c r="Y36">
-        <v>-0.1890363975894944</v>
-      </c>
-      <c r="Z36">
-        <v>0.03338110881394199</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>0.07095603784690484</v>
-      </c>
-      <c r="AC36">
-        <v>-0.07095603784690484</v>
-      </c>
-      <c r="AD36">
-        <v>31807.8</v>
-      </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
-      <c r="AF36">
-        <v>31807.8</v>
-      </c>
-      <c r="AG36">
-        <v>30096.6</v>
-      </c>
-      <c r="AH36">
-        <v>0.9220908355631056</v>
-      </c>
-      <c r="AI36">
-        <v>0.8099358321450397</v>
-      </c>
-      <c r="AJ36">
-        <v>0.9180242861631096</v>
-      </c>
-      <c r="AK36">
-        <v>0.8012768631126068</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
+      <c r="D38">
+        <v>0.0602</v>
+      </c>
+      <c r="E38">
+        <v>0.0542</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>671.1</v>
+      </c>
+      <c r="L38">
+        <v>0.5088717015468608</v>
+      </c>
+      <c r="M38">
+        <v>730.4</v>
+      </c>
+      <c r="N38">
+        <v>0.2744832769635475</v>
+      </c>
+      <c r="O38">
+        <v>1.088362390105796</v>
+      </c>
+      <c r="P38">
+        <v>15.1</v>
+      </c>
+      <c r="Q38">
+        <v>0.005674558436677941</v>
+      </c>
+      <c r="R38">
+        <v>0.02250037252272389</v>
+      </c>
+      <c r="S38">
+        <v>715.3</v>
+      </c>
+      <c r="T38">
+        <v>0.9793263964950711</v>
+      </c>
+      <c r="U38">
+        <v>2144.4</v>
+      </c>
+      <c r="V38">
+        <v>0.8058624577226607</v>
+      </c>
+      <c r="W38">
+        <v>0.09362052369459983</v>
+      </c>
+      <c r="X38">
+        <v>0.2284428970987747</v>
+      </c>
+      <c r="Y38">
+        <v>-0.1348223734041748</v>
+      </c>
+      <c r="Z38">
+        <v>0.03538987089727867</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0.05901122711567974</v>
+      </c>
+      <c r="AC38">
+        <v>-0.05901122711567974</v>
+      </c>
+      <c r="AD38">
+        <v>37275.7</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>37275.7</v>
+      </c>
+      <c r="AG38">
+        <v>35131.3</v>
+      </c>
+      <c r="AH38">
+        <v>0.9333695573244659</v>
+      </c>
+      <c r="AI38">
+        <v>0.8304730544125085</v>
+      </c>
+      <c r="AJ38">
+        <v>0.9295888315873868</v>
+      </c>
+      <c r="AK38">
+        <v>0.8219674547560277</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/china/china_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/china/china_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0381</v>
+        <v>0.03975</v>
       </c>
       <c r="E2">
-        <v>0.04099999999999999</v>
+        <v>0.0438</v>
+      </c>
+      <c r="F2">
+        <v>0.0716</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3.105891831714807E-06</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2.888677615052131E-06</v>
       </c>
       <c r="K2">
-        <v>725.3</v>
+        <v>30382.35</v>
       </c>
       <c r="L2">
-        <v>0.5298027757487217</v>
+        <v>0.4807607711831686</v>
       </c>
       <c r="M2">
-        <v>213.8</v>
+        <v>8844.1059</v>
       </c>
       <c r="N2">
-        <v>0.05863960504662644</v>
+        <v>0.05523961802423919</v>
       </c>
       <c r="O2">
-        <v>0.2947745760375017</v>
+        <v>0.2910935427970516</v>
       </c>
       <c r="P2">
-        <v>213.8</v>
+        <v>8844.1059</v>
       </c>
       <c r="Q2">
-        <v>0.05863960504662644</v>
+        <v>0.05523961802423919</v>
       </c>
       <c r="R2">
-        <v>0.2947745760375017</v>
+        <v>0.2910935427970516</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +639,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1853.9</v>
+        <v>166630.3</v>
       </c>
       <c r="V2">
-        <v>0.5084750411409764</v>
+        <v>1.040760278918006</v>
       </c>
       <c r="W2">
-        <v>0.09945834761741515</v>
+        <v>0.09480818451408198</v>
       </c>
       <c r="X2">
-        <v>0.1920325325413729</v>
+        <v>0.1368017822393021</v>
       </c>
       <c r="Y2">
-        <v>-0.09257418492395775</v>
+        <v>-0.04199359772522017</v>
       </c>
       <c r="Z2">
-        <v>0.03226962224034623</v>
+        <v>0.05547424864390299</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06163010589969715</v>
+        <v>0.05711166067982623</v>
       </c>
       <c r="AC2">
-        <v>-0.06163010589969715</v>
+        <v>-0.05711166067982623</v>
       </c>
       <c r="AD2">
-        <v>41193.1</v>
+        <v>1104507.9</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>11.32359408723109</v>
       </c>
       <c r="AF2">
-        <v>41193.1</v>
+        <v>1104519.223594087</v>
       </c>
       <c r="AG2">
-        <v>39339.2</v>
+        <v>937888.9235940871</v>
       </c>
       <c r="AH2">
-        <v>0.9186870387675042</v>
+        <v>0.8733975888059249</v>
       </c>
       <c r="AI2">
-        <v>0.8210556318503356</v>
+        <v>0.7514245733978762</v>
       </c>
       <c r="AJ2">
-        <v>0.9151801085024613</v>
+        <v>0.8541845414178599</v>
       </c>
       <c r="AK2">
-        <v>0.8141896227000848</v>
+        <v>0.7196428265937003</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>448804.5103616415</v>
+      </c>
+      <c r="AP2">
+        <v>381100.740997191</v>
       </c>
     </row>
     <row r="3">
@@ -701,117 +710,4411 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bank of Tianjin Co., Ltd. (SEHK:1578)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.00984</v>
+      </c>
+      <c r="E3">
+        <v>-0.0349</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>537.2</v>
+      </c>
+      <c r="L3">
+        <v>0.4272307937012884</v>
+      </c>
+      <c r="M3">
+        <v>103.2002</v>
+      </c>
+      <c r="N3">
+        <v>0.07255357142857143</v>
+      </c>
+      <c r="O3">
+        <v>0.1921075949367089</v>
+      </c>
+      <c r="P3">
+        <v>103.2002</v>
+      </c>
+      <c r="Q3">
+        <v>0.07255357142857143</v>
+      </c>
+      <c r="R3">
+        <v>0.1921075949367089</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>6080.3</v>
+      </c>
+      <c r="V3">
+        <v>4.274676602924634</v>
+      </c>
+      <c r="W3">
+        <v>0.06165995202185417</v>
+      </c>
+      <c r="X3">
+        <v>0.3771437085151693</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3154837564933152</v>
+      </c>
+      <c r="Z3">
+        <v>0.03306754468089583</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.05585668009508321</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05585668009508321</v>
+      </c>
+      <c r="AD3">
+        <v>38832.4</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>38832.4</v>
+      </c>
+      <c r="AG3">
+        <v>32752.1</v>
+      </c>
+      <c r="AH3">
+        <v>0.9646650834186233</v>
+      </c>
+      <c r="AI3">
+        <v>0.800669692102458</v>
+      </c>
+      <c r="AJ3">
+        <v>0.958378323018625</v>
+      </c>
+      <c r="AK3">
+        <v>0.772098275325557</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Xiamen Bank Co., Ltd. (SHSE:601187)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>361.3</v>
+      </c>
+      <c r="L4">
+        <v>0.5470926711084192</v>
+      </c>
+      <c r="M4">
+        <v>153.1</v>
+      </c>
+      <c r="N4">
+        <v>0.07507846214201647</v>
+      </c>
+      <c r="O4">
+        <v>0.4237475781898699</v>
+      </c>
+      <c r="P4">
+        <v>153.1</v>
+      </c>
+      <c r="Q4">
+        <v>0.07507846214201647</v>
+      </c>
+      <c r="R4">
+        <v>0.4237475781898699</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3450.8</v>
+      </c>
+      <c r="V4">
+        <v>1.692232247940369</v>
+      </c>
+      <c r="W4">
+        <v>0.09014471057884232</v>
+      </c>
+      <c r="X4">
+        <v>0.1776672604818542</v>
+      </c>
+      <c r="Y4">
+        <v>-0.08752254990301184</v>
+      </c>
+      <c r="Z4">
+        <v>0.03285147194890213</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.0561633226381817</v>
+      </c>
+      <c r="AC4">
+        <v>-0.0561633226381817</v>
+      </c>
+      <c r="AD4">
+        <v>20519.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>20519.1</v>
+      </c>
+      <c r="AG4">
+        <v>17068.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.9096031172561762</v>
+      </c>
+      <c r="AI4">
+        <v>0.8190603544627175</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8932775088316106</v>
+      </c>
+      <c r="AK4">
+        <v>0.790155176564265</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bank of Guiyang Co.,Ltd. (SHSE:601997)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.00835</v>
+      </c>
+      <c r="E5">
+        <v>-0.0159</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>751.5</v>
+      </c>
+      <c r="L5">
+        <v>0.550912689685507</v>
+      </c>
+      <c r="M5">
+        <v>149.9042</v>
+      </c>
+      <c r="N5">
+        <v>0.0498766261853269</v>
+      </c>
+      <c r="O5">
+        <v>0.1994733200266134</v>
+      </c>
+      <c r="P5">
+        <v>149.9042</v>
+      </c>
+      <c r="Q5">
+        <v>0.0498766261853269</v>
+      </c>
+      <c r="R5">
+        <v>0.1994733200266134</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>4292.7</v>
+      </c>
+      <c r="V5">
+        <v>1.428281483946099</v>
+      </c>
+      <c r="W5">
+        <v>0.0996684350132626</v>
+      </c>
+      <c r="X5">
+        <v>0.16598610084264</v>
+      </c>
+      <c r="Y5">
+        <v>-0.06631766582937738</v>
+      </c>
+      <c r="Z5">
+        <v>0.04491145125127168</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05621387397155694</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05621387397155694</v>
+      </c>
+      <c r="AD5">
+        <v>27208.4</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>27208.4</v>
+      </c>
+      <c r="AG5">
+        <v>22915.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.9005259168793172</v>
+      </c>
+      <c r="AI5">
+        <v>0.7400605465509409</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8840524358440196</v>
+      </c>
+      <c r="AK5">
+        <v>0.7056977617915522</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bank of Changsha Co., Ltd. (SHSE:601577)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.0977</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1112.7</v>
+      </c>
+      <c r="L6">
+        <v>0.4557444194142945</v>
+      </c>
+      <c r="M6">
+        <v>217.1664</v>
+      </c>
+      <c r="N6">
+        <v>0.04433686531512218</v>
+      </c>
+      <c r="O6">
+        <v>0.1951706659476948</v>
+      </c>
+      <c r="P6">
+        <v>217.1664</v>
+      </c>
+      <c r="Q6">
+        <v>0.04433686531512218</v>
+      </c>
+      <c r="R6">
+        <v>0.1951706659476948</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>7720.2</v>
+      </c>
+      <c r="V6">
+        <v>1.576162185337171</v>
+      </c>
+      <c r="W6">
+        <v>0.1380949426000621</v>
+      </c>
+      <c r="X6">
+        <v>0.1640305239824661</v>
+      </c>
+      <c r="Y6">
+        <v>-0.02593558138240401</v>
+      </c>
+      <c r="Z6">
+        <v>0.06618396512838307</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05622334595477807</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05622334595477807</v>
+      </c>
+      <c r="AD6">
+        <v>43514.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>43514.1</v>
+      </c>
+      <c r="AG6">
+        <v>35793.9</v>
+      </c>
+      <c r="AH6">
+        <v>0.8988250895435448</v>
+      </c>
+      <c r="AI6">
+        <v>0.7957911715919627</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8796299026835742</v>
+      </c>
+      <c r="AK6">
+        <v>0.7622194160574615</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bank of Qingdao Co., Ltd. (SEHK:3866)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0999</v>
+      </c>
+      <c r="E7">
+        <v>0.126</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>572.4</v>
+      </c>
+      <c r="L7">
+        <v>0.4376481382368682</v>
+      </c>
+      <c r="M7">
+        <v>176.4</v>
+      </c>
+      <c r="N7">
+        <v>0.06465327664565312</v>
+      </c>
+      <c r="O7">
+        <v>0.3081761006289309</v>
+      </c>
+      <c r="P7">
+        <v>176.4</v>
+      </c>
+      <c r="Q7">
+        <v>0.06465327664565312</v>
+      </c>
+      <c r="R7">
+        <v>0.3081761006289309</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>4102.5</v>
+      </c>
+      <c r="V7">
+        <v>1.503628500219909</v>
+      </c>
+      <c r="W7">
+        <v>0.1089663049685894</v>
+      </c>
+      <c r="X7">
+        <v>0.1604239717427831</v>
+      </c>
+      <c r="Y7">
+        <v>-0.05145766677419368</v>
+      </c>
+      <c r="Z7">
+        <v>0.05712301604633084</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05624169174360913</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05624169174360913</v>
+      </c>
+      <c r="AD7">
+        <v>23388.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>23388.4</v>
+      </c>
+      <c r="AG7">
+        <v>19285.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.8955308460454573</v>
+      </c>
+      <c r="AI7">
+        <v>0.7902447594977767</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8760623776363545</v>
+      </c>
+      <c r="AK7">
+        <v>0.7564907683798869</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Qingdao Rural Commercial Bank Co., Ltd. (SZSE:002958)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.0677</v>
+      </c>
+      <c r="E8">
+        <v>-0.00124</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>388.5</v>
+      </c>
+      <c r="L8">
+        <v>0.4978216299333675</v>
+      </c>
+      <c r="M8">
+        <v>161.8</v>
+      </c>
+      <c r="N8">
+        <v>0.06992523445265569</v>
+      </c>
+      <c r="O8">
+        <v>0.4164736164736165</v>
+      </c>
+      <c r="P8">
+        <v>161.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.06992523445265569</v>
+      </c>
+      <c r="R8">
+        <v>0.4164736164736165</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2593.9</v>
+      </c>
+      <c r="V8">
+        <v>1.12100782229137</v>
+      </c>
+      <c r="W8">
+        <v>0.07363253856942496</v>
+      </c>
+      <c r="X8">
+        <v>0.1428760163622144</v>
+      </c>
+      <c r="Y8">
+        <v>-0.06924347779278946</v>
+      </c>
+      <c r="Z8">
+        <v>0.04112303184874481</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05635121134995375</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05635121134995375</v>
+      </c>
+      <c r="AD8">
+        <v>16326.3</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>16326.3</v>
+      </c>
+      <c r="AG8">
+        <v>13732.4</v>
+      </c>
+      <c r="AH8">
+        <v>0.8758650658254739</v>
+      </c>
+      <c r="AI8">
+        <v>0.7334564273969648</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8557985329951453</v>
+      </c>
+      <c r="AK8">
+        <v>0.6982990516386565</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chongqing Rural Commercial Bank Co., Ltd. (SEHK:3618)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.00479</v>
+      </c>
+      <c r="E9">
+        <v>0.009439999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.0635</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1604.6</v>
+      </c>
+      <c r="L9">
+        <v>0.5339411686410223</v>
+      </c>
+      <c r="M9">
+        <v>486.6</v>
+      </c>
+      <c r="N9">
+        <v>0.05507702407497539</v>
+      </c>
+      <c r="O9">
+        <v>0.3032531472017949</v>
+      </c>
+      <c r="P9">
+        <v>486.6</v>
+      </c>
+      <c r="Q9">
+        <v>0.05507702407497539</v>
+      </c>
+      <c r="R9">
+        <v>0.3032531472017949</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>7456.8</v>
+      </c>
+      <c r="V9">
+        <v>0.8440163442710161</v>
+      </c>
+      <c r="W9">
+        <v>0.09678275450257547</v>
+      </c>
+      <c r="X9">
+        <v>0.1396591554211701</v>
+      </c>
+      <c r="Y9">
+        <v>-0.04287640091859467</v>
+      </c>
+      <c r="Z9">
+        <v>0.04998993614023531</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.05637592035316742</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05637592035316742</v>
+      </c>
+      <c r="AD9">
+        <v>59880.8</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>59880.8</v>
+      </c>
+      <c r="AG9">
+        <v>52424</v>
+      </c>
+      <c r="AH9">
+        <v>0.8714282180054923</v>
+      </c>
+      <c r="AI9">
+        <v>0.7607775377969763</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8557776910783575</v>
+      </c>
+      <c r="AK9">
+        <v>0.7357423947275351</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bank of Suzhou Co., Ltd. (SZSE:002966)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.173</v>
+      </c>
+      <c r="E10">
+        <v>0.156</v>
+      </c>
+      <c r="F10">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>715.4</v>
+      </c>
+      <c r="L10">
+        <v>0.4660586319218241</v>
+      </c>
+      <c r="M10">
+        <v>304.9</v>
+      </c>
+      <c r="N10">
+        <v>0.0747175729654226</v>
+      </c>
+      <c r="O10">
+        <v>0.4261951355884819</v>
+      </c>
+      <c r="P10">
+        <v>304.9</v>
+      </c>
+      <c r="Q10">
+        <v>0.0747175729654226</v>
+      </c>
+      <c r="R10">
+        <v>0.4261951355884819</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1698.5</v>
+      </c>
+      <c r="V10">
+        <v>0.41622760800843</v>
+      </c>
+      <c r="W10">
+        <v>0.1174153522952945</v>
+      </c>
+      <c r="X10">
+        <v>0.137278314924808</v>
+      </c>
+      <c r="Y10">
+        <v>-0.01986296262951352</v>
+      </c>
+      <c r="Z10">
+        <v>0.06117292609832303</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.05639537610684235</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05639537610684235</v>
+      </c>
+      <c r="AD10">
+        <v>26818.4</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>26818.4</v>
+      </c>
+      <c r="AG10">
+        <v>25119.9</v>
+      </c>
+      <c r="AH10">
+        <v>0.8679346647636986</v>
+      </c>
+      <c r="AI10">
+        <v>0.7882756836833071</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8602528715163387</v>
+      </c>
+      <c r="AK10">
+        <v>0.7771500877081715</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bank of Nanjing Co., Ltd. (SHSE:601009)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0978</v>
+      </c>
+      <c r="E11">
+        <v>0.0992</v>
+      </c>
+      <c r="F11">
+        <v>0.08310000000000001</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>2834.2</v>
+      </c>
+      <c r="L11">
+        <v>0.530193055971266</v>
+      </c>
+      <c r="M11">
+        <v>1355.9868</v>
+      </c>
+      <c r="N11">
+        <v>0.08635593511778529</v>
+      </c>
+      <c r="O11">
+        <v>0.4784372309646461</v>
+      </c>
+      <c r="P11">
+        <v>1355.9868</v>
+      </c>
+      <c r="Q11">
+        <v>0.08635593511778529</v>
+      </c>
+      <c r="R11">
+        <v>0.4784372309646461</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>8595.5</v>
+      </c>
+      <c r="V11">
+        <v>0.5474038835075117</v>
+      </c>
+      <c r="W11">
+        <v>0.1319779462439697</v>
+      </c>
+      <c r="X11">
+        <v>0.1363252495537962</v>
+      </c>
+      <c r="Y11">
+        <v>-0.004347303309826578</v>
+      </c>
+      <c r="Z11">
+        <v>0.0582415954117965</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.05640346396222409</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05640346396222409</v>
+      </c>
+      <c r="AD11">
+        <v>101902.4</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>101902.4</v>
+      </c>
+      <c r="AG11">
+        <v>93306.89999999999</v>
+      </c>
+      <c r="AH11">
+        <v>0.8664823769798315</v>
+      </c>
+      <c r="AI11">
+        <v>0.7965873407351413</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8559543598155018</v>
+      </c>
+      <c r="AK11">
+        <v>0.7819350329595184</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bank of Jiangsu Co., Ltd. (SHSE:600919)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.17</v>
+      </c>
+      <c r="E12">
+        <v>0.164</v>
+      </c>
+      <c r="F12">
+        <v>0.0433</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>4466.7</v>
+      </c>
+      <c r="L12">
+        <v>0.5187262655471554</v>
+      </c>
+      <c r="M12">
+        <v>1229.5371</v>
+      </c>
+      <c r="N12">
+        <v>0.04980040341362453</v>
+      </c>
+      <c r="O12">
+        <v>0.2752674457653301</v>
+      </c>
+      <c r="P12">
+        <v>1229.5371</v>
+      </c>
+      <c r="Q12">
+        <v>0.04980040341362453</v>
+      </c>
+      <c r="R12">
+        <v>0.2752674457653301</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>11837.3</v>
+      </c>
+      <c r="V12">
+        <v>0.4794506122085276</v>
+      </c>
+      <c r="W12">
+        <v>0.1445066321578777</v>
+      </c>
+      <c r="X12">
+        <v>0.132150849114406</v>
+      </c>
+      <c r="Y12">
+        <v>0.01235578304347168</v>
+      </c>
+      <c r="Z12">
+        <v>0.06387685295839092</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05644109039664847</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05644109039664847</v>
+      </c>
+      <c r="AD12">
+        <v>151318.4</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>151318.4</v>
+      </c>
+      <c r="AG12">
+        <v>139481.1</v>
+      </c>
+      <c r="AH12">
+        <v>0.8597260233501148</v>
+      </c>
+      <c r="AI12">
+        <v>0.7727845408772719</v>
+      </c>
+      <c r="AJ12">
+        <v>0.8496117448699645</v>
+      </c>
+      <c r="AK12">
+        <v>0.7581648294305655</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Qilu Bank Co., Ltd. (SHSE:601665)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.101</v>
+      </c>
+      <c r="E13">
+        <v>0.156</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>675.6</v>
+      </c>
+      <c r="L13">
+        <v>0.5795162120432321</v>
+      </c>
+      <c r="M13">
+        <v>297.3</v>
+      </c>
+      <c r="N13">
+        <v>0.08028842258770154</v>
+      </c>
+      <c r="O13">
+        <v>0.4400532859680284</v>
+      </c>
+      <c r="P13">
+        <v>297.3</v>
+      </c>
+      <c r="Q13">
+        <v>0.08028842258770154</v>
+      </c>
+      <c r="R13">
+        <v>0.4400532859680284</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>3353.7</v>
+      </c>
+      <c r="V13">
+        <v>0.905695535931297</v>
+      </c>
+      <c r="W13">
+        <v>0.1315932995714842</v>
+      </c>
+      <c r="X13">
+        <v>0.1319926402876362</v>
+      </c>
+      <c r="Y13">
+        <v>-0.0003993407161519413</v>
+      </c>
+      <c r="Z13">
+        <v>0.06746683951017383</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05644259146990688</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05644259146990688</v>
+      </c>
+      <c r="AD13">
+        <v>22644.1</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>22644.1</v>
+      </c>
+      <c r="AG13">
+        <v>19290.4</v>
+      </c>
+      <c r="AH13">
+        <v>0.8594564846092534</v>
+      </c>
+      <c r="AI13">
+        <v>0.7777174827672662</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8389574354268416</v>
+      </c>
+      <c r="AK13">
+        <v>0.7487811694562618</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bank of Jiujiang Co., Ltd. (SEHK:6190)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.0859</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-6.55</v>
+      </c>
+      <c r="L14">
+        <v>-0.01485260770975057</v>
+      </c>
+      <c r="M14">
+        <v>25.6266</v>
+      </c>
+      <c r="N14">
+        <v>0.01331597817614965</v>
+      </c>
+      <c r="O14">
+        <v>-3.912458015267176</v>
+      </c>
+      <c r="P14">
+        <v>25.6266</v>
+      </c>
+      <c r="Q14">
+        <v>0.01331597817614965</v>
+      </c>
+      <c r="R14">
+        <v>-3.912458015267176</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>3753.2</v>
+      </c>
+      <c r="V14">
+        <v>1.95022083658093</v>
+      </c>
+      <c r="W14">
+        <v>-0.001160771248316438</v>
+      </c>
+      <c r="X14">
+        <v>0.1310127410022331</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1321735122505495</v>
+      </c>
+      <c r="Z14">
+        <v>0.03934443780277819</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05645201874107453</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05645201874107453</v>
+      </c>
+      <c r="AD14">
+        <v>11605.8</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>11605.8</v>
+      </c>
+      <c r="AG14">
+        <v>7852.599999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0.8577636859493137</v>
+      </c>
+      <c r="AI14">
+        <v>0.6547627107169455</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8031624919454645</v>
+      </c>
+      <c r="AK14">
+        <v>0.5620240480961923</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bank of Xi'an Co.,Ltd. (SHSE:600928)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.0254</v>
+      </c>
+      <c r="E15">
+        <v>-0.006730000000000001</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>354.1</v>
+      </c>
+      <c r="L15">
+        <v>0.5742783003567954</v>
+      </c>
+      <c r="M15">
+        <v>53.7</v>
+      </c>
+      <c r="N15">
+        <v>0.02443018970929439</v>
+      </c>
+      <c r="O15">
+        <v>0.1516520756848348</v>
+      </c>
+      <c r="P15">
+        <v>53.7</v>
+      </c>
+      <c r="Q15">
+        <v>0.02443018970929439</v>
+      </c>
+      <c r="R15">
+        <v>0.1516520756848348</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>3377.4</v>
+      </c>
+      <c r="V15">
+        <v>1.536508803057186</v>
+      </c>
+      <c r="W15">
+        <v>0.08495885217975481</v>
+      </c>
+      <c r="X15">
+        <v>0.1259791225594227</v>
+      </c>
+      <c r="Y15">
+        <v>-0.04102027037966786</v>
+      </c>
+      <c r="Z15">
+        <v>0.04458584909071189</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.05650426105155545</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05650426105155545</v>
+      </c>
+      <c r="AD15">
+        <v>12299.6</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>12299.6</v>
+      </c>
+      <c r="AG15">
+        <v>8922.200000000001</v>
+      </c>
+      <c r="AH15">
+        <v>0.8483828469343413</v>
+      </c>
+      <c r="AI15">
+        <v>0.7251438543533629</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8023344693938113</v>
+      </c>
+      <c r="AK15">
+        <v>0.6568071730392663</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bank of Hangzhou Co., Ltd. (SHSE:600926)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.177</v>
+      </c>
+      <c r="E16">
+        <v>0.213</v>
+      </c>
+      <c r="F16">
+        <v>0.16</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>6.644699050673564E-05</v>
+      </c>
+      <c r="J16">
+        <v>5.88587466837192E-05</v>
+      </c>
+      <c r="K16">
+        <v>2361.1</v>
+      </c>
+      <c r="L16">
+        <v>0.5705758681520504</v>
+      </c>
+      <c r="M16">
+        <v>250.9</v>
+      </c>
+      <c r="N16">
+        <v>0.02089457773632359</v>
+      </c>
+      <c r="O16">
+        <v>0.1062640294777858</v>
+      </c>
+      <c r="P16">
+        <v>250.9</v>
+      </c>
+      <c r="Q16">
+        <v>0.02089457773632359</v>
+      </c>
+      <c r="R16">
+        <v>0.1062640294777858</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>13493.6</v>
+      </c>
+      <c r="V16">
+        <v>1.123726879804129</v>
+      </c>
+      <c r="W16">
+        <v>0.1750687714563236</v>
+      </c>
+      <c r="X16">
+        <v>0.1243765295647593</v>
+      </c>
+      <c r="Y16">
+        <v>0.05069224189156429</v>
+      </c>
+      <c r="Z16">
+        <v>0.05704425785552893</v>
+      </c>
+      <c r="AA16">
+        <v>3.357553522879336E-06</v>
+      </c>
+      <c r="AB16">
+        <v>0.05652237109581312</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05651901354229024</v>
+      </c>
+      <c r="AD16">
+        <v>65527.6</v>
+      </c>
+      <c r="AE16">
+        <v>0.3201785429203863</v>
+      </c>
+      <c r="AF16">
+        <v>65527.92017854292</v>
+      </c>
+      <c r="AG16">
+        <v>52034.32017854292</v>
+      </c>
+      <c r="AH16">
+        <v>0.8451309346783303</v>
+      </c>
+      <c r="AI16">
+        <v>0.7759896703531446</v>
+      </c>
+      <c r="AJ16">
+        <v>0.812500254261591</v>
+      </c>
+      <c r="AK16">
+        <v>0.7333867795506783</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>193296.7551622419</v>
+      </c>
+      <c r="AP16">
+        <v>153493.5698482092</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dongguan Rural Commercial Bank Co., Ltd. (SEHK:9889)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.007860000000000001</v>
+      </c>
+      <c r="E17">
+        <v>-0.007820000000000001</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>664.2</v>
+      </c>
+      <c r="L17">
+        <v>0.4979383761901192</v>
+      </c>
+      <c r="M17">
+        <v>261.763</v>
+      </c>
+      <c r="N17">
+        <v>0.06708259655057533</v>
+      </c>
+      <c r="O17">
+        <v>0.394102679915688</v>
+      </c>
+      <c r="P17">
+        <v>261.763</v>
+      </c>
+      <c r="Q17">
+        <v>0.06708259655057533</v>
+      </c>
+      <c r="R17">
+        <v>0.394102679915688</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>5256.6</v>
+      </c>
+      <c r="V17">
+        <v>1.34712078111786</v>
+      </c>
+      <c r="W17">
+        <v>0.08959935248887091</v>
+      </c>
+      <c r="X17">
+        <v>0.116907237730389</v>
+      </c>
+      <c r="Y17">
+        <v>-0.02730788524151806</v>
+      </c>
+      <c r="Z17">
+        <v>0.07071515665588718</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.05661816381396795</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05661816381396795</v>
+      </c>
+      <c r="AD17">
+        <v>18775.3</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>18775.3</v>
+      </c>
+      <c r="AG17">
+        <v>13518.7</v>
+      </c>
+      <c r="AH17">
+        <v>0.827930009613095</v>
+      </c>
+      <c r="AI17">
+        <v>0.682296549869539</v>
+      </c>
+      <c r="AJ17">
+        <v>0.7760091385011021</v>
+      </c>
+      <c r="AK17">
+        <v>0.6072763373043681</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bank of Lanzhou Co., Ltd. (SZSE:001227)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.0123</v>
+      </c>
+      <c r="E18">
+        <v>-0.0127</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>-0.0004691016854299235</v>
+      </c>
+      <c r="J18">
+        <v>-0.0004691016854299235</v>
+      </c>
+      <c r="K18">
+        <v>267.7</v>
+      </c>
+      <c r="L18">
+        <v>0.4082659752935793</v>
+      </c>
+      <c r="M18">
+        <v>109.7</v>
+      </c>
+      <c r="N18">
+        <v>0.05714732235882476</v>
+      </c>
+      <c r="O18">
+        <v>0.4097870750840493</v>
+      </c>
+      <c r="P18">
+        <v>109.7</v>
+      </c>
+      <c r="Q18">
+        <v>0.05714732235882476</v>
+      </c>
+      <c r="R18">
+        <v>0.4097870750840493</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1278.3</v>
+      </c>
+      <c r="V18">
+        <v>0.6659199833298604</v>
+      </c>
+      <c r="W18">
+        <v>0.05986269818198082</v>
+      </c>
+      <c r="X18">
+        <v>0.1175818666465153</v>
+      </c>
+      <c r="Y18">
+        <v>-0.0577191684645345</v>
+      </c>
+      <c r="Z18">
+        <v>0.06600671395170141</v>
+      </c>
+      <c r="AA18">
+        <v>-3.096386076443397E-05</v>
+      </c>
+      <c r="AB18">
+        <v>0.05660864630067364</v>
+      </c>
+      <c r="AC18">
+        <v>-0.05663961016143807</v>
+      </c>
+      <c r="AD18">
+        <v>9337.5</v>
+      </c>
+      <c r="AE18">
+        <v>10.73794987568201</v>
+      </c>
+      <c r="AF18">
+        <v>9348.237949875682</v>
+      </c>
+      <c r="AG18">
+        <v>8069.937949875682</v>
+      </c>
+      <c r="AH18">
+        <v>0.829639012511608</v>
+      </c>
+      <c r="AI18">
+        <v>0.6539315537343839</v>
+      </c>
+      <c r="AJ18">
+        <v>0.8078389601569221</v>
+      </c>
+      <c r="AK18">
+        <v>0.6199471789382668</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>5074.728260869565</v>
+      </c>
+      <c r="AP18">
+        <v>4385.83584232374</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bank of Chengdu Co., Ltd. (SHSE:601838)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.172</v>
+      </c>
+      <c r="E19">
+        <v>0.19</v>
+      </c>
+      <c r="F19">
+        <v>0.0638</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1789.5</v>
+      </c>
+      <c r="L19">
+        <v>0.6204923717059639</v>
+      </c>
+      <c r="M19">
+        <v>550.8</v>
+      </c>
+      <c r="N19">
+        <v>0.06160798174578318</v>
+      </c>
+      <c r="O19">
+        <v>0.3077954735959765</v>
+      </c>
+      <c r="P19">
+        <v>550.8</v>
+      </c>
+      <c r="Q19">
+        <v>0.06160798174578318</v>
+      </c>
+      <c r="R19">
+        <v>0.3077954735959765</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>11120.6</v>
+      </c>
+      <c r="V19">
+        <v>1.24385933515279</v>
+      </c>
+      <c r="W19">
+        <v>0.1925435765009684</v>
+      </c>
+      <c r="X19">
+        <v>0.1089382255476415</v>
+      </c>
+      <c r="Y19">
+        <v>0.08360535095332691</v>
+      </c>
+      <c r="Z19">
+        <v>0.09736335707774889</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.0567469813154983</v>
+      </c>
+      <c r="AC19">
+        <v>-0.0567469813154983</v>
+      </c>
+      <c r="AD19">
+        <v>36860.6</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>36860.6</v>
+      </c>
+      <c r="AG19">
+        <v>25740</v>
+      </c>
+      <c r="AH19">
+        <v>0.804799021855418</v>
+      </c>
+      <c r="AI19">
+        <v>0.7703847681150333</v>
+      </c>
+      <c r="AJ19">
+        <v>0.7422059722494549</v>
+      </c>
+      <c r="AK19">
+        <v>0.7008582382155615</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jiangsu Zijin Rural Commercial Bank Co.,Ltd (SHSE:601860)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.0262</v>
+      </c>
+      <c r="E20">
+        <v>0.0291</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>231.1</v>
+      </c>
+      <c r="L20">
+        <v>0.4559084632077333</v>
+      </c>
+      <c r="M20">
+        <v>65.8</v>
+      </c>
+      <c r="N20">
+        <v>0.04603008044770899</v>
+      </c>
+      <c r="O20">
+        <v>0.2847252271743834</v>
+      </c>
+      <c r="P20">
+        <v>65.8</v>
+      </c>
+      <c r="Q20">
+        <v>0.04603008044770899</v>
+      </c>
+      <c r="R20">
+        <v>0.2847252271743834</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1649.6</v>
+      </c>
+      <c r="V20">
+        <v>1.153969919552291</v>
+      </c>
+      <c r="W20">
+        <v>0.09283361452558848</v>
+      </c>
+      <c r="X20">
+        <v>0.09768609417459231</v>
+      </c>
+      <c r="Y20">
+        <v>-0.00485247964900383</v>
+      </c>
+      <c r="Z20">
+        <v>0.1227360774818402</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.05700166153300547</v>
+      </c>
+      <c r="AC20">
+        <v>-0.05700166153300547</v>
+      </c>
+      <c r="AD20">
+        <v>4503.7</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>4503.7</v>
+      </c>
+      <c r="AG20">
+        <v>2854.1</v>
+      </c>
+      <c r="AH20">
+        <v>0.7590676194970674</v>
+      </c>
+      <c r="AI20">
+        <v>0.6170635464335625</v>
+      </c>
+      <c r="AJ20">
+        <v>0.6662853674479409</v>
+      </c>
+      <c r="AK20">
+        <v>0.5052398654629138</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jiangsu Zhangjiagang Rural Commercial Bank Co., Ltd (SZSE:002839)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.103</v>
+      </c>
+      <c r="E21">
+        <v>0.152</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>267.3</v>
+      </c>
+      <c r="L21">
+        <v>0.5249410840534171</v>
+      </c>
+      <c r="M21">
+        <v>121.6</v>
+      </c>
+      <c r="N21">
+        <v>0.08309416427497607</v>
+      </c>
+      <c r="O21">
+        <v>0.4549195660306771</v>
+      </c>
+      <c r="P21">
+        <v>121.6</v>
+      </c>
+      <c r="Q21">
+        <v>0.08309416427497607</v>
+      </c>
+      <c r="R21">
+        <v>0.4549195660306771</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1359.4</v>
+      </c>
+      <c r="V21">
+        <v>0.9289326226595599</v>
+      </c>
+      <c r="W21">
+        <v>0.1173758398103017</v>
+      </c>
+      <c r="X21">
+        <v>0.09092048547120021</v>
+      </c>
+      <c r="Y21">
+        <v>0.02645535433910146</v>
+      </c>
+      <c r="Z21">
+        <v>0.09313044114419489</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05722165982664699</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05722165982664699</v>
+      </c>
+      <c r="AD21">
+        <v>3754.9</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>3754.9</v>
+      </c>
+      <c r="AG21">
+        <v>2395.5</v>
+      </c>
+      <c r="AH21">
+        <v>0.7195638426307418</v>
+      </c>
+      <c r="AI21">
+        <v>0.5903373895544445</v>
+      </c>
+      <c r="AJ21">
+        <v>0.6207727590764207</v>
+      </c>
+      <c r="AK21">
+        <v>0.4789850435895385</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jiangsu Suzhou Rural Commercial Bank Co., Ltd (SHSE:603323)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.08900000000000001</v>
+      </c>
+      <c r="E22">
+        <v>0.161</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>273.6</v>
+      </c>
+      <c r="L22">
+        <v>0.5599672533769955</v>
+      </c>
+      <c r="M22">
+        <v>109.4</v>
+      </c>
+      <c r="N22">
+        <v>0.08226182419730807</v>
+      </c>
+      <c r="O22">
+        <v>0.3998538011695906</v>
+      </c>
+      <c r="P22">
+        <v>109.4</v>
+      </c>
+      <c r="Q22">
+        <v>0.08226182419730807</v>
+      </c>
+      <c r="R22">
+        <v>0.3998538011695906</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>421.5</v>
+      </c>
+      <c r="V22">
+        <v>0.3169411233927363</v>
+      </c>
+      <c r="W22">
+        <v>0.1294535131298793</v>
+      </c>
+      <c r="X22">
+        <v>0.08512239955340289</v>
+      </c>
+      <c r="Y22">
+        <v>0.04433111357647646</v>
+      </c>
+      <c r="Z22">
+        <v>0.09801010992537913</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.05747698719954998</v>
+      </c>
+      <c r="AC22">
+        <v>-0.05747698719954998</v>
+      </c>
+      <c r="AD22">
+        <v>2746</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>2746</v>
+      </c>
+      <c r="AG22">
+        <v>2324.5</v>
+      </c>
+      <c r="AH22">
+        <v>0.6737162344512868</v>
+      </c>
+      <c r="AI22">
+        <v>0.529237173804109</v>
+      </c>
+      <c r="AJ22">
+        <v>0.6360825306479859</v>
+      </c>
+      <c r="AK22">
+        <v>0.4876130142015061</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jiangsu Jiangyin Rural Commercial Bank Co.,LTD. (SZSE:002807)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E23">
+        <v>0.155</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>279.4</v>
+      </c>
+      <c r="L23">
+        <v>0.6182783801726045</v>
+      </c>
+      <c r="M23">
+        <v>89.2</v>
+      </c>
+      <c r="N23">
+        <v>0.06080850773740541</v>
+      </c>
+      <c r="O23">
+        <v>0.3192555476020043</v>
+      </c>
+      <c r="P23">
+        <v>89.2</v>
+      </c>
+      <c r="Q23">
+        <v>0.06080850773740541</v>
+      </c>
+      <c r="R23">
+        <v>0.3192555476020043</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>240.8</v>
+      </c>
+      <c r="V23">
+        <v>0.1641557025018747</v>
+      </c>
+      <c r="W23">
+        <v>0.1362129485179407</v>
+      </c>
+      <c r="X23">
+        <v>0.08184092311642491</v>
+      </c>
+      <c r="Y23">
+        <v>0.05437202540151581</v>
+      </c>
+      <c r="Z23">
+        <v>0.1048856910757805</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.05766225913891761</v>
+      </c>
+      <c r="AC23">
+        <v>-0.05766225913891761</v>
+      </c>
+      <c r="AD23">
+        <v>2612.9</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>2612.9</v>
+      </c>
+      <c r="AG23">
+        <v>2372.1</v>
+      </c>
+      <c r="AH23">
+        <v>0.6404480611794696</v>
+      </c>
+      <c r="AI23">
+        <v>0.5058759752957348</v>
+      </c>
+      <c r="AJ23">
+        <v>0.6178952852305287</v>
+      </c>
+      <c r="AK23">
+        <v>0.4817131368925533</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jiangsu Changshu Rural Commercial Bank Co., Ltd. (SHSE:601128)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.124</v>
+      </c>
+      <c r="E24">
+        <v>0.166</v>
+      </c>
+      <c r="F24">
+        <v>0.184</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>533.1</v>
+      </c>
+      <c r="L24">
+        <v>0.450519732950224</v>
+      </c>
+      <c r="M24">
+        <v>69.5</v>
+      </c>
+      <c r="N24">
+        <v>0.02222648629633183</v>
+      </c>
+      <c r="O24">
+        <v>0.1303695366722941</v>
+      </c>
+      <c r="P24">
+        <v>69.5</v>
+      </c>
+      <c r="Q24">
+        <v>0.02222648629633183</v>
+      </c>
+      <c r="R24">
+        <v>0.1303695366722941</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>2096.2</v>
+      </c>
+      <c r="V24">
+        <v>0.6703764111420256</v>
+      </c>
+      <c r="W24">
+        <v>0.1586371075732778</v>
+      </c>
+      <c r="X24">
+        <v>0.07966396144756743</v>
+      </c>
+      <c r="Y24">
+        <v>0.07897314612571035</v>
+      </c>
+      <c r="Z24">
+        <v>0.1527152022156804</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.0578075286588997</v>
+      </c>
+      <c r="AC24">
+        <v>-0.0578075286588997</v>
+      </c>
+      <c r="AD24">
+        <v>4981.5</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>4981.5</v>
+      </c>
+      <c r="AG24">
+        <v>2885.3</v>
+      </c>
+      <c r="AH24">
+        <v>0.6143628829362143</v>
+      </c>
+      <c r="AI24">
+        <v>0.5410557184750733</v>
+      </c>
+      <c r="AJ24">
+        <v>0.4799075213732078</v>
+      </c>
+      <c r="AK24">
+        <v>0.4057630646340777</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jiangxi Bank Co., Ltd. (SEHK:1916)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>-0.123</v>
+      </c>
+      <c r="E25">
+        <v>-0.304</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>63</v>
+      </c>
+      <c r="L25">
+        <v>0.1221403644823575</v>
+      </c>
+      <c r="M25">
+        <v>80.3</v>
+      </c>
+      <c r="N25">
+        <v>0.1418226774991169</v>
+      </c>
+      <c r="O25">
+        <v>1.274603174603175</v>
+      </c>
+      <c r="P25">
+        <v>80.3</v>
+      </c>
+      <c r="Q25">
+        <v>0.1418226774991169</v>
+      </c>
+      <c r="R25">
+        <v>1.274603174603175</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>994.4</v>
+      </c>
+      <c r="V25">
+        <v>1.756269869304133</v>
+      </c>
+      <c r="W25">
+        <v>0.009692009476631489</v>
+      </c>
+      <c r="X25">
+        <v>0.3710142947217294</v>
+      </c>
+      <c r="Y25">
+        <v>-0.3613222852450979</v>
+      </c>
+      <c r="Z25">
+        <v>0.02722874367115153</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.05839091011210708</v>
+      </c>
+      <c r="AC25">
+        <v>-0.05839091011210708</v>
+      </c>
+      <c r="AD25">
+        <v>15157.7</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>15157.7</v>
+      </c>
+      <c r="AG25">
+        <v>14163.3</v>
+      </c>
+      <c r="AH25">
+        <v>0.9639911217954833</v>
+      </c>
+      <c r="AI25">
+        <v>0.6955625917767989</v>
+      </c>
+      <c r="AJ25">
+        <v>0.9615601344241148</v>
+      </c>
+      <c r="AK25">
+        <v>0.6810064622841097</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bank of Zhengzhou Co., Ltd. (SEHK:6196)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.0746</v>
+      </c>
+      <c r="E26">
+        <v>-0.16</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>191.5</v>
+      </c>
+      <c r="L26">
+        <v>0.2702130661775081</v>
+      </c>
+      <c r="M26">
+        <v>-0</v>
+      </c>
+      <c r="N26">
+        <v>-0</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-0</v>
+      </c>
+      <c r="Q26">
+        <v>-0</v>
+      </c>
+      <c r="R26">
+        <v>-0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>1430</v>
+      </c>
+      <c r="V26">
+        <v>0.6210640608034745</v>
+      </c>
+      <c r="W26">
+        <v>0.02604450005440104</v>
+      </c>
+      <c r="X26">
+        <v>0.1963608518513128</v>
+      </c>
+      <c r="Y26">
+        <v>-0.1703163517969117</v>
+      </c>
+      <c r="Z26">
+        <v>0.0230915352759287</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.0585171191055224</v>
+      </c>
+      <c r="AC26">
+        <v>-0.0585171191055224</v>
+      </c>
+      <c r="AD26">
+        <v>26888.1</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>26888.1</v>
+      </c>
+      <c r="AG26">
+        <v>25458.1</v>
+      </c>
+      <c r="AH26">
+        <v>0.9211218679986023</v>
+      </c>
+      <c r="AI26">
+        <v>0.76853005739373</v>
+      </c>
+      <c r="AJ26">
+        <v>0.917058709105711</v>
+      </c>
+      <c r="AK26">
+        <v>0.7586660070806165</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jinshang Bank Co., Ltd. (SEHK:2558)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.0585</v>
+      </c>
+      <c r="E27">
+        <v>0.0781</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>275.1</v>
+      </c>
+      <c r="L27">
+        <v>0.4596491228070176</v>
+      </c>
+      <c r="M27">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.07427937915742794</v>
+      </c>
+      <c r="O27">
+        <v>0.292257360959651</v>
+      </c>
+      <c r="P27">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="Q27">
+        <v>0.07427937915742794</v>
+      </c>
+      <c r="R27">
+        <v>0.292257360959651</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>1174.9</v>
+      </c>
+      <c r="V27">
+        <v>1.085458240946046</v>
+      </c>
+      <c r="W27">
+        <v>0.08367042793272302</v>
+      </c>
+      <c r="X27">
+        <v>0.124993069322591</v>
+      </c>
+      <c r="Y27">
+        <v>-0.04132264138986801</v>
+      </c>
+      <c r="Z27">
+        <v>0.06856769699608184</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.05873710842736634</v>
+      </c>
+      <c r="AC27">
+        <v>-0.05873710842736634</v>
+      </c>
+      <c r="AD27">
+        <v>5964.4</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>5964.4</v>
+      </c>
+      <c r="AG27">
+        <v>4789.5</v>
+      </c>
+      <c r="AH27">
+        <v>0.846398365215417</v>
+      </c>
+      <c r="AI27">
+        <v>0.6313672354659779</v>
+      </c>
+      <c r="AJ27">
+        <v>0.8156644357022429</v>
+      </c>
+      <c r="AK27">
+        <v>0.579008450295579</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Wuxi Rural Commercial Bank Co.,Ltd (SHSE:600908)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.09630000000000001</v>
+      </c>
+      <c r="E28">
+        <v>0.139</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>326.5</v>
+      </c>
+      <c r="L28">
+        <v>0.5993024963289281</v>
+      </c>
+      <c r="M28">
+        <v>104.4</v>
+      </c>
+      <c r="N28">
+        <v>0.05875070343275183</v>
+      </c>
+      <c r="O28">
+        <v>0.3197549770290965</v>
+      </c>
+      <c r="P28">
+        <v>104.4</v>
+      </c>
+      <c r="Q28">
+        <v>0.05875070343275183</v>
+      </c>
+      <c r="R28">
+        <v>0.3197549770290965</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>1515</v>
+      </c>
+      <c r="V28">
+        <v>0.8525604952166573</v>
+      </c>
+      <c r="W28">
+        <v>0.1152569895509743</v>
+      </c>
+      <c r="X28">
+        <v>0.07053449700118461</v>
+      </c>
+      <c r="Y28">
+        <v>0.04472249254978969</v>
+      </c>
+      <c r="Z28">
+        <v>0.1448011907293217</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.05874667072896782</v>
+      </c>
+      <c r="AC28">
+        <v>-0.05874667072896782</v>
+      </c>
+      <c r="AD28">
+        <v>1429</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>1429</v>
+      </c>
+      <c r="AG28">
+        <v>-86</v>
+      </c>
+      <c r="AH28">
+        <v>0.4457267623206488</v>
+      </c>
+      <c r="AI28">
+        <v>0.3055769395261312</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.0508574807806032</v>
+      </c>
+      <c r="AK28">
+        <v>-0.02720313785031948</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bank of Ningbo Co., Ltd. (SZSE:002142)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0.162</v>
+      </c>
+      <c r="E29">
+        <v>0.157</v>
+      </c>
+      <c r="F29">
+        <v>0.0684</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2.933424741449365E-05</v>
+      </c>
+      <c r="J29">
+        <v>2.602503409276726E-05</v>
+      </c>
+      <c r="K29">
+        <v>3833.9</v>
+      </c>
+      <c r="L29">
+        <v>0.4913114796114514</v>
+      </c>
+      <c r="M29">
+        <v>567.9096</v>
+      </c>
+      <c r="N29">
+        <v>0.02582170186646054</v>
+      </c>
+      <c r="O29">
+        <v>0.1481284331881374</v>
+      </c>
+      <c r="P29">
+        <v>567.9096</v>
+      </c>
+      <c r="Q29">
+        <v>0.02582170186646054</v>
+      </c>
+      <c r="R29">
+        <v>0.1481284331881374</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>14053.2</v>
+      </c>
+      <c r="V29">
+        <v>0.638970604951463</v>
+      </c>
+      <c r="W29">
+        <v>0.1550121498085546</v>
+      </c>
+      <c r="X29">
+        <v>0.1205940161553538</v>
+      </c>
+      <c r="Y29">
+        <v>0.03441813365320079</v>
+      </c>
+      <c r="Z29">
+        <v>0.06382388855085867</v>
+      </c>
+      <c r="AA29">
+        <v>1.661018875469075E-06</v>
+      </c>
+      <c r="AB29">
+        <v>0.05876515165223047</v>
+      </c>
+      <c r="AC29">
+        <v>-0.058763490633355</v>
+      </c>
+      <c r="AD29">
+        <v>112830.6</v>
+      </c>
+      <c r="AE29">
+        <v>0.2654656686287011</v>
+      </c>
+      <c r="AF29">
+        <v>112830.8654656686</v>
+      </c>
+      <c r="AG29">
+        <v>98777.66546566864</v>
+      </c>
+      <c r="AH29">
+        <v>0.8368729574655378</v>
+      </c>
+      <c r="AI29">
+        <v>0.7799767619616893</v>
+      </c>
+      <c r="AJ29">
+        <v>0.8178911339043752</v>
+      </c>
+      <c r="AK29">
+        <v>0.7563022828494402</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>400108.5106382979</v>
+      </c>
+      <c r="AP29">
+        <v>350275.4094527257</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Zhongyuan Bank Co., Ltd. (SEHK:1216)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.0414</v>
+      </c>
+      <c r="E30">
+        <v>0.0438</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>449.8</v>
+      </c>
+      <c r="L30">
+        <v>0.2517913121361397</v>
+      </c>
+      <c r="M30">
+        <v>97.3</v>
+      </c>
+      <c r="N30">
+        <v>0.06892887503542081</v>
+      </c>
+      <c r="O30">
+        <v>0.2163183637172076</v>
+      </c>
+      <c r="P30">
+        <v>97.3</v>
+      </c>
+      <c r="Q30">
+        <v>0.06892887503542081</v>
+      </c>
+      <c r="R30">
+        <v>0.2163183637172076</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>8139.8</v>
+      </c>
+      <c r="V30">
+        <v>5.766364409181072</v>
+      </c>
+      <c r="W30">
+        <v>0.03984480192757424</v>
+      </c>
+      <c r="X30">
+        <v>0.4167589077341714</v>
+      </c>
+      <c r="Y30">
+        <v>-0.3769141058065972</v>
+      </c>
+      <c r="Z30">
+        <v>0.0333694474539545</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.06019359658391842</v>
+      </c>
+      <c r="AC30">
+        <v>-0.06019359658391842</v>
+      </c>
+      <c r="AD30">
+        <v>43370.1</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>43370.1</v>
+      </c>
+      <c r="AG30">
+        <v>35230.3</v>
+      </c>
+      <c r="AH30">
+        <v>0.9684781953342548</v>
+      </c>
+      <c r="AI30">
+        <v>0.7612729395037783</v>
+      </c>
+      <c r="AJ30">
+        <v>0.9614757968336796</v>
+      </c>
+      <c r="AK30">
+        <v>0.7214784961100291</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Harbin Bank Co., Ltd. (SEHK:6138)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>-0.108</v>
+      </c>
+      <c r="E31">
+        <v>-0.291</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>125.8</v>
+      </c>
+      <c r="L31">
+        <v>0.1439688715953308</v>
+      </c>
+      <c r="M31">
+        <v>76.7</v>
+      </c>
+      <c r="N31">
+        <v>0.1617460986925348</v>
+      </c>
+      <c r="O31">
+        <v>0.609697933227345</v>
+      </c>
+      <c r="P31">
+        <v>76.7</v>
+      </c>
+      <c r="Q31">
+        <v>0.1617460986925348</v>
+      </c>
+      <c r="R31">
+        <v>0.609697933227345</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>11383.9</v>
+      </c>
+      <c r="V31">
+        <v>24.00653732602278</v>
+      </c>
+      <c r="W31">
+        <v>0.01478625747834366</v>
+      </c>
+      <c r="X31">
+        <v>0.3648825458603454</v>
+      </c>
+      <c r="Y31">
+        <v>-0.3500962883820017</v>
+      </c>
+      <c r="Z31">
+        <v>0.1422756285007164</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.06019914227037429</v>
+      </c>
+      <c r="AC31">
+        <v>-0.06019914227037429</v>
+      </c>
+      <c r="AD31">
+        <v>12443.5</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>12443.5</v>
+      </c>
+      <c r="AG31">
+        <v>1059.6</v>
+      </c>
+      <c r="AH31">
+        <v>0.9632906786811893</v>
+      </c>
+      <c r="AI31">
+        <v>0.5819342468315952</v>
+      </c>
+      <c r="AJ31">
+        <v>0.6908332246707525</v>
+      </c>
+      <c r="AK31">
+        <v>0.1059695372583533</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Huishang Bank Corporation Limited (SEHK:3698)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0906</v>
+      </c>
+      <c r="E32">
+        <v>0.09759999999999999</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>2058.9</v>
+      </c>
+      <c r="L32">
+        <v>0.5309727666597895</v>
+      </c>
+      <c r="M32">
+        <v>848</v>
+      </c>
+      <c r="N32">
+        <v>0.1919898571396228</v>
+      </c>
+      <c r="O32">
+        <v>0.4118704162416824</v>
+      </c>
+      <c r="P32">
+        <v>848</v>
+      </c>
+      <c r="Q32">
+        <v>0.1919898571396228</v>
+      </c>
+      <c r="R32">
+        <v>0.4118704162416824</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>2508</v>
+      </c>
+      <c r="V32">
+        <v>0.5678190586157713</v>
+      </c>
+      <c r="W32">
+        <v>0.1173122286417558</v>
+      </c>
+      <c r="X32">
+        <v>0.2148869833719676</v>
+      </c>
+      <c r="Y32">
+        <v>-0.09757475473021175</v>
+      </c>
+      <c r="Z32">
+        <v>0.05722051946480457</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.0602347678824403</v>
+      </c>
+      <c r="AC32">
+        <v>-0.0602347678824403</v>
+      </c>
+      <c r="AD32">
+        <v>58651</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>58651</v>
+      </c>
+      <c r="AG32">
+        <v>56143</v>
+      </c>
+      <c r="AH32">
+        <v>0.9299659573253588</v>
+      </c>
+      <c r="AI32">
+        <v>0.7337492634484001</v>
+      </c>
+      <c r="AJ32">
+        <v>0.9270655995138697</v>
+      </c>
+      <c r="AK32">
+        <v>0.7251247331298684</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bank of Gansu Co., Ltd. (SEHK:2139)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>-0.0823</v>
+      </c>
+      <c r="E33">
+        <v>-0.184</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>86.8</v>
+      </c>
+      <c r="L33">
+        <v>0.2140039447731755</v>
+      </c>
+      <c r="M33">
+        <v>0.004</v>
+      </c>
+      <c r="N33">
+        <v>8.279859242392879E-06</v>
+      </c>
+      <c r="O33">
+        <v>4.608294930875576E-05</v>
+      </c>
+      <c r="P33">
+        <v>0.004</v>
+      </c>
+      <c r="Q33">
+        <v>8.279859242392879E-06</v>
+      </c>
+      <c r="R33">
+        <v>4.608294930875576E-05</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>824.5</v>
+      </c>
+      <c r="V33">
+        <v>1.706685986338232</v>
+      </c>
+      <c r="W33">
+        <v>0.01910085161631054</v>
+      </c>
+      <c r="X33">
+        <v>0.2021517848960381</v>
+      </c>
+      <c r="Y33">
+        <v>-0.1830509332797276</v>
+      </c>
+      <c r="Z33">
+        <v>0.04709980839574987</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.06024102042132959</v>
+      </c>
+      <c r="AC33">
+        <v>-0.06024102042132959</v>
+      </c>
+      <c r="AD33">
+        <v>5883.3</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>5883.3</v>
+      </c>
+      <c r="AG33">
+        <v>5058.8</v>
+      </c>
+      <c r="AH33">
+        <v>0.9241172405126916</v>
+      </c>
+      <c r="AI33">
+        <v>0.5599196756571558</v>
+      </c>
+      <c r="AJ33">
+        <v>0.9128277305617206</v>
+      </c>
+      <c r="AK33">
+        <v>0.5224467876359354</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Guangzhou Rural Commercial Bank Co., Ltd. (SEHK:1551)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>-0.0806</v>
+      </c>
+      <c r="E34">
+        <v>-0.166</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>371.5</v>
+      </c>
+      <c r="L34">
+        <v>0.2702801018552201</v>
+      </c>
+      <c r="M34">
+        <v>169.6</v>
+      </c>
+      <c r="N34">
+        <v>0.05643363391341962</v>
+      </c>
+      <c r="O34">
+        <v>0.4565275908479138</v>
+      </c>
+      <c r="P34">
+        <v>169.6</v>
+      </c>
+      <c r="Q34">
+        <v>0.05643363391341962</v>
+      </c>
+      <c r="R34">
+        <v>0.4565275908479138</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>6332.4</v>
+      </c>
+      <c r="V34">
+        <v>2.107077496422986</v>
+      </c>
+      <c r="W34">
+        <v>0.03595834059275606</v>
+      </c>
+      <c r="X34">
+        <v>0.1807383066602523</v>
+      </c>
+      <c r="Y34">
+        <v>-0.1447799660674962</v>
+      </c>
+      <c r="Z34">
+        <v>0.04059350090519519</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.0602542725657123</v>
+      </c>
+      <c r="AC34">
+        <v>-0.0602542725657123</v>
+      </c>
+      <c r="AD34">
+        <v>31037.9</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>31037.9</v>
+      </c>
+      <c r="AG34">
+        <v>24705.5</v>
+      </c>
+      <c r="AH34">
+        <v>0.9117209898011936</v>
+      </c>
+      <c r="AI34">
+        <v>0.6950957052988957</v>
+      </c>
+      <c r="AJ34">
+        <v>0.891547699813791</v>
+      </c>
+      <c r="AK34">
+        <v>0.6447105059198388</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Shengjing Bank Co., Ltd. (SEHK:2066)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>-0.07679999999999999</v>
+      </c>
+      <c r="E35">
+        <v>-0.363</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="L35">
+        <v>0.0831130379612985</v>
+      </c>
+      <c r="M35">
+        <v>0.308</v>
+      </c>
+      <c r="N35">
+        <v>0.0002266372332597498</v>
+      </c>
+      <c r="O35">
+        <v>0.003918575063613232</v>
+      </c>
+      <c r="P35">
+        <v>0.308</v>
+      </c>
+      <c r="Q35">
+        <v>0.0002266372332597498</v>
+      </c>
+      <c r="R35">
+        <v>0.003918575063613232</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>7907.6</v>
+      </c>
+      <c r="V35">
+        <v>5.8186902133922</v>
+      </c>
+      <c r="W35">
+        <v>0.006983935172021609</v>
+      </c>
+      <c r="X35">
+        <v>0.1655888824085038</v>
+      </c>
+      <c r="Y35">
+        <v>-0.1586049472364821</v>
+      </c>
+      <c r="Z35">
+        <v>0.03767819151055404</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.06026660495956905</v>
+      </c>
+      <c r="AC35">
+        <v>-0.06026660495956905</v>
+      </c>
+      <c r="AD35">
+        <v>12256.2</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>12256.2</v>
+      </c>
+      <c r="AG35">
+        <v>4348.6</v>
+      </c>
+      <c r="AH35">
+        <v>0.9001850872554205</v>
+      </c>
+      <c r="AI35">
+        <v>0.52660932035164</v>
+      </c>
+      <c r="AJ35">
+        <v>0.7618964188100077</v>
+      </c>
+      <c r="AK35">
+        <v>0.2829977483047207</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bank of Guizhou Co., Ltd. (SEHK:6199)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.0304</v>
+      </c>
+      <c r="E36">
+        <v>0.0218</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>491.2</v>
+      </c>
+      <c r="L36">
+        <v>0.4490766136405193</v>
+      </c>
+      <c r="M36">
+        <v>139.1</v>
+      </c>
+      <c r="N36">
+        <v>0.06223992124927289</v>
+      </c>
+      <c r="O36">
+        <v>0.2831840390879479</v>
+      </c>
+      <c r="P36">
+        <v>139.1</v>
+      </c>
+      <c r="Q36">
+        <v>0.06223992124927289</v>
+      </c>
+      <c r="R36">
+        <v>0.2831840390879479</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>2071.6</v>
+      </c>
+      <c r="V36">
+        <v>0.9269318537742181</v>
+      </c>
+      <c r="W36">
+        <v>0.07592197594979752</v>
+      </c>
+      <c r="X36">
+        <v>0.1587084990134794</v>
+      </c>
+      <c r="Y36">
+        <v>-0.08278652306368184</v>
+      </c>
+      <c r="Z36">
+        <v>0.04319768727686329</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0.06027333741019839</v>
+      </c>
+      <c r="AC36">
+        <v>-0.06027333741019839</v>
+      </c>
+      <c r="AD36">
+        <v>18826.7</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>18826.7</v>
+      </c>
+      <c r="AG36">
+        <v>16755.1</v>
+      </c>
+      <c r="AH36">
+        <v>0.8938874539446195</v>
+      </c>
+      <c r="AI36">
+        <v>0.7311453381800106</v>
+      </c>
+      <c r="AJ36">
+        <v>0.8823117430226435</v>
+      </c>
+      <c r="AK36">
+        <v>0.7076231100599714</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Weihai City Commercial Bank Co., Ltd. (SEHK:9677)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>269.8</v>
+      </c>
+      <c r="L37">
+        <v>0.4384140396490088</v>
+      </c>
+      <c r="M37">
+        <v>122.4</v>
+      </c>
+      <c r="N37">
+        <v>0.05501123595505619</v>
+      </c>
+      <c r="O37">
+        <v>0.4536693847294292</v>
+      </c>
+      <c r="P37">
+        <v>122.4</v>
+      </c>
+      <c r="Q37">
+        <v>0.05501123595505619</v>
+      </c>
+      <c r="R37">
+        <v>0.4536693847294292</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>1211.7</v>
+      </c>
+      <c r="V37">
+        <v>0.5445842696629214</v>
+      </c>
+      <c r="W37">
+        <v>0.07688800227985182</v>
+      </c>
+      <c r="X37">
+        <v>0.1299732049093949</v>
+      </c>
+      <c r="Y37">
+        <v>-0.05308520262954311</v>
+      </c>
+      <c r="Z37">
+        <v>0.04705720424845347</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0.06031392341336334</v>
+      </c>
+      <c r="AC37">
+        <v>-0.06031392341336334</v>
+      </c>
+      <c r="AD37">
+        <v>13218.1</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>13218.1</v>
+      </c>
+      <c r="AG37">
+        <v>12006.4</v>
+      </c>
+      <c r="AH37">
+        <v>0.8559227098186245</v>
+      </c>
+      <c r="AI37">
+        <v>0.7661245450119398</v>
+      </c>
+      <c r="AJ37">
+        <v>0.8436555785094931</v>
+      </c>
+      <c r="AK37">
+        <v>0.7484586852850419</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Bank of Chongqing Co., Ltd. (SEHK:1963)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D38">
         <v>0.0381</v>
       </c>
-      <c r="E3">
+      <c r="E38">
         <v>0.04099999999999999</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
         <v>725.3</v>
       </c>
-      <c r="L3">
+      <c r="L38">
         <v>0.5298027757487217</v>
       </c>
-      <c r="M3">
+      <c r="M38">
         <v>213.8</v>
       </c>
-      <c r="N3">
+      <c r="N38">
         <v>0.05863960504662644</v>
       </c>
-      <c r="O3">
+      <c r="O38">
         <v>0.2947745760375017</v>
       </c>
-      <c r="P3">
+      <c r="P38">
         <v>213.8</v>
       </c>
-      <c r="Q3">
+      <c r="Q38">
         <v>0.05863960504662644</v>
       </c>
-      <c r="R3">
+      <c r="R38">
         <v>0.2947745760375017</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
         <v>1853.9</v>
       </c>
-      <c r="V3">
+      <c r="V38">
         <v>0.5084750411409764</v>
       </c>
-      <c r="W3">
+      <c r="W38">
         <v>0.09945834761741515</v>
       </c>
-      <c r="X3">
-        <v>0.1920325325413729</v>
-      </c>
-      <c r="Y3">
-        <v>-0.09257418492395775</v>
-      </c>
-      <c r="Z3">
+      <c r="X38">
+        <v>0.1919679697397795</v>
+      </c>
+      <c r="Y38">
+        <v>-0.09250962212236438</v>
+      </c>
+      <c r="Z38">
         <v>0.03226962224034623</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06163010589969715</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06163010589969715</v>
-      </c>
-      <c r="AD3">
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0.06162485610711413</v>
+      </c>
+      <c r="AC38">
+        <v>-0.06162485610711413</v>
+      </c>
+      <c r="AD38">
         <v>41193.1</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
         <v>41193.1</v>
       </c>
-      <c r="AG3">
+      <c r="AG38">
         <v>39339.2</v>
       </c>
-      <c r="AH3">
+      <c r="AH38">
         <v>0.9186870387675042</v>
       </c>
-      <c r="AI3">
+      <c r="AI38">
         <v>0.8210556318503356</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ38">
         <v>0.9151801085024613</v>
       </c>
-      <c r="AK3">
+      <c r="AK38">
         <v>0.8141896227000848</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
         <v>0</v>
       </c>
     </row>
